--- a/Book2026.xlsx
+++ b/Book2026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\syana05012019\2024\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{04B04301-B2FD-4B6B-9C78-5CA0C5B84D01}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{633226A8-D1B9-4A90-B877-1AEAD4AC32C0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" tabRatio="947" firstSheet="11" activeTab="22" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -47,7 +47,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="735" uniqueCount="255">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="738" uniqueCount="258">
   <si>
     <t>صفحة الإيرادات</t>
   </si>
@@ -812,6 +812,15 @@
   </si>
   <si>
     <t>تحت حساب فاتورة المياه عن شهر فبراير /2025</t>
+  </si>
+  <si>
+    <t>تحت حساب كهرباء شهر فبراير /2026</t>
+  </si>
+  <si>
+    <t>تحت حساب اكرامية للمحصل</t>
+  </si>
+  <si>
+    <t>تحت حساب كهربة خلفية المنزل</t>
   </si>
 </sst>
 </file>
@@ -12629,11 +12638,11 @@
       </c>
       <c r="D5" s="71">
         <f>outcomes!C3</f>
-        <v>4633</v>
+        <v>5339</v>
       </c>
       <c r="E5" s="72">
         <f>(C3+C5)-D5</f>
-        <v>11569</v>
+        <v>10863</v>
       </c>
       <c r="F5" s="2"/>
       <c r="G5" s="2"/>
@@ -13020,7 +13029,7 @@
       </c>
       <c r="C3" s="53">
         <f>SUM(C5:C2002)</f>
-        <v>4633</v>
+        <v>5339</v>
       </c>
     </row>
     <row r="4" spans="1:19" ht="36" x14ac:dyDescent="0.2">
@@ -13233,9 +13242,15 @@
       <c r="A14" s="33">
         <v>10</v>
       </c>
-      <c r="B14" s="60"/>
-      <c r="C14" s="55"/>
-      <c r="D14" s="8"/>
+      <c r="B14" s="60">
+        <v>46075</v>
+      </c>
+      <c r="C14" s="55">
+        <v>683</v>
+      </c>
+      <c r="D14" s="8" t="s">
+        <v>255</v>
+      </c>
       <c r="S14">
         <v>1</v>
       </c>
@@ -13244,9 +13259,15 @@
       <c r="A15" s="33">
         <v>11</v>
       </c>
-      <c r="B15" s="60"/>
-      <c r="C15" s="55"/>
-      <c r="D15" s="8"/>
+      <c r="B15" s="60">
+        <v>46075</v>
+      </c>
+      <c r="C15" s="55">
+        <v>3</v>
+      </c>
+      <c r="D15" s="8" t="s">
+        <v>256</v>
+      </c>
       <c r="E15" s="2"/>
       <c r="F15" s="2"/>
       <c r="G15" s="2"/>
@@ -13261,9 +13282,15 @@
       <c r="A16" s="33">
         <v>12</v>
       </c>
-      <c r="B16" s="60"/>
-      <c r="C16" s="55"/>
-      <c r="D16" s="8"/>
+      <c r="B16" s="60">
+        <v>46075</v>
+      </c>
+      <c r="C16" s="55">
+        <v>20</v>
+      </c>
+      <c r="D16" s="8" t="s">
+        <v>257</v>
+      </c>
       <c r="S16">
         <v>6</v>
       </c>

--- a/Book2026.xlsx
+++ b/Book2026.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\syana05012019\2024\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{633226A8-D1B9-4A90-B877-1AEAD4AC32C0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B0E0217F-CCF4-472F-A986-3E6888766298}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" tabRatio="947" firstSheet="11" activeTab="22" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" tabRatio="947" firstSheet="11" activeTab="19" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="monthly_elctricity" sheetId="28" r:id="rId1"/>
@@ -47,7 +47,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="738" uniqueCount="258">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="740" uniqueCount="258">
   <si>
     <t>صفحة الإيرادات</t>
   </si>
@@ -10583,7 +10583,7 @@
       <c r="C4" s="10"/>
       <c r="D4" s="11">
         <f>SUM(D6:D2001)</f>
-        <v>150</v>
+        <v>300</v>
       </c>
       <c r="E4" s="11"/>
       <c r="F4" s="11">
@@ -10660,7 +10660,9 @@
       <c r="C7" s="51">
         <v>46087</v>
       </c>
-      <c r="D7" s="73"/>
+      <c r="D7" s="73">
+        <v>150</v>
+      </c>
       <c r="E7" s="8"/>
       <c r="F7" s="73">
         <v>150</v>
@@ -11283,7 +11285,7 @@
       </c>
       <c r="C4" s="53">
         <f>SUM(C6:C2000)</f>
-        <v>2300</v>
+        <v>2450</v>
       </c>
     </row>
     <row r="5" spans="1:17" ht="18" x14ac:dyDescent="0.2">
@@ -11655,12 +11657,22 @@
       <c r="A19" s="8">
         <v>14</v>
       </c>
-      <c r="B19" s="51"/>
-      <c r="C19" s="55"/>
+      <c r="B19" s="51">
+        <v>46076</v>
+      </c>
+      <c r="C19" s="55">
+        <v>150</v>
+      </c>
       <c r="D19" s="8"/>
-      <c r="E19" s="8"/>
-      <c r="F19" s="8"/>
-      <c r="G19" s="8"/>
+      <c r="E19" s="8" t="s">
+        <v>186</v>
+      </c>
+      <c r="F19" s="8">
+        <v>1</v>
+      </c>
+      <c r="G19" s="8" t="s">
+        <v>230</v>
+      </c>
       <c r="H19" s="2"/>
       <c r="I19" s="2"/>
       <c r="J19" s="2"/>
@@ -12634,7 +12646,7 @@
       <c r="B5" s="9"/>
       <c r="C5" s="70">
         <f>incomes!C4</f>
-        <v>2300</v>
+        <v>2450</v>
       </c>
       <c r="D5" s="71">
         <f>outcomes!C3</f>
@@ -12642,7 +12654,7 @@
       </c>
       <c r="E5" s="72">
         <f>(C3+C5)-D5</f>
-        <v>10863</v>
+        <v>11013</v>
       </c>
       <c r="F5" s="2"/>
       <c r="G5" s="2"/>
@@ -19387,7 +19399,7 @@
       </c>
       <c r="C7" s="26">
         <f>Apartment1!D7</f>
-        <v>0</v>
+        <v>150</v>
       </c>
       <c r="D7" s="26">
         <f>Apartment2!D7</f>
@@ -20370,12 +20382,12 @@
       </c>
       <c r="C5" s="91">
         <f>Apartment1!D4</f>
-        <v>150</v>
+        <v>300</v>
       </c>
       <c r="D5" s="92"/>
       <c r="E5" s="94">
         <f>D5-C5</f>
-        <v>-150</v>
+        <v>-300</v>
       </c>
       <c r="F5" s="2" t="s">
         <v>50</v>

--- a/Book2026.xlsx
+++ b/Book2026.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\syana05012019\2024\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B0E0217F-CCF4-472F-A986-3E6888766298}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ED837289-3D1A-448C-A6C8-4E331A32C5E8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" tabRatio="947" firstSheet="11" activeTab="19" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" tabRatio="947" firstSheet="11" activeTab="12" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="monthly_elctricity" sheetId="28" r:id="rId1"/>
@@ -47,7 +47,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="740" uniqueCount="258">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="742" uniqueCount="258">
   <si>
     <t>صفحة الإيرادات</t>
   </si>
@@ -5324,7 +5324,7 @@
       <c r="C4" s="76"/>
       <c r="D4" s="83">
         <f>SUM(D6:D2001)</f>
-        <v>0</v>
+        <v>600</v>
       </c>
       <c r="E4" s="11"/>
       <c r="F4" s="83">
@@ -5371,7 +5371,9 @@
       <c r="C6" s="77">
         <v>45315</v>
       </c>
-      <c r="D6" s="33"/>
+      <c r="D6" s="33">
+        <v>300</v>
+      </c>
       <c r="E6" s="8"/>
       <c r="F6" s="33">
         <v>300</v>
@@ -5396,7 +5398,9 @@
       <c r="C7" s="77">
         <v>46080</v>
       </c>
-      <c r="D7" s="33"/>
+      <c r="D7" s="33">
+        <v>300</v>
+      </c>
       <c r="E7" s="8"/>
       <c r="F7" s="33">
         <v>300</v>
@@ -11285,7 +11289,7 @@
       </c>
       <c r="C4" s="53">
         <f>SUM(C6:C2000)</f>
-        <v>2450</v>
+        <v>2750</v>
       </c>
     </row>
     <row r="5" spans="1:17" ht="18" x14ac:dyDescent="0.2">
@@ -11684,11 +11688,22 @@
       <c r="A20" s="8">
         <v>15</v>
       </c>
-      <c r="B20" s="51"/>
-      <c r="C20" s="55"/>
-      <c r="E20" s="8"/>
-      <c r="F20" s="8"/>
-      <c r="G20" s="8"/>
+      <c r="B20" s="51">
+        <v>46079</v>
+      </c>
+      <c r="C20" s="55">
+        <v>300</v>
+      </c>
+      <c r="D20" s="8"/>
+      <c r="E20" s="8" t="s">
+        <v>249</v>
+      </c>
+      <c r="F20" s="8">
+        <v>8</v>
+      </c>
+      <c r="G20" s="8" t="s">
+        <v>223</v>
+      </c>
       <c r="H20" s="2"/>
       <c r="I20" s="2"/>
       <c r="J20" s="2"/>
@@ -12646,7 +12661,7 @@
       <c r="B5" s="9"/>
       <c r="C5" s="70">
         <f>incomes!C4</f>
-        <v>2450</v>
+        <v>2750</v>
       </c>
       <c r="D5" s="71">
         <f>outcomes!C3</f>
@@ -12654,7 +12669,7 @@
       </c>
       <c r="E5" s="72">
         <f>(C3+C5)-D5</f>
-        <v>11013</v>
+        <v>11313</v>
       </c>
       <c r="F5" s="2"/>
       <c r="G5" s="2"/>
@@ -19365,7 +19380,7 @@
       </c>
       <c r="J6" s="26">
         <f>Apartment8!D6</f>
-        <v>0</v>
+        <v>300</v>
       </c>
       <c r="K6" s="26">
         <f>Apartment9!D6</f>
@@ -19427,7 +19442,7 @@
       </c>
       <c r="J7" s="26">
         <f>Apartment8!D7</f>
-        <v>0</v>
+        <v>300</v>
       </c>
       <c r="K7" s="26">
         <f>Apartment9!D7</f>
@@ -20570,12 +20585,12 @@
       </c>
       <c r="C12" s="91">
         <f>Apartment8!D4</f>
-        <v>0</v>
+        <v>600</v>
       </c>
       <c r="D12" s="92"/>
       <c r="E12" s="94">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>-600</v>
       </c>
       <c r="F12" s="2" t="s">
         <v>120</v>

--- a/Book2026.xlsx
+++ b/Book2026.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\syana05012019\2024\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ED837289-3D1A-448C-A6C8-4E331A32C5E8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{76B75B5F-20DE-4BE6-AB60-E439836D5031}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" tabRatio="947" firstSheet="11" activeTab="12" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" tabRatio="947" firstSheet="11" activeTab="13" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="monthly_elctricity" sheetId="28" r:id="rId1"/>
@@ -47,7 +47,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="742" uniqueCount="258">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="750" uniqueCount="258">
   <si>
     <t>صفحة الإيرادات</t>
   </si>
@@ -5986,7 +5986,7 @@
       <c r="C4" s="49"/>
       <c r="D4" s="83">
         <f>SUM(D6:D2001)</f>
-        <v>0</v>
+        <v>900</v>
       </c>
       <c r="E4" s="11"/>
       <c r="F4" s="83">
@@ -6033,7 +6033,9 @@
       <c r="C6" s="51">
         <v>45314</v>
       </c>
-      <c r="D6" s="33"/>
+      <c r="D6" s="33">
+        <v>300</v>
+      </c>
       <c r="E6" s="8"/>
       <c r="F6" s="33">
         <v>300</v>
@@ -6058,7 +6060,9 @@
       <c r="C7" s="51">
         <v>45322</v>
       </c>
-      <c r="D7" s="33"/>
+      <c r="D7" s="33">
+        <v>300</v>
+      </c>
       <c r="E7" s="8"/>
       <c r="F7" s="33">
         <v>300</v>
@@ -6083,7 +6087,9 @@
       <c r="C8" s="51">
         <v>46084</v>
       </c>
-      <c r="D8" s="33"/>
+      <c r="D8" s="33">
+        <v>300</v>
+      </c>
       <c r="E8" s="8"/>
       <c r="F8" s="33">
         <v>300</v>
@@ -7965,7 +7971,7 @@
       <c r="C4" s="10"/>
       <c r="D4" s="11">
         <f>SUM(D6:D2001)</f>
-        <v>0</v>
+        <v>450</v>
       </c>
       <c r="E4" s="11"/>
       <c r="F4" s="11">
@@ -8012,7 +8018,9 @@
       <c r="C6" s="9">
         <v>45292</v>
       </c>
-      <c r="D6" s="8"/>
+      <c r="D6" s="8">
+        <v>150</v>
+      </c>
       <c r="E6" s="8"/>
       <c r="F6" s="8">
         <v>150</v>
@@ -8037,7 +8045,9 @@
       <c r="C7" s="9">
         <v>45322</v>
       </c>
-      <c r="D7" s="8"/>
+      <c r="D7" s="8">
+        <v>150</v>
+      </c>
       <c r="E7" s="8"/>
       <c r="F7" s="8">
         <v>150</v>
@@ -8062,7 +8072,9 @@
       <c r="C8" s="63">
         <v>46084</v>
       </c>
-      <c r="D8" s="8"/>
+      <c r="D8" s="8">
+        <v>150</v>
+      </c>
       <c r="E8" s="8"/>
       <c r="F8" s="8">
         <v>150</v>
@@ -8624,7 +8636,7 @@
       <c r="C4" s="62"/>
       <c r="D4" s="11">
         <f>SUM(D6:D2001)</f>
-        <v>0</v>
+        <v>450</v>
       </c>
       <c r="E4" s="11"/>
       <c r="F4" s="11">
@@ -8671,7 +8683,9 @@
       <c r="C6" s="63">
         <v>45292</v>
       </c>
-      <c r="D6" s="8"/>
+      <c r="D6" s="8">
+        <v>150</v>
+      </c>
       <c r="E6" s="8"/>
       <c r="F6" s="8">
         <v>150</v>
@@ -8696,7 +8710,9 @@
       <c r="C7" s="63">
         <v>45322</v>
       </c>
-      <c r="D7" s="8"/>
+      <c r="D7" s="8">
+        <v>150</v>
+      </c>
       <c r="E7" s="8"/>
       <c r="F7" s="8">
         <v>150</v>
@@ -8721,7 +8737,9 @@
       <c r="C8" s="63">
         <v>46084</v>
       </c>
-      <c r="D8" s="8"/>
+      <c r="D8" s="8">
+        <v>150</v>
+      </c>
       <c r="E8" s="8"/>
       <c r="F8" s="8">
         <v>150</v>
@@ -9283,7 +9301,7 @@
       <c r="C4" s="76"/>
       <c r="D4" s="11">
         <f>SUM(D6:D2001)</f>
-        <v>150</v>
+        <v>225</v>
       </c>
       <c r="E4" s="11"/>
       <c r="F4" s="83">
@@ -9384,7 +9402,9 @@
       <c r="C8" s="77">
         <v>46122</v>
       </c>
-      <c r="D8" s="8"/>
+      <c r="D8" s="8">
+        <v>75</v>
+      </c>
       <c r="E8" s="8"/>
       <c r="F8" s="33">
         <v>75</v>
@@ -11289,7 +11309,7 @@
       </c>
       <c r="C4" s="53">
         <f>SUM(C6:C2000)</f>
-        <v>2750</v>
+        <v>3425</v>
       </c>
     </row>
     <row r="5" spans="1:17" ht="18" x14ac:dyDescent="0.2">
@@ -11715,12 +11735,21 @@
       <c r="A21" s="8">
         <v>16</v>
       </c>
-      <c r="B21" s="51"/>
-      <c r="C21" s="55"/>
-      <c r="D21" s="8"/>
-      <c r="E21" s="8"/>
-      <c r="F21" s="8"/>
-      <c r="G21" s="8"/>
+      <c r="B21" s="51">
+        <v>46082</v>
+      </c>
+      <c r="C21" s="55">
+        <v>300</v>
+      </c>
+      <c r="E21" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="F21" s="8">
+        <v>7</v>
+      </c>
+      <c r="G21" s="8" t="s">
+        <v>224</v>
+      </c>
       <c r="H21" s="2"/>
       <c r="I21" s="2"/>
       <c r="J21" s="2"/>
@@ -11732,11 +11761,22 @@
       <c r="A22" s="8">
         <v>17</v>
       </c>
-      <c r="B22" s="51"/>
-      <c r="C22" s="55"/>
-      <c r="E22" s="8"/>
-      <c r="F22" s="8"/>
-      <c r="G22" s="8"/>
+      <c r="B22" s="51">
+        <v>46082</v>
+      </c>
+      <c r="C22" s="55">
+        <v>150</v>
+      </c>
+      <c r="D22" s="8"/>
+      <c r="E22" s="8" t="s">
+        <v>244</v>
+      </c>
+      <c r="F22" s="8">
+        <v>4</v>
+      </c>
+      <c r="G22" s="8" t="s">
+        <v>224</v>
+      </c>
       <c r="H22" s="2"/>
       <c r="I22" s="2"/>
       <c r="J22" s="2"/>
@@ -11748,12 +11788,22 @@
       <c r="A23" s="8">
         <v>18</v>
       </c>
-      <c r="B23" s="51"/>
-      <c r="C23" s="55"/>
+      <c r="B23" s="51">
+        <v>46082</v>
+      </c>
+      <c r="C23" s="55">
+        <v>150</v>
+      </c>
       <c r="D23" s="8"/>
-      <c r="E23" s="8"/>
-      <c r="F23" s="8"/>
-      <c r="G23" s="8"/>
+      <c r="E23" s="8" t="s">
+        <v>141</v>
+      </c>
+      <c r="F23" s="8">
+        <v>3</v>
+      </c>
+      <c r="G23" s="8" t="s">
+        <v>224</v>
+      </c>
       <c r="H23" s="2"/>
       <c r="I23" s="2"/>
       <c r="J23" s="2"/>
@@ -11765,12 +11815,21 @@
       <c r="A24" s="8">
         <v>19</v>
       </c>
-      <c r="B24" s="51"/>
-      <c r="C24" s="55"/>
-      <c r="D24" s="8"/>
-      <c r="E24" s="8"/>
-      <c r="F24" s="8"/>
-      <c r="G24" s="8"/>
+      <c r="B24" s="51">
+        <v>46082</v>
+      </c>
+      <c r="C24" s="55">
+        <v>75</v>
+      </c>
+      <c r="E24" s="8" t="s">
+        <v>160</v>
+      </c>
+      <c r="F24" s="8">
+        <v>2</v>
+      </c>
+      <c r="G24" s="8" t="s">
+        <v>224</v>
+      </c>
       <c r="H24" s="2"/>
       <c r="I24" s="2"/>
       <c r="J24" s="2"/>
@@ -12661,7 +12720,7 @@
       <c r="B5" s="9"/>
       <c r="C5" s="70">
         <f>incomes!C4</f>
-        <v>2750</v>
+        <v>3425</v>
       </c>
       <c r="D5" s="71">
         <f>outcomes!C3</f>
@@ -12669,7 +12728,7 @@
       </c>
       <c r="E5" s="72">
         <f>(C3+C5)-D5</f>
-        <v>11313</v>
+        <v>11988</v>
       </c>
       <c r="F5" s="2"/>
       <c r="G5" s="2"/>
@@ -19360,11 +19419,11 @@
       </c>
       <c r="E6" s="26">
         <f>Apartment3!D6</f>
-        <v>0</v>
+        <v>150</v>
       </c>
       <c r="F6" s="26">
         <f>Apartment4!D6</f>
-        <v>0</v>
+        <v>150</v>
       </c>
       <c r="G6" s="26">
         <f>Apartment5!D6</f>
@@ -19376,7 +19435,7 @@
       </c>
       <c r="I6" s="26">
         <f>Apartment7!D6</f>
-        <v>0</v>
+        <v>300</v>
       </c>
       <c r="J6" s="26">
         <f>Apartment8!D6</f>
@@ -19422,11 +19481,11 @@
       </c>
       <c r="E7" s="26">
         <f>Apartment3!D7</f>
-        <v>0</v>
+        <v>150</v>
       </c>
       <c r="F7" s="26">
         <f>Apartment4!D7</f>
-        <v>0</v>
+        <v>150</v>
       </c>
       <c r="G7" s="26">
         <f>Apartment5!D7</f>
@@ -19438,7 +19497,7 @@
       </c>
       <c r="I7" s="26">
         <f>Apartment7!D7</f>
-        <v>0</v>
+        <v>300</v>
       </c>
       <c r="J7" s="26">
         <f>Apartment8!D7</f>
@@ -19480,15 +19539,15 @@
       </c>
       <c r="D8" s="26">
         <f>Apartment2!D8</f>
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="E8" s="26">
         <f>Apartment3!D8</f>
-        <v>0</v>
+        <v>150</v>
       </c>
       <c r="F8" s="26">
         <f>Apartment4!D8</f>
-        <v>0</v>
+        <v>150</v>
       </c>
       <c r="G8" s="26">
         <f>Apartment5!D8</f>
@@ -19500,7 +19559,7 @@
       </c>
       <c r="I8" s="26">
         <f>Apartment7!D8</f>
-        <v>0</v>
+        <v>300</v>
       </c>
       <c r="J8" s="26">
         <f>Apartment8!D8</f>
@@ -20424,12 +20483,12 @@
       </c>
       <c r="C6" s="91">
         <f>Apartment2!D4</f>
-        <v>150</v>
+        <v>225</v>
       </c>
       <c r="D6" s="92"/>
       <c r="E6" s="94">
         <f t="shared" ref="E6:E18" si="0">D6-C6</f>
-        <v>-150</v>
+        <v>-225</v>
       </c>
       <c r="F6" s="2" t="s">
         <v>51</v>
@@ -20451,12 +20510,12 @@
       </c>
       <c r="C7" s="91">
         <f>Apartment3!D4</f>
-        <v>0</v>
+        <v>450</v>
       </c>
       <c r="D7" s="92"/>
       <c r="E7" s="94">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>-450</v>
       </c>
       <c r="F7" s="2" t="s">
         <v>48</v>
@@ -20478,12 +20537,12 @@
       </c>
       <c r="C8" s="91">
         <f>Apartment4!D4</f>
-        <v>0</v>
+        <v>450</v>
       </c>
       <c r="D8" s="92"/>
       <c r="E8" s="94">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>-450</v>
       </c>
       <c r="F8" s="2" t="s">
         <v>48</v>
@@ -20558,12 +20617,12 @@
       </c>
       <c r="C11" s="91">
         <f>Apartment7!D4</f>
-        <v>0</v>
+        <v>900</v>
       </c>
       <c r="D11" s="92"/>
       <c r="E11" s="94">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>-900</v>
       </c>
       <c r="F11" s="2" t="s">
         <v>48</v>

--- a/Book2026.xlsx
+++ b/Book2026.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\syana05012019\2024\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{76B75B5F-20DE-4BE6-AB60-E439836D5031}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{23807E75-7BAE-452C-BD64-CFC70D1C37BE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" tabRatio="947" firstSheet="11" activeTab="13" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" tabRatio="947" firstSheet="11" activeTab="22" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="monthly_elctricity" sheetId="28" r:id="rId1"/>
@@ -47,7 +47,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="750" uniqueCount="258">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="753" uniqueCount="261">
   <si>
     <t>صفحة الإيرادات</t>
   </si>
@@ -821,6 +821,15 @@
   </si>
   <si>
     <t>تحت حساب كهربة خلفية المنزل</t>
+  </si>
+  <si>
+    <t>تحت حساب نظافة السلم لام احمد عن شهر فبراير /2026</t>
+  </si>
+  <si>
+    <t>تحت حساب شراء اوتوماتيك للموتور</t>
+  </si>
+  <si>
+    <t>تحت حساب مواصلات لشراء الاوتوماتيك نوع ماكسيكى هاى بريشر</t>
   </si>
 </sst>
 </file>
@@ -12724,11 +12733,11 @@
       </c>
       <c r="D5" s="71">
         <f>outcomes!C3</f>
-        <v>5339</v>
+        <v>6649</v>
       </c>
       <c r="E5" s="72">
         <f>(C3+C5)-D5</f>
-        <v>11988</v>
+        <v>10678</v>
       </c>
       <c r="F5" s="2"/>
       <c r="G5" s="2"/>
@@ -13115,7 +13124,7 @@
       </c>
       <c r="C3" s="53">
         <f>SUM(C5:C2002)</f>
-        <v>5339</v>
+        <v>6649</v>
       </c>
     </row>
     <row r="4" spans="1:19" ht="36" x14ac:dyDescent="0.2">
@@ -13385,9 +13394,15 @@
       <c r="A17" s="33">
         <v>13</v>
       </c>
-      <c r="B17" s="60"/>
-      <c r="C17" s="55"/>
-      <c r="D17" s="8"/>
+      <c r="B17" s="60">
+        <v>46056</v>
+      </c>
+      <c r="C17" s="55">
+        <v>400</v>
+      </c>
+      <c r="D17" s="8" t="s">
+        <v>258</v>
+      </c>
       <c r="E17" s="2"/>
       <c r="F17" s="2"/>
       <c r="G17" s="2"/>
@@ -13402,9 +13417,15 @@
       <c r="A18" s="33">
         <v>14</v>
       </c>
-      <c r="B18" s="60"/>
-      <c r="C18" s="55"/>
-      <c r="D18" s="8"/>
+      <c r="B18" s="60">
+        <v>46057</v>
+      </c>
+      <c r="C18" s="55">
+        <v>900</v>
+      </c>
+      <c r="D18" s="8" t="s">
+        <v>259</v>
+      </c>
       <c r="E18" s="2"/>
       <c r="F18" s="2"/>
       <c r="G18" s="2"/>
@@ -13419,9 +13440,15 @@
       <c r="A19" s="33">
         <v>15</v>
       </c>
-      <c r="B19" s="60"/>
-      <c r="C19" s="55"/>
-      <c r="D19" s="8"/>
+      <c r="B19" s="60">
+        <v>46057</v>
+      </c>
+      <c r="C19" s="55">
+        <v>10</v>
+      </c>
+      <c r="D19" s="8" t="s">
+        <v>260</v>
+      </c>
       <c r="I19" s="2"/>
       <c r="J19" s="2"/>
       <c r="S19">

--- a/Book2026.xlsx
+++ b/Book2026.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\syana05012019\2024\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{23807E75-7BAE-452C-BD64-CFC70D1C37BE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6F249ABC-4043-4209-AC73-1522FDA81788}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" tabRatio="947" firstSheet="11" activeTab="22" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" tabRatio="947" firstSheet="11" activeTab="20" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="monthly_elctricity" sheetId="28" r:id="rId1"/>
@@ -47,7 +47,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="753" uniqueCount="261">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="759" uniqueCount="266">
   <si>
     <t>صفحة الإيرادات</t>
   </si>
@@ -830,6 +830,21 @@
   </si>
   <si>
     <t>تحت حساب مواصلات لشراء الاوتوماتيك نوع ماكسيكى هاى بريشر</t>
+  </si>
+  <si>
+    <t>ا/سامى</t>
+  </si>
+  <si>
+    <t xml:space="preserve">تحت حساب صيانة شهور يناير وفبراير ومارس / 2026 </t>
+  </si>
+  <si>
+    <t>البنك الاهلى</t>
+  </si>
+  <si>
+    <t>تحت حساب فوائد شهادة  رقم 1807951149146700023 بتاريخ اصدار 21- ديسمبر - 2025 بفائدة 14%، عن شهر يناير/ 2026</t>
+  </si>
+  <si>
+    <t>تحت حساب فوائد شهادة  رقم 1807951149146700023 بتاريخ اصدار 21- ديسمبر - 2025 بفائدة 14%، عن شهر فبراير / 2026</t>
   </si>
 </sst>
 </file>
@@ -7343,7 +7358,7 @@
       <c r="C4" s="76"/>
       <c r="D4" s="80">
         <f>SUM(D6:D2001)</f>
-        <v>0</v>
+        <v>900</v>
       </c>
       <c r="E4" s="11"/>
       <c r="F4" s="11">
@@ -7390,7 +7405,9 @@
       <c r="C6" s="77">
         <v>46335</v>
       </c>
-      <c r="D6" s="81"/>
+      <c r="D6" s="81">
+        <v>300</v>
+      </c>
       <c r="E6" s="8"/>
       <c r="F6" s="8">
         <v>300</v>
@@ -7413,7 +7430,9 @@
       <c r="C7" s="77">
         <v>46335</v>
       </c>
-      <c r="D7" s="81"/>
+      <c r="D7" s="81">
+        <v>300</v>
+      </c>
       <c r="E7" s="8"/>
       <c r="F7" s="8">
         <v>300</v>
@@ -7436,7 +7455,9 @@
       <c r="C8" s="77">
         <v>46335</v>
       </c>
-      <c r="D8" s="81"/>
+      <c r="D8" s="81">
+        <v>300</v>
+      </c>
       <c r="E8" s="8"/>
       <c r="F8" s="8">
         <v>300</v>
@@ -11318,7 +11339,7 @@
       </c>
       <c r="C4" s="53">
         <f>SUM(C6:C2000)</f>
-        <v>3425</v>
+        <v>4441</v>
       </c>
     </row>
     <row r="5" spans="1:17" ht="18" x14ac:dyDescent="0.2">
@@ -11850,12 +11871,22 @@
       <c r="A25" s="8">
         <v>20</v>
       </c>
-      <c r="B25" s="51"/>
-      <c r="C25" s="55"/>
+      <c r="B25" s="51">
+        <v>46085</v>
+      </c>
+      <c r="C25" s="55">
+        <v>900</v>
+      </c>
       <c r="D25" s="8"/>
-      <c r="E25" s="8"/>
-      <c r="F25" s="8"/>
-      <c r="G25" s="8"/>
+      <c r="E25" s="8" t="s">
+        <v>261</v>
+      </c>
+      <c r="F25" s="8">
+        <v>5</v>
+      </c>
+      <c r="G25" s="8" t="s">
+        <v>262</v>
+      </c>
       <c r="H25" s="2"/>
       <c r="I25" s="2"/>
       <c r="J25" s="2"/>
@@ -11867,12 +11898,20 @@
       <c r="A26" s="8">
         <v>21</v>
       </c>
-      <c r="B26" s="51"/>
-      <c r="C26" s="55"/>
+      <c r="B26" s="51">
+        <v>46044</v>
+      </c>
+      <c r="C26" s="55">
+        <v>58</v>
+      </c>
       <c r="D26" s="8"/>
-      <c r="E26" s="8"/>
+      <c r="E26" s="8" t="s">
+        <v>263</v>
+      </c>
       <c r="F26" s="8"/>
-      <c r="G26" s="8"/>
+      <c r="G26" s="8" t="s">
+        <v>264</v>
+      </c>
       <c r="H26" s="2"/>
       <c r="I26" s="2"/>
       <c r="J26" s="2"/>
@@ -11884,11 +11923,20 @@
       <c r="A27" s="8">
         <v>22</v>
       </c>
-      <c r="B27" s="51"/>
-      <c r="C27" s="55"/>
-      <c r="E27" s="8"/>
+      <c r="B27" s="51">
+        <v>46075</v>
+      </c>
+      <c r="C27" s="55">
+        <v>58</v>
+      </c>
+      <c r="D27" s="8"/>
+      <c r="E27" s="8" t="s">
+        <v>263</v>
+      </c>
       <c r="F27" s="8"/>
-      <c r="G27" s="8"/>
+      <c r="G27" s="8" t="s">
+        <v>265</v>
+      </c>
       <c r="H27" s="2"/>
       <c r="I27" s="2"/>
       <c r="J27" s="2"/>
@@ -12729,7 +12777,7 @@
       <c r="B5" s="9"/>
       <c r="C5" s="70">
         <f>incomes!C4</f>
-        <v>3425</v>
+        <v>4441</v>
       </c>
       <c r="D5" s="71">
         <f>outcomes!C3</f>
@@ -12737,7 +12785,7 @@
       </c>
       <c r="E5" s="72">
         <f>(C3+C5)-D5</f>
-        <v>10678</v>
+        <v>11694</v>
       </c>
       <c r="F5" s="2"/>
       <c r="G5" s="2"/>
@@ -19454,7 +19502,7 @@
       </c>
       <c r="G6" s="26">
         <f>Apartment5!D6</f>
-        <v>0</v>
+        <v>300</v>
       </c>
       <c r="H6" s="26">
         <f>Apartment6!D6</f>
@@ -19516,7 +19564,7 @@
       </c>
       <c r="G7" s="26">
         <f>Apartment5!D7</f>
-        <v>0</v>
+        <v>300</v>
       </c>
       <c r="H7" s="26">
         <f>Apartment6!D7</f>
@@ -19578,7 +19626,7 @@
       </c>
       <c r="G8" s="26">
         <f>Apartment5!D8</f>
-        <v>0</v>
+        <v>300</v>
       </c>
       <c r="H8" s="26">
         <f>Apartment6!D8</f>
@@ -20591,12 +20639,12 @@
       </c>
       <c r="C9" s="91">
         <f>Apartment5!D4</f>
-        <v>0</v>
+        <v>900</v>
       </c>
       <c r="D9" s="92"/>
       <c r="E9" s="94">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>-900</v>
       </c>
       <c r="F9" s="2" t="s">
         <v>119</v>

--- a/Book2026.xlsx
+++ b/Book2026.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\syana05012019\2024\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6F249ABC-4043-4209-AC73-1522FDA81788}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{341960FF-3EB5-40EF-8495-D7A403ACC05A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" tabRatio="947" firstSheet="11" activeTab="20" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" tabRatio="947" firstSheet="10" activeTab="11" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="monthly_elctricity" sheetId="28" r:id="rId1"/>
@@ -47,7 +47,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="759" uniqueCount="266">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="771" uniqueCount="268">
   <si>
     <t>صفحة الإيرادات</t>
   </si>
@@ -826,9 +826,6 @@
     <t>تحت حساب نظافة السلم لام احمد عن شهر فبراير /2026</t>
   </si>
   <si>
-    <t>تحت حساب شراء اوتوماتيك للموتور</t>
-  </si>
-  <si>
     <t>تحت حساب مواصلات لشراء الاوتوماتيك نوع ماكسيكى هاى بريشر</t>
   </si>
   <si>
@@ -845,6 +842,15 @@
   </si>
   <si>
     <t>تحت حساب فوائد شهادة  رقم 1807951149146700023 بتاريخ اصدار 21- ديسمبر - 2025 بفائدة 14%، عن شهر فبراير / 2026</t>
+  </si>
+  <si>
+    <t>تحت حساب كهرباء شهر مارس /2026</t>
+  </si>
+  <si>
+    <t>تحت حساب اصلاح الموتور - شراء بالونة ايطالى ب 1500 من الدقى - و 150 مصنعية</t>
+  </si>
+  <si>
+    <t>تحت حساب شراء اوتوماتيك للموتورب 900 جنيه ومصعية تركيب وضبط ب 100 جنيه</t>
   </si>
 </sst>
 </file>
@@ -3224,7 +3230,7 @@
       <c r="C4" s="10"/>
       <c r="D4" s="89">
         <f>SUM(D6:D2001)</f>
-        <v>0</v>
+        <v>450</v>
       </c>
       <c r="E4" s="11"/>
       <c r="F4" s="11">
@@ -3269,9 +3275,11 @@
         <v>1</v>
       </c>
       <c r="C6" s="9">
-        <v>46372</v>
-      </c>
-      <c r="D6" s="90"/>
+        <v>46092</v>
+      </c>
+      <c r="D6" s="90">
+        <v>150</v>
+      </c>
       <c r="E6" s="8"/>
       <c r="F6" s="8">
         <v>150</v>
@@ -3294,9 +3302,11 @@
         <v>2</v>
       </c>
       <c r="C7" s="9">
-        <v>46372</v>
-      </c>
-      <c r="D7" s="90"/>
+        <v>46092</v>
+      </c>
+      <c r="D7" s="90">
+        <v>150</v>
+      </c>
       <c r="E7" s="8"/>
       <c r="F7" s="8">
         <v>150</v>
@@ -3319,9 +3329,11 @@
         <v>3</v>
       </c>
       <c r="C8" s="9">
-        <v>46372</v>
-      </c>
-      <c r="D8" s="90"/>
+        <v>46092</v>
+      </c>
+      <c r="D8" s="90">
+        <v>150</v>
+      </c>
       <c r="E8" s="8"/>
       <c r="F8" s="8">
         <v>150</v>
@@ -4572,7 +4584,7 @@
       <c r="C4" s="49"/>
       <c r="D4" s="11">
         <f>SUM(D6:D2004)</f>
-        <v>0</v>
+        <v>450</v>
       </c>
       <c r="E4" s="11"/>
       <c r="F4" s="11">
@@ -4631,9 +4643,11 @@
         <v>1</v>
       </c>
       <c r="C6" s="51">
-        <v>46195</v>
-      </c>
-      <c r="D6" s="55"/>
+        <v>46092</v>
+      </c>
+      <c r="D6" s="55">
+        <v>150</v>
+      </c>
       <c r="E6" s="8"/>
       <c r="F6" s="8">
         <v>150</v>
@@ -4663,9 +4677,11 @@
         <v>2</v>
       </c>
       <c r="C7" s="51">
-        <v>46195</v>
-      </c>
-      <c r="D7" s="55"/>
+        <v>46092</v>
+      </c>
+      <c r="D7" s="55">
+        <v>150</v>
+      </c>
       <c r="E7" s="8"/>
       <c r="F7" s="8">
         <v>150</v>
@@ -4695,9 +4711,11 @@
         <v>3</v>
       </c>
       <c r="C8" s="51">
-        <v>46195</v>
-      </c>
-      <c r="D8" s="55"/>
+        <v>46092</v>
+      </c>
+      <c r="D8" s="55">
+        <v>150</v>
+      </c>
       <c r="E8" s="8"/>
       <c r="F8" s="8">
         <v>150</v>
@@ -6010,7 +6028,7 @@
       <c r="C4" s="49"/>
       <c r="D4" s="83">
         <f>SUM(D6:D2001)</f>
-        <v>900</v>
+        <v>1200</v>
       </c>
       <c r="E4" s="11"/>
       <c r="F4" s="83">
@@ -6138,7 +6156,9 @@
       <c r="C9" s="51">
         <v>45384</v>
       </c>
-      <c r="D9" s="33"/>
+      <c r="D9" s="33">
+        <v>300</v>
+      </c>
       <c r="E9" s="8"/>
       <c r="F9" s="33">
         <v>300</v>
@@ -8001,7 +8021,7 @@
       <c r="C4" s="10"/>
       <c r="D4" s="11">
         <f>SUM(D6:D2001)</f>
-        <v>450</v>
+        <v>600</v>
       </c>
       <c r="E4" s="11"/>
       <c r="F4" s="11">
@@ -8129,7 +8149,9 @@
       <c r="C9" s="63">
         <v>45384</v>
       </c>
-      <c r="D9" s="8"/>
+      <c r="D9" s="8">
+        <v>150</v>
+      </c>
       <c r="E9" s="8"/>
       <c r="F9" s="8">
         <v>150</v>
@@ -8666,7 +8688,7 @@
       <c r="C4" s="62"/>
       <c r="D4" s="11">
         <f>SUM(D6:D2001)</f>
-        <v>450</v>
+        <v>600</v>
       </c>
       <c r="E4" s="11"/>
       <c r="F4" s="11">
@@ -8794,7 +8816,9 @@
       <c r="C9" s="63">
         <v>45384</v>
       </c>
-      <c r="D9" s="8"/>
+      <c r="D9" s="8">
+        <v>150</v>
+      </c>
       <c r="E9" s="8"/>
       <c r="F9" s="8">
         <v>150</v>
@@ -11339,7 +11363,7 @@
       </c>
       <c r="C4" s="53">
         <f>SUM(C6:C2000)</f>
-        <v>4441</v>
+        <v>5941</v>
       </c>
     </row>
     <row r="5" spans="1:17" ht="18" x14ac:dyDescent="0.2">
@@ -11879,13 +11903,13 @@
       </c>
       <c r="D25" s="8"/>
       <c r="E25" s="8" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="F25" s="8">
         <v>5</v>
       </c>
       <c r="G25" s="8" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="H25" s="2"/>
       <c r="I25" s="2"/>
@@ -11906,11 +11930,11 @@
       </c>
       <c r="D26" s="8"/>
       <c r="E26" s="8" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="F26" s="8"/>
       <c r="G26" s="8" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="H26" s="2"/>
       <c r="I26" s="2"/>
@@ -11931,11 +11955,11 @@
       </c>
       <c r="D27" s="8"/>
       <c r="E27" s="8" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="F27" s="8"/>
       <c r="G27" s="8" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="H27" s="2"/>
       <c r="I27" s="2"/>
@@ -11948,12 +11972,21 @@
       <c r="A28" s="8">
         <v>23</v>
       </c>
-      <c r="B28" s="51"/>
-      <c r="C28" s="55"/>
-      <c r="D28" s="8"/>
-      <c r="E28" s="8"/>
-      <c r="F28" s="8"/>
-      <c r="G28" s="8"/>
+      <c r="B28" s="51">
+        <v>46092</v>
+      </c>
+      <c r="C28" s="55">
+        <v>300</v>
+      </c>
+      <c r="E28" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="F28" s="8">
+        <v>7</v>
+      </c>
+      <c r="G28" s="8" t="s">
+        <v>225</v>
+      </c>
       <c r="H28" s="2"/>
       <c r="I28" s="2"/>
       <c r="J28" s="2"/>
@@ -11965,12 +11998,22 @@
       <c r="A29" s="8">
         <v>24</v>
       </c>
-      <c r="B29" s="51"/>
-      <c r="C29" s="55"/>
+      <c r="B29" s="51">
+        <v>46092</v>
+      </c>
+      <c r="C29" s="55">
+        <v>150</v>
+      </c>
       <c r="D29" s="8"/>
-      <c r="E29" s="8"/>
-      <c r="F29" s="8"/>
-      <c r="G29" s="8"/>
+      <c r="E29" s="8" t="s">
+        <v>244</v>
+      </c>
+      <c r="F29" s="8">
+        <v>4</v>
+      </c>
+      <c r="G29" s="8" t="s">
+        <v>225</v>
+      </c>
       <c r="H29" s="2"/>
       <c r="I29" s="2"/>
       <c r="J29" s="2"/>
@@ -11982,12 +12025,22 @@
       <c r="A30" s="8">
         <v>25</v>
       </c>
-      <c r="B30" s="51"/>
-      <c r="C30" s="55"/>
+      <c r="B30" s="51">
+        <v>46092</v>
+      </c>
+      <c r="C30" s="55">
+        <v>150</v>
+      </c>
       <c r="D30" s="8"/>
-      <c r="E30" s="8"/>
-      <c r="F30" s="8"/>
-      <c r="G30" s="8"/>
+      <c r="E30" s="8" t="s">
+        <v>141</v>
+      </c>
+      <c r="F30" s="8">
+        <v>3</v>
+      </c>
+      <c r="G30" s="8" t="s">
+        <v>225</v>
+      </c>
       <c r="H30" s="2"/>
       <c r="I30" s="2"/>
       <c r="J30" s="2"/>
@@ -11999,11 +12052,21 @@
       <c r="A31" s="8">
         <v>26</v>
       </c>
-      <c r="B31" s="51"/>
-      <c r="C31" s="55"/>
-      <c r="E31" s="8"/>
-      <c r="F31" s="8"/>
-      <c r="G31" s="8"/>
+      <c r="B31" s="51">
+        <v>46092</v>
+      </c>
+      <c r="C31" s="55">
+        <v>450</v>
+      </c>
+      <c r="E31" s="8" t="s">
+        <v>187</v>
+      </c>
+      <c r="F31" s="8">
+        <v>11</v>
+      </c>
+      <c r="G31" s="8" t="s">
+        <v>261</v>
+      </c>
       <c r="H31" s="2"/>
       <c r="I31" s="2"/>
       <c r="J31" s="2"/>
@@ -12015,11 +12078,21 @@
       <c r="A32" s="8">
         <v>27</v>
       </c>
-      <c r="B32" s="51"/>
-      <c r="C32" s="55"/>
-      <c r="E32" s="8"/>
-      <c r="F32" s="8"/>
-      <c r="G32" s="8"/>
+      <c r="B32" s="51">
+        <v>46092</v>
+      </c>
+      <c r="C32" s="55">
+        <v>450</v>
+      </c>
+      <c r="E32" s="8" t="s">
+        <v>184</v>
+      </c>
+      <c r="F32" s="8">
+        <v>9</v>
+      </c>
+      <c r="G32" s="8" t="s">
+        <v>261</v>
+      </c>
       <c r="H32" s="2"/>
       <c r="I32" s="2"/>
       <c r="J32" s="2"/>
@@ -12777,15 +12850,15 @@
       <c r="B5" s="9"/>
       <c r="C5" s="70">
         <f>incomes!C4</f>
-        <v>4441</v>
+        <v>5941</v>
       </c>
       <c r="D5" s="71">
         <f>outcomes!C3</f>
-        <v>6649</v>
+        <v>9074</v>
       </c>
       <c r="E5" s="72">
         <f>(C3+C5)-D5</f>
-        <v>11694</v>
+        <v>10769</v>
       </c>
       <c r="F5" s="2"/>
       <c r="G5" s="2"/>
@@ -13172,7 +13245,7 @@
       </c>
       <c r="C3" s="53">
         <f>SUM(C5:C2002)</f>
-        <v>6649</v>
+        <v>9074</v>
       </c>
     </row>
     <row r="4" spans="1:19" ht="36" x14ac:dyDescent="0.2">
@@ -13469,10 +13542,10 @@
         <v>46057</v>
       </c>
       <c r="C18" s="55">
-        <v>900</v>
+        <v>1000</v>
       </c>
       <c r="D18" s="8" t="s">
-        <v>259</v>
+        <v>267</v>
       </c>
       <c r="E18" s="2"/>
       <c r="F18" s="2"/>
@@ -13495,7 +13568,7 @@
         <v>10</v>
       </c>
       <c r="D19" s="8" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="I19" s="2"/>
       <c r="J19" s="2"/>
@@ -13507,9 +13580,15 @@
       <c r="A20" s="33">
         <v>16</v>
       </c>
-      <c r="B20" s="60"/>
-      <c r="C20" s="55"/>
-      <c r="D20" s="8"/>
+      <c r="B20" s="60">
+        <v>46091</v>
+      </c>
+      <c r="C20" s="55">
+        <v>675</v>
+      </c>
+      <c r="D20" s="8" t="s">
+        <v>265</v>
+      </c>
       <c r="E20" s="2"/>
       <c r="F20" s="2"/>
       <c r="G20" s="2"/>
@@ -13524,9 +13603,15 @@
       <c r="A21" s="33">
         <v>17</v>
       </c>
-      <c r="B21" s="60"/>
-      <c r="C21" s="55"/>
-      <c r="D21" s="8"/>
+      <c r="B21" s="60">
+        <v>46092</v>
+      </c>
+      <c r="C21" s="55">
+        <v>1650</v>
+      </c>
+      <c r="D21" s="8" t="s">
+        <v>266</v>
+      </c>
       <c r="E21" s="2"/>
       <c r="F21" s="2"/>
       <c r="G21" s="2"/>
@@ -14337,7 +14422,7 @@
     <mergeCell ref="B2:N2"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="landscape" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>
+  <pageSetup paperSize="9" orientation="landscape" horizontalDpi="1200" verticalDpi="1200" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -19518,7 +19603,7 @@
       </c>
       <c r="K6" s="26">
         <f>Apartment9!D6</f>
-        <v>0</v>
+        <v>150</v>
       </c>
       <c r="L6" s="26">
         <f>Apartment10!D6</f>
@@ -19526,7 +19611,7 @@
       </c>
       <c r="M6" s="26">
         <f>Apartment11!D6</f>
-        <v>0</v>
+        <v>150</v>
       </c>
       <c r="N6" s="26">
         <f>Apartment12!D6</f>
@@ -19580,7 +19665,7 @@
       </c>
       <c r="K7" s="26">
         <f>Apartment9!D7</f>
-        <v>0</v>
+        <v>150</v>
       </c>
       <c r="L7" s="26">
         <f>Apartment10!D7</f>
@@ -19588,7 +19673,7 @@
       </c>
       <c r="M7" s="26">
         <f>Apartment11!D7</f>
-        <v>0</v>
+        <v>150</v>
       </c>
       <c r="N7" s="26">
         <f>Apartment12!D7</f>
@@ -19642,7 +19727,7 @@
       </c>
       <c r="K8" s="26">
         <f>Apartment9!D8</f>
-        <v>0</v>
+        <v>150</v>
       </c>
       <c r="L8" s="26">
         <f>Apartment10!D8</f>
@@ -19650,7 +19735,7 @@
       </c>
       <c r="M8" s="26">
         <f>Apartment11!D8</f>
-        <v>0</v>
+        <v>150</v>
       </c>
       <c r="N8" s="26">
         <f>Apartment12!D8</f>
@@ -19680,11 +19765,11 @@
       </c>
       <c r="E9" s="26">
         <f>Apartment3!D9</f>
-        <v>0</v>
+        <v>150</v>
       </c>
       <c r="F9" s="26">
         <f>Apartment4!D9</f>
-        <v>0</v>
+        <v>150</v>
       </c>
       <c r="G9" s="26">
         <f>Apartment5!D9</f>
@@ -19696,7 +19781,7 @@
       </c>
       <c r="I9" s="26">
         <f>Apartment7!D9</f>
-        <v>0</v>
+        <v>300</v>
       </c>
       <c r="J9" s="26">
         <f>Apartment8!D9</f>
@@ -20585,12 +20670,12 @@
       </c>
       <c r="C7" s="91">
         <f>Apartment3!D4</f>
-        <v>450</v>
+        <v>600</v>
       </c>
       <c r="D7" s="92"/>
       <c r="E7" s="94">
         <f t="shared" si="0"/>
-        <v>-450</v>
+        <v>-600</v>
       </c>
       <c r="F7" s="2" t="s">
         <v>48</v>
@@ -20612,12 +20697,12 @@
       </c>
       <c r="C8" s="91">
         <f>Apartment4!D4</f>
-        <v>450</v>
+        <v>600</v>
       </c>
       <c r="D8" s="92"/>
       <c r="E8" s="94">
         <f t="shared" si="0"/>
-        <v>-450</v>
+        <v>-600</v>
       </c>
       <c r="F8" s="2" t="s">
         <v>48</v>
@@ -20692,12 +20777,12 @@
       </c>
       <c r="C11" s="91">
         <f>Apartment7!D4</f>
-        <v>900</v>
+        <v>1200</v>
       </c>
       <c r="D11" s="92"/>
       <c r="E11" s="94">
         <f t="shared" si="0"/>
-        <v>-900</v>
+        <v>-1200</v>
       </c>
       <c r="F11" s="2" t="s">
         <v>48</v>
@@ -20746,12 +20831,12 @@
       </c>
       <c r="C13" s="91">
         <f>Apartment9!D4</f>
-        <v>0</v>
+        <v>450</v>
       </c>
       <c r="D13" s="92"/>
       <c r="E13" s="94">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>-450</v>
       </c>
       <c r="F13" s="2" t="s">
         <v>53</v>
@@ -20797,12 +20882,12 @@
       </c>
       <c r="C15" s="91">
         <f>Apartment11!D4</f>
-        <v>0</v>
+        <v>450</v>
       </c>
       <c r="D15" s="92"/>
       <c r="E15" s="94">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>-450</v>
       </c>
       <c r="F15" s="2" t="s">
         <v>54</v>

--- a/Book2026.xlsx
+++ b/Book2026.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\syana05012019\2024\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{341960FF-3EB5-40EF-8495-D7A403ACC05A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A066581B-4719-4557-A163-E77C1F9D7AB4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" tabRatio="947" firstSheet="10" activeTab="11" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" tabRatio="947" firstSheet="11" activeTab="12" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="monthly_elctricity" sheetId="28" r:id="rId1"/>
@@ -47,7 +47,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="771" uniqueCount="268">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="773" uniqueCount="268">
   <si>
     <t>صفحة الإيرادات</t>
   </si>
@@ -1424,21 +1424,6 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" readingOrder="2"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1456,6 +1441,21 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -4628,12 +4628,12 @@
       <c r="Q5" s="12" t="s">
         <v>37</v>
       </c>
-      <c r="R5" s="105" t="s">
+      <c r="R5" s="100" t="s">
         <v>77</v>
       </c>
-      <c r="S5" s="106"/>
-      <c r="T5" s="106"/>
-      <c r="U5" s="107"/>
+      <c r="S5" s="101"/>
+      <c r="T5" s="101"/>
+      <c r="U5" s="102"/>
     </row>
     <row r="6" spans="1:22" ht="18" x14ac:dyDescent="0.25">
       <c r="A6" s="8">
@@ -4864,10 +4864,10 @@
         <f>SUM(Q6:Q11)</f>
         <v>0</v>
       </c>
-      <c r="R12" s="108"/>
-      <c r="S12" s="109"/>
-      <c r="T12" s="109"/>
-      <c r="U12" s="110"/>
+      <c r="R12" s="103"/>
+      <c r="S12" s="104"/>
+      <c r="T12" s="104"/>
+      <c r="U12" s="105"/>
     </row>
     <row r="13" spans="1:22" ht="18" x14ac:dyDescent="0.25">
       <c r="A13" s="8">
@@ -5366,7 +5366,7 @@
       <c r="C4" s="76"/>
       <c r="D4" s="83">
         <f>SUM(D6:D2001)</f>
-        <v>600</v>
+        <v>900</v>
       </c>
       <c r="E4" s="11"/>
       <c r="F4" s="83">
@@ -5465,9 +5465,11 @@
         <v>3</v>
       </c>
       <c r="C8" s="77">
-        <v>46125</v>
-      </c>
-      <c r="D8" s="33"/>
+        <v>46093</v>
+      </c>
+      <c r="D8" s="33">
+        <v>300</v>
+      </c>
       <c r="E8" s="8"/>
       <c r="F8" s="33">
         <v>300</v>
@@ -9995,20 +9997,20 @@
     </row>
     <row r="3" spans="1:17" ht="20.25" x14ac:dyDescent="0.25">
       <c r="C3" s="83"/>
-      <c r="F3" s="100" t="s">
+      <c r="F3" s="106" t="s">
         <v>236</v>
       </c>
-      <c r="G3" s="100"/>
-      <c r="H3" s="100"/>
-      <c r="I3" s="100"/>
-      <c r="J3" s="100"/>
-      <c r="K3" s="100"/>
-      <c r="L3" s="100"/>
-      <c r="M3" s="100"/>
-      <c r="N3" s="100"/>
-      <c r="O3" s="100"/>
-      <c r="P3" s="100"/>
-      <c r="Q3" s="100"/>
+      <c r="G3" s="106"/>
+      <c r="H3" s="106"/>
+      <c r="I3" s="106"/>
+      <c r="J3" s="106"/>
+      <c r="K3" s="106"/>
+      <c r="L3" s="106"/>
+      <c r="M3" s="106"/>
+      <c r="N3" s="106"/>
+      <c r="O3" s="106"/>
+      <c r="P3" s="106"/>
+      <c r="Q3" s="106"/>
     </row>
     <row r="4" spans="1:17" ht="36" x14ac:dyDescent="0.2">
       <c r="A4" s="12" t="s">
@@ -11363,7 +11365,7 @@
       </c>
       <c r="C4" s="53">
         <f>SUM(C6:C2000)</f>
-        <v>5941</v>
+        <v>6241</v>
       </c>
     </row>
     <row r="5" spans="1:17" ht="18" x14ac:dyDescent="0.2">
@@ -12104,12 +12106,22 @@
       <c r="A33" s="8">
         <v>28</v>
       </c>
-      <c r="B33" s="51"/>
-      <c r="C33" s="55"/>
+      <c r="B33" s="51">
+        <v>46093</v>
+      </c>
+      <c r="C33" s="55">
+        <v>300</v>
+      </c>
       <c r="D33" s="8"/>
-      <c r="E33" s="8"/>
-      <c r="F33" s="8"/>
-      <c r="G33" s="8"/>
+      <c r="E33" s="8" t="s">
+        <v>249</v>
+      </c>
+      <c r="F33" s="8">
+        <v>8</v>
+      </c>
+      <c r="G33" s="8" t="s">
+        <v>224</v>
+      </c>
       <c r="H33" s="2"/>
       <c r="I33" s="2"/>
       <c r="J33" s="2"/>
@@ -12850,7 +12862,7 @@
       <c r="B5" s="9"/>
       <c r="C5" s="70">
         <f>incomes!C4</f>
-        <v>5941</v>
+        <v>6241</v>
       </c>
       <c r="D5" s="71">
         <f>outcomes!C3</f>
@@ -12858,7 +12870,7 @@
       </c>
       <c r="E5" s="72">
         <f>(C3+C5)-D5</f>
-        <v>10769</v>
+        <v>11069</v>
       </c>
       <c r="F5" s="2"/>
       <c r="G5" s="2"/>
@@ -14602,20 +14614,20 @@
     </row>
     <row r="3" spans="1:17" ht="20.25" x14ac:dyDescent="0.25">
       <c r="C3" s="83"/>
-      <c r="F3" s="100" t="s">
+      <c r="F3" s="106" t="s">
         <v>188</v>
       </c>
-      <c r="G3" s="100"/>
-      <c r="H3" s="100"/>
-      <c r="I3" s="100"/>
-      <c r="J3" s="100"/>
-      <c r="K3" s="100"/>
-      <c r="L3" s="100"/>
-      <c r="M3" s="100"/>
-      <c r="N3" s="100"/>
-      <c r="O3" s="100"/>
-      <c r="P3" s="100"/>
-      <c r="Q3" s="100"/>
+      <c r="G3" s="106"/>
+      <c r="H3" s="106"/>
+      <c r="I3" s="106"/>
+      <c r="J3" s="106"/>
+      <c r="K3" s="106"/>
+      <c r="L3" s="106"/>
+      <c r="M3" s="106"/>
+      <c r="N3" s="106"/>
+      <c r="O3" s="106"/>
+      <c r="P3" s="106"/>
+      <c r="Q3" s="106"/>
     </row>
     <row r="4" spans="1:17" ht="36" x14ac:dyDescent="0.2">
       <c r="A4" s="12" t="s">
@@ -19463,21 +19475,21 @@
   <sheetData>
     <row r="1" spans="1:20" ht="26.25" x14ac:dyDescent="0.4">
       <c r="B1" s="18"/>
-      <c r="C1" s="101" t="s">
+      <c r="C1" s="107" t="s">
         <v>140</v>
       </c>
-      <c r="D1" s="101"/>
-      <c r="E1" s="101"/>
-      <c r="F1" s="101"/>
-      <c r="G1" s="101"/>
-      <c r="H1" s="101"/>
-      <c r="I1" s="101"/>
-      <c r="J1" s="101"/>
-      <c r="K1" s="101"/>
-      <c r="L1" s="101"/>
-      <c r="M1" s="101"/>
-      <c r="N1" s="101"/>
-      <c r="O1" s="101"/>
+      <c r="D1" s="107"/>
+      <c r="E1" s="107"/>
+      <c r="F1" s="107"/>
+      <c r="G1" s="107"/>
+      <c r="H1" s="107"/>
+      <c r="I1" s="107"/>
+      <c r="J1" s="107"/>
+      <c r="K1" s="107"/>
+      <c r="L1" s="107"/>
+      <c r="M1" s="107"/>
+      <c r="N1" s="107"/>
+      <c r="O1" s="107"/>
     </row>
     <row r="2" spans="1:20" ht="26.25" x14ac:dyDescent="0.4">
       <c r="B2" s="18"/>
@@ -19723,7 +19735,7 @@
       </c>
       <c r="J8" s="26">
         <f>Apartment8!D8</f>
-        <v>0</v>
+        <v>300</v>
       </c>
       <c r="K8" s="26">
         <f>Apartment9!D8</f>
@@ -20571,11 +20583,11 @@
     </row>
     <row r="3" spans="1:14" ht="18" x14ac:dyDescent="0.25">
       <c r="C3" s="83"/>
-      <c r="G3" s="102" t="s">
+      <c r="G3" s="108" t="s">
         <v>94</v>
       </c>
-      <c r="H3" s="102"/>
-      <c r="I3" s="102"/>
+      <c r="H3" s="108"/>
+      <c r="I3" s="108"/>
     </row>
     <row r="4" spans="1:14" ht="36" x14ac:dyDescent="0.2">
       <c r="A4" s="12" t="s">
@@ -20804,12 +20816,12 @@
       </c>
       <c r="C12" s="91">
         <f>Apartment8!D4</f>
-        <v>600</v>
+        <v>900</v>
       </c>
       <c r="D12" s="92"/>
       <c r="E12" s="94">
         <f t="shared" si="0"/>
-        <v>-600</v>
+        <v>-900</v>
       </c>
       <c r="F12" s="2" t="s">
         <v>120</v>
@@ -22906,14 +22918,14 @@
       <c r="F20" s="8"/>
       <c r="G20" s="8"/>
       <c r="H20" s="2"/>
-      <c r="I20" s="103" t="s">
+      <c r="I20" s="109" t="s">
         <v>118</v>
       </c>
-      <c r="J20" s="103"/>
-      <c r="K20" s="103"/>
-      <c r="L20" s="103"/>
-      <c r="M20" s="103"/>
-      <c r="N20" s="103"/>
+      <c r="J20" s="109"/>
+      <c r="K20" s="109"/>
+      <c r="L20" s="109"/>
+      <c r="M20" s="109"/>
+      <c r="N20" s="109"/>
     </row>
     <row r="21" spans="1:17" ht="23.25" x14ac:dyDescent="0.35">
       <c r="A21" s="8"/>
@@ -22924,14 +22936,14 @@
       <c r="F21" s="8"/>
       <c r="G21" s="8"/>
       <c r="H21" s="2"/>
-      <c r="I21" s="103" t="s">
+      <c r="I21" s="109" t="s">
         <v>238</v>
       </c>
-      <c r="J21" s="103"/>
-      <c r="K21" s="103"/>
-      <c r="L21" s="103"/>
-      <c r="M21" s="103"/>
-      <c r="N21" s="103"/>
+      <c r="J21" s="109"/>
+      <c r="K21" s="109"/>
+      <c r="L21" s="109"/>
+      <c r="M21" s="109"/>
+      <c r="N21" s="109"/>
     </row>
     <row r="22" spans="1:17" ht="18" x14ac:dyDescent="0.25">
       <c r="A22" s="8"/>
@@ -22969,13 +22981,13 @@
       <c r="G23" s="48"/>
       <c r="H23" s="48"/>
       <c r="I23" s="48"/>
-      <c r="J23" s="104"/>
-      <c r="K23" s="104"/>
-      <c r="L23" s="104"/>
-      <c r="M23" s="104"/>
-      <c r="N23" s="104"/>
-      <c r="O23" s="104"/>
-      <c r="P23" s="104"/>
+      <c r="J23" s="110"/>
+      <c r="K23" s="110"/>
+      <c r="L23" s="110"/>
+      <c r="M23" s="110"/>
+      <c r="N23" s="110"/>
+      <c r="O23" s="110"/>
+      <c r="P23" s="110"/>
     </row>
     <row r="24" spans="1:17" ht="18" x14ac:dyDescent="0.25">
       <c r="A24" s="8"/>
@@ -22989,13 +23001,13 @@
       </c>
       <c r="H24" s="8"/>
       <c r="I24" s="8"/>
-      <c r="J24" s="104"/>
-      <c r="K24" s="104"/>
-      <c r="L24" s="104"/>
-      <c r="M24" s="104"/>
-      <c r="N24" s="104"/>
-      <c r="O24" s="104"/>
-      <c r="P24" s="104"/>
+      <c r="J24" s="110"/>
+      <c r="K24" s="110"/>
+      <c r="L24" s="110"/>
+      <c r="M24" s="110"/>
+      <c r="N24" s="110"/>
+      <c r="O24" s="110"/>
+      <c r="P24" s="110"/>
     </row>
     <row r="25" spans="1:17" ht="36" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="8"/>
@@ -23009,13 +23021,13 @@
       </c>
       <c r="H25" s="48"/>
       <c r="I25" s="48"/>
-      <c r="J25" s="104"/>
-      <c r="K25" s="104"/>
-      <c r="L25" s="104"/>
-      <c r="M25" s="104"/>
-      <c r="N25" s="104"/>
-      <c r="O25" s="104"/>
-      <c r="P25" s="104"/>
+      <c r="J25" s="110"/>
+      <c r="K25" s="110"/>
+      <c r="L25" s="110"/>
+      <c r="M25" s="110"/>
+      <c r="N25" s="110"/>
+      <c r="O25" s="110"/>
+      <c r="P25" s="110"/>
     </row>
     <row r="26" spans="1:17" ht="23.25" x14ac:dyDescent="0.35">
       <c r="A26" s="8"/>

--- a/Book2026.xlsx
+++ b/Book2026.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\syana05012019\2024\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A066581B-4719-4557-A163-E77C1F9D7AB4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{53538664-C9DC-4F6A-83F0-CA8523F5E0F5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" tabRatio="947" firstSheet="11" activeTab="12" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" tabRatio="947" firstSheet="11" activeTab="22" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="monthly_elctricity" sheetId="28" r:id="rId1"/>
@@ -47,7 +47,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="773" uniqueCount="268">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="774" uniqueCount="269">
   <si>
     <t>صفحة الإيرادات</t>
   </si>
@@ -851,6 +851,9 @@
   </si>
   <si>
     <t>تحت حساب شراء اوتوماتيك للموتورب 900 جنيه ومصعية تركيب وضبط ب 100 جنيه</t>
+  </si>
+  <si>
+    <t>تحت حساب فاتورة المياه عن شهر مارس /2025</t>
   </si>
 </sst>
 </file>
@@ -1424,6 +1427,21 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1441,21 +1459,6 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" readingOrder="2"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -4628,12 +4631,12 @@
       <c r="Q5" s="12" t="s">
         <v>37</v>
       </c>
-      <c r="R5" s="100" t="s">
+      <c r="R5" s="105" t="s">
         <v>77</v>
       </c>
-      <c r="S5" s="101"/>
-      <c r="T5" s="101"/>
-      <c r="U5" s="102"/>
+      <c r="S5" s="106"/>
+      <c r="T5" s="106"/>
+      <c r="U5" s="107"/>
     </row>
     <row r="6" spans="1:22" ht="18" x14ac:dyDescent="0.25">
       <c r="A6" s="8">
@@ -4864,10 +4867,10 @@
         <f>SUM(Q6:Q11)</f>
         <v>0</v>
       </c>
-      <c r="R12" s="103"/>
-      <c r="S12" s="104"/>
-      <c r="T12" s="104"/>
-      <c r="U12" s="105"/>
+      <c r="R12" s="108"/>
+      <c r="S12" s="109"/>
+      <c r="T12" s="109"/>
+      <c r="U12" s="110"/>
     </row>
     <row r="13" spans="1:22" ht="18" x14ac:dyDescent="0.25">
       <c r="A13" s="8">
@@ -9997,20 +10000,20 @@
     </row>
     <row r="3" spans="1:17" ht="20.25" x14ac:dyDescent="0.25">
       <c r="C3" s="83"/>
-      <c r="F3" s="106" t="s">
+      <c r="F3" s="100" t="s">
         <v>236</v>
       </c>
-      <c r="G3" s="106"/>
-      <c r="H3" s="106"/>
-      <c r="I3" s="106"/>
-      <c r="J3" s="106"/>
-      <c r="K3" s="106"/>
-      <c r="L3" s="106"/>
-      <c r="M3" s="106"/>
-      <c r="N3" s="106"/>
-      <c r="O3" s="106"/>
-      <c r="P3" s="106"/>
-      <c r="Q3" s="106"/>
+      <c r="G3" s="100"/>
+      <c r="H3" s="100"/>
+      <c r="I3" s="100"/>
+      <c r="J3" s="100"/>
+      <c r="K3" s="100"/>
+      <c r="L3" s="100"/>
+      <c r="M3" s="100"/>
+      <c r="N3" s="100"/>
+      <c r="O3" s="100"/>
+      <c r="P3" s="100"/>
+      <c r="Q3" s="100"/>
     </row>
     <row r="4" spans="1:17" ht="36" x14ac:dyDescent="0.2">
       <c r="A4" s="12" t="s">
@@ -12866,11 +12869,11 @@
       </c>
       <c r="D5" s="71">
         <f>outcomes!C3</f>
-        <v>9074</v>
+        <v>10104</v>
       </c>
       <c r="E5" s="72">
         <f>(C3+C5)-D5</f>
-        <v>11069</v>
+        <v>10039</v>
       </c>
       <c r="F5" s="2"/>
       <c r="G5" s="2"/>
@@ -13257,7 +13260,7 @@
       </c>
       <c r="C3" s="53">
         <f>SUM(C5:C2002)</f>
-        <v>9074</v>
+        <v>10104</v>
       </c>
     </row>
     <row r="4" spans="1:19" ht="36" x14ac:dyDescent="0.2">
@@ -13638,9 +13641,15 @@
       <c r="A22" s="33">
         <v>18</v>
       </c>
-      <c r="B22" s="60"/>
-      <c r="C22" s="55"/>
-      <c r="D22" s="8"/>
+      <c r="B22" s="60">
+        <v>46096</v>
+      </c>
+      <c r="C22" s="55">
+        <v>1030</v>
+      </c>
+      <c r="D22" s="8" t="s">
+        <v>268</v>
+      </c>
       <c r="E22" s="2"/>
       <c r="F22" s="2"/>
       <c r="G22" s="2"/>
@@ -14614,20 +14623,20 @@
     </row>
     <row r="3" spans="1:17" ht="20.25" x14ac:dyDescent="0.25">
       <c r="C3" s="83"/>
-      <c r="F3" s="106" t="s">
+      <c r="F3" s="100" t="s">
         <v>188</v>
       </c>
-      <c r="G3" s="106"/>
-      <c r="H3" s="106"/>
-      <c r="I3" s="106"/>
-      <c r="J3" s="106"/>
-      <c r="K3" s="106"/>
-      <c r="L3" s="106"/>
-      <c r="M3" s="106"/>
-      <c r="N3" s="106"/>
-      <c r="O3" s="106"/>
-      <c r="P3" s="106"/>
-      <c r="Q3" s="106"/>
+      <c r="G3" s="100"/>
+      <c r="H3" s="100"/>
+      <c r="I3" s="100"/>
+      <c r="J3" s="100"/>
+      <c r="K3" s="100"/>
+      <c r="L3" s="100"/>
+      <c r="M3" s="100"/>
+      <c r="N3" s="100"/>
+      <c r="O3" s="100"/>
+      <c r="P3" s="100"/>
+      <c r="Q3" s="100"/>
     </row>
     <row r="4" spans="1:17" ht="36" x14ac:dyDescent="0.2">
       <c r="A4" s="12" t="s">
@@ -19475,21 +19484,21 @@
   <sheetData>
     <row r="1" spans="1:20" ht="26.25" x14ac:dyDescent="0.4">
       <c r="B1" s="18"/>
-      <c r="C1" s="107" t="s">
+      <c r="C1" s="101" t="s">
         <v>140</v>
       </c>
-      <c r="D1" s="107"/>
-      <c r="E1" s="107"/>
-      <c r="F1" s="107"/>
-      <c r="G1" s="107"/>
-      <c r="H1" s="107"/>
-      <c r="I1" s="107"/>
-      <c r="J1" s="107"/>
-      <c r="K1" s="107"/>
-      <c r="L1" s="107"/>
-      <c r="M1" s="107"/>
-      <c r="N1" s="107"/>
-      <c r="O1" s="107"/>
+      <c r="D1" s="101"/>
+      <c r="E1" s="101"/>
+      <c r="F1" s="101"/>
+      <c r="G1" s="101"/>
+      <c r="H1" s="101"/>
+      <c r="I1" s="101"/>
+      <c r="J1" s="101"/>
+      <c r="K1" s="101"/>
+      <c r="L1" s="101"/>
+      <c r="M1" s="101"/>
+      <c r="N1" s="101"/>
+      <c r="O1" s="101"/>
     </row>
     <row r="2" spans="1:20" ht="26.25" x14ac:dyDescent="0.4">
       <c r="B2" s="18"/>
@@ -20583,11 +20592,11 @@
     </row>
     <row r="3" spans="1:14" ht="18" x14ac:dyDescent="0.25">
       <c r="C3" s="83"/>
-      <c r="G3" s="108" t="s">
+      <c r="G3" s="102" t="s">
         <v>94</v>
       </c>
-      <c r="H3" s="108"/>
-      <c r="I3" s="108"/>
+      <c r="H3" s="102"/>
+      <c r="I3" s="102"/>
     </row>
     <row r="4" spans="1:14" ht="36" x14ac:dyDescent="0.2">
       <c r="A4" s="12" t="s">
@@ -22918,14 +22927,14 @@
       <c r="F20" s="8"/>
       <c r="G20" s="8"/>
       <c r="H20" s="2"/>
-      <c r="I20" s="109" t="s">
+      <c r="I20" s="103" t="s">
         <v>118</v>
       </c>
-      <c r="J20" s="109"/>
-      <c r="K20" s="109"/>
-      <c r="L20" s="109"/>
-      <c r="M20" s="109"/>
-      <c r="N20" s="109"/>
+      <c r="J20" s="103"/>
+      <c r="K20" s="103"/>
+      <c r="L20" s="103"/>
+      <c r="M20" s="103"/>
+      <c r="N20" s="103"/>
     </row>
     <row r="21" spans="1:17" ht="23.25" x14ac:dyDescent="0.35">
       <c r="A21" s="8"/>
@@ -22936,14 +22945,14 @@
       <c r="F21" s="8"/>
       <c r="G21" s="8"/>
       <c r="H21" s="2"/>
-      <c r="I21" s="109" t="s">
+      <c r="I21" s="103" t="s">
         <v>238</v>
       </c>
-      <c r="J21" s="109"/>
-      <c r="K21" s="109"/>
-      <c r="L21" s="109"/>
-      <c r="M21" s="109"/>
-      <c r="N21" s="109"/>
+      <c r="J21" s="103"/>
+      <c r="K21" s="103"/>
+      <c r="L21" s="103"/>
+      <c r="M21" s="103"/>
+      <c r="N21" s="103"/>
     </row>
     <row r="22" spans="1:17" ht="18" x14ac:dyDescent="0.25">
       <c r="A22" s="8"/>
@@ -22981,13 +22990,13 @@
       <c r="G23" s="48"/>
       <c r="H23" s="48"/>
       <c r="I23" s="48"/>
-      <c r="J23" s="110"/>
-      <c r="K23" s="110"/>
-      <c r="L23" s="110"/>
-      <c r="M23" s="110"/>
-      <c r="N23" s="110"/>
-      <c r="O23" s="110"/>
-      <c r="P23" s="110"/>
+      <c r="J23" s="104"/>
+      <c r="K23" s="104"/>
+      <c r="L23" s="104"/>
+      <c r="M23" s="104"/>
+      <c r="N23" s="104"/>
+      <c r="O23" s="104"/>
+      <c r="P23" s="104"/>
     </row>
     <row r="24" spans="1:17" ht="18" x14ac:dyDescent="0.25">
       <c r="A24" s="8"/>
@@ -23001,13 +23010,13 @@
       </c>
       <c r="H24" s="8"/>
       <c r="I24" s="8"/>
-      <c r="J24" s="110"/>
-      <c r="K24" s="110"/>
-      <c r="L24" s="110"/>
-      <c r="M24" s="110"/>
-      <c r="N24" s="110"/>
-      <c r="O24" s="110"/>
-      <c r="P24" s="110"/>
+      <c r="J24" s="104"/>
+      <c r="K24" s="104"/>
+      <c r="L24" s="104"/>
+      <c r="M24" s="104"/>
+      <c r="N24" s="104"/>
+      <c r="O24" s="104"/>
+      <c r="P24" s="104"/>
     </row>
     <row r="25" spans="1:17" ht="36" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="8"/>
@@ -23021,13 +23030,13 @@
       </c>
       <c r="H25" s="48"/>
       <c r="I25" s="48"/>
-      <c r="J25" s="110"/>
-      <c r="K25" s="110"/>
-      <c r="L25" s="110"/>
-      <c r="M25" s="110"/>
-      <c r="N25" s="110"/>
-      <c r="O25" s="110"/>
-      <c r="P25" s="110"/>
+      <c r="J25" s="104"/>
+      <c r="K25" s="104"/>
+      <c r="L25" s="104"/>
+      <c r="M25" s="104"/>
+      <c r="N25" s="104"/>
+      <c r="O25" s="104"/>
+      <c r="P25" s="104"/>
     </row>
     <row r="26" spans="1:17" ht="23.25" x14ac:dyDescent="0.35">
       <c r="A26" s="8"/>

--- a/Book2026.xlsx
+++ b/Book2026.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\syana05012019\2024\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{53538664-C9DC-4F6A-83F0-CA8523F5E0F5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B36C8839-FF3B-44D8-BF72-ED34C986D9EC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" tabRatio="947" firstSheet="11" activeTab="22" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" tabRatio="947" firstSheet="6" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="monthly_elctricity" sheetId="28" r:id="rId1"/>
@@ -47,7 +47,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="774" uniqueCount="269">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="777" uniqueCount="271">
   <si>
     <t>صفحة الإيرادات</t>
   </si>
@@ -854,6 +854,12 @@
   </si>
   <si>
     <t>تحت حساب فاتورة المياه عن شهر مارس /2025</t>
+  </si>
+  <si>
+    <t>منال</t>
+  </si>
+  <si>
+    <t>13، 14</t>
   </si>
 </sst>
 </file>
@@ -11368,7 +11374,7 @@
       </c>
       <c r="C4" s="53">
         <f>SUM(C6:C2000)</f>
-        <v>6241</v>
+        <v>6991</v>
       </c>
     </row>
     <row r="5" spans="1:17" ht="18" x14ac:dyDescent="0.2">
@@ -12136,12 +12142,22 @@
       <c r="A34" s="8">
         <v>29</v>
       </c>
-      <c r="B34" s="51"/>
-      <c r="C34" s="55"/>
+      <c r="B34" s="51">
+        <v>46097</v>
+      </c>
+      <c r="C34" s="55">
+        <v>750</v>
+      </c>
       <c r="D34" s="8"/>
-      <c r="E34" s="8"/>
-      <c r="F34" s="8"/>
-      <c r="G34" s="8"/>
+      <c r="E34" s="8" t="s">
+        <v>269</v>
+      </c>
+      <c r="F34" s="8" t="s">
+        <v>270</v>
+      </c>
+      <c r="G34" s="8" t="s">
+        <v>261</v>
+      </c>
       <c r="H34" s="2"/>
       <c r="I34" s="2"/>
       <c r="J34" s="2"/>
@@ -12865,7 +12881,7 @@
       <c r="B5" s="9"/>
       <c r="C5" s="70">
         <f>incomes!C4</f>
-        <v>6241</v>
+        <v>6991</v>
       </c>
       <c r="D5" s="71">
         <f>outcomes!C3</f>
@@ -12873,7 +12889,7 @@
       </c>
       <c r="E5" s="72">
         <f>(C3+C5)-D5</f>
-        <v>10039</v>
+        <v>10789</v>
       </c>
       <c r="F5" s="2"/>
       <c r="G5" s="2"/>
@@ -19640,11 +19656,11 @@
       </c>
       <c r="O6" s="26">
         <f>Apartment13!D6</f>
-        <v>0</v>
+        <v>125</v>
       </c>
       <c r="P6" s="26">
         <f>Apartment14!D6</f>
-        <v>0</v>
+        <v>125</v>
       </c>
     </row>
     <row r="7" spans="1:20" ht="23.25" x14ac:dyDescent="0.35">
@@ -19702,11 +19718,11 @@
       </c>
       <c r="O7" s="26">
         <f>Apartment13!D7</f>
-        <v>0</v>
+        <v>125</v>
       </c>
       <c r="P7" s="26">
         <f>Apartment14!D7</f>
-        <v>0</v>
+        <v>125</v>
       </c>
     </row>
     <row r="8" spans="1:20" ht="23.25" x14ac:dyDescent="0.35">
@@ -19764,11 +19780,11 @@
       </c>
       <c r="O8" s="26">
         <f>Apartment13!D8</f>
-        <v>0</v>
+        <v>125</v>
       </c>
       <c r="P8" s="26">
         <f>Apartment14!D8</f>
-        <v>0</v>
+        <v>125</v>
       </c>
     </row>
     <row r="9" spans="1:20" ht="23.25" x14ac:dyDescent="0.35">
@@ -20956,12 +20972,12 @@
       </c>
       <c r="C17" s="91">
         <f>Apartment13!D4</f>
-        <v>0</v>
+        <v>375</v>
       </c>
       <c r="D17" s="92"/>
       <c r="E17" s="94">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>-375</v>
       </c>
       <c r="F17" s="2" t="s">
         <v>56</v>
@@ -20983,12 +20999,12 @@
       </c>
       <c r="C18" s="91">
         <f>Apartment14!D4</f>
-        <v>0</v>
+        <v>375</v>
       </c>
       <c r="D18" s="92"/>
       <c r="E18" s="94">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>-375</v>
       </c>
       <c r="F18" s="2" t="s">
         <v>57</v>
@@ -21249,12 +21265,12 @@
       <c r="C4" s="62"/>
       <c r="D4" s="11">
         <f>SUM(D6:D2001)</f>
-        <v>0</v>
+        <v>375</v>
       </c>
       <c r="E4" s="11"/>
       <c r="F4" s="11">
         <f>SUM(F6:F2001)</f>
-        <v>1500</v>
+        <v>1725</v>
       </c>
     </row>
     <row r="5" spans="1:17" ht="36" x14ac:dyDescent="0.2">
@@ -21296,7 +21312,9 @@
       <c r="C6" s="63">
         <v>46134</v>
       </c>
-      <c r="D6" s="33"/>
+      <c r="D6" s="33">
+        <v>125</v>
+      </c>
       <c r="E6" s="8"/>
       <c r="F6" s="8">
         <v>125</v>
@@ -21321,7 +21339,9 @@
       <c r="C7" s="63">
         <v>46134</v>
       </c>
-      <c r="D7" s="33"/>
+      <c r="D7" s="33">
+        <v>125</v>
+      </c>
       <c r="E7" s="8"/>
       <c r="F7" s="8">
         <v>125</v>
@@ -21346,7 +21366,9 @@
       <c r="C8" s="63">
         <v>46242</v>
       </c>
-      <c r="D8" s="33"/>
+      <c r="D8" s="33">
+        <v>125</v>
+      </c>
       <c r="E8" s="8"/>
       <c r="F8" s="8">
         <v>125</v>
@@ -21374,7 +21396,7 @@
       <c r="D9" s="33"/>
       <c r="E9" s="8"/>
       <c r="F9" s="8">
-        <v>125</v>
+        <v>150</v>
       </c>
       <c r="G9" s="8" t="s">
         <v>101</v>
@@ -21399,7 +21421,7 @@
       <c r="D10" s="33"/>
       <c r="E10" s="8"/>
       <c r="F10" s="8">
-        <v>125</v>
+        <v>150</v>
       </c>
       <c r="G10" s="8" t="s">
         <v>102</v>
@@ -21424,7 +21446,7 @@
       <c r="D11" s="33"/>
       <c r="E11" s="8"/>
       <c r="F11" s="8">
-        <v>125</v>
+        <v>150</v>
       </c>
       <c r="G11" s="8" t="s">
         <v>103</v>
@@ -21449,7 +21471,7 @@
       <c r="D12" s="33"/>
       <c r="E12" s="8"/>
       <c r="F12" s="8">
-        <v>125</v>
+        <v>150</v>
       </c>
       <c r="G12" s="8" t="s">
         <v>104</v>
@@ -21474,7 +21496,7 @@
       <c r="D13" s="33"/>
       <c r="E13" s="8"/>
       <c r="F13" s="8">
-        <v>125</v>
+        <v>150</v>
       </c>
       <c r="G13" s="8" t="s">
         <v>105</v>
@@ -21499,7 +21521,7 @@
       <c r="D14" s="33"/>
       <c r="E14" s="8"/>
       <c r="F14" s="8">
-        <v>125</v>
+        <v>150</v>
       </c>
       <c r="G14" s="8" t="s">
         <v>106</v>
@@ -21524,7 +21546,7 @@
       <c r="D15" s="33"/>
       <c r="E15" s="8"/>
       <c r="F15" s="8">
-        <v>125</v>
+        <v>150</v>
       </c>
       <c r="G15" s="8" t="s">
         <v>107</v>
@@ -21549,7 +21571,7 @@
       <c r="D16" s="33"/>
       <c r="E16" s="8"/>
       <c r="F16" s="8">
-        <v>125</v>
+        <v>150</v>
       </c>
       <c r="G16" s="8" t="s">
         <v>108</v>
@@ -21574,7 +21596,7 @@
       <c r="D17" s="33"/>
       <c r="E17" s="8"/>
       <c r="F17" s="8">
-        <v>125</v>
+        <v>150</v>
       </c>
       <c r="G17" s="8" t="s">
         <v>153</v>
@@ -22551,12 +22573,12 @@
       <c r="C4" s="49"/>
       <c r="D4" s="83">
         <f>SUM(D6:D2001)</f>
-        <v>0</v>
+        <v>375</v>
       </c>
       <c r="E4" s="11"/>
       <c r="F4" s="11">
         <f>SUM(F6:F2001)</f>
-        <v>1500</v>
+        <v>1725</v>
       </c>
     </row>
     <row r="5" spans="1:17" ht="36" x14ac:dyDescent="0.2">
@@ -22598,7 +22620,9 @@
       <c r="C6" s="51">
         <v>46134</v>
       </c>
-      <c r="D6" s="33"/>
+      <c r="D6" s="33">
+        <v>125</v>
+      </c>
       <c r="E6" s="8"/>
       <c r="F6" s="8">
         <v>125</v>
@@ -22623,7 +22647,9 @@
       <c r="C7" s="51">
         <v>46134</v>
       </c>
-      <c r="D7" s="33"/>
+      <c r="D7" s="33">
+        <v>125</v>
+      </c>
       <c r="E7" s="8"/>
       <c r="F7" s="8">
         <v>125</v>
@@ -22648,7 +22674,9 @@
       <c r="C8" s="51">
         <v>46242</v>
       </c>
-      <c r="D8" s="33"/>
+      <c r="D8" s="33">
+        <v>125</v>
+      </c>
       <c r="E8" s="8"/>
       <c r="F8" s="8">
         <v>125</v>
@@ -22676,7 +22704,7 @@
       <c r="D9" s="33"/>
       <c r="E9" s="8"/>
       <c r="F9" s="8">
-        <v>125</v>
+        <v>150</v>
       </c>
       <c r="G9" s="8" t="s">
         <v>101</v>
@@ -22701,7 +22729,7 @@
       <c r="D10" s="33"/>
       <c r="E10" s="8"/>
       <c r="F10" s="8">
-        <v>125</v>
+        <v>150</v>
       </c>
       <c r="G10" s="8" t="s">
         <v>102</v>
@@ -22726,7 +22754,7 @@
       <c r="D11" s="33"/>
       <c r="E11" s="8"/>
       <c r="F11" s="8">
-        <v>125</v>
+        <v>150</v>
       </c>
       <c r="G11" s="8" t="s">
         <v>103</v>
@@ -22751,7 +22779,7 @@
       <c r="D12" s="33"/>
       <c r="E12" s="8"/>
       <c r="F12" s="8">
-        <v>125</v>
+        <v>150</v>
       </c>
       <c r="G12" s="8" t="s">
         <v>104</v>
@@ -22776,7 +22804,7 @@
       <c r="D13" s="33"/>
       <c r="E13" s="8"/>
       <c r="F13" s="8">
-        <v>125</v>
+        <v>150</v>
       </c>
       <c r="G13" s="8" t="s">
         <v>105</v>
@@ -22801,7 +22829,7 @@
       <c r="D14" s="33"/>
       <c r="E14" s="8"/>
       <c r="F14" s="8">
-        <v>125</v>
+        <v>150</v>
       </c>
       <c r="G14" s="8" t="s">
         <v>106</v>
@@ -22826,7 +22854,7 @@
       <c r="D15" s="33"/>
       <c r="E15" s="8"/>
       <c r="F15" s="8">
-        <v>125</v>
+        <v>150</v>
       </c>
       <c r="G15" s="8" t="s">
         <v>107</v>
@@ -22851,7 +22879,7 @@
       <c r="D16" s="33"/>
       <c r="E16" s="8"/>
       <c r="F16" s="8">
-        <v>125</v>
+        <v>150</v>
       </c>
       <c r="G16" s="8" t="s">
         <v>108</v>
@@ -22876,7 +22904,7 @@
       <c r="D17" s="33"/>
       <c r="E17" s="8"/>
       <c r="F17" s="8">
-        <v>125</v>
+        <v>150</v>
       </c>
       <c r="G17" s="8" t="s">
         <v>109</v>

--- a/Book2026.xlsx
+++ b/Book2026.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\syana05012019\2024\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B36C8839-FF3B-44D8-BF72-ED34C986D9EC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{49D30609-CBCC-419A-83E7-EB099791587D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" tabRatio="947" firstSheet="6" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" tabRatio="947" firstSheet="11" activeTab="22" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="monthly_elctricity" sheetId="28" r:id="rId1"/>
@@ -47,7 +47,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="777" uniqueCount="271">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="782" uniqueCount="272">
   <si>
     <t>صفحة الإيرادات</t>
   </si>
@@ -860,6 +860,9 @@
   </si>
   <si>
     <t>13، 14</t>
+  </si>
+  <si>
+    <t>تحت حساب نظافة السلم لام احمد عن شهر مارس /2026</t>
   </si>
 </sst>
 </file>
@@ -9366,7 +9369,7 @@
       <c r="C4" s="76"/>
       <c r="D4" s="11">
         <f>SUM(D6:D2001)</f>
-        <v>225</v>
+        <v>300</v>
       </c>
       <c r="E4" s="11"/>
       <c r="F4" s="83">
@@ -9492,9 +9495,11 @@
         <v>4</v>
       </c>
       <c r="C9" s="77">
-        <v>46122</v>
-      </c>
-      <c r="D9" s="8"/>
+        <v>46116</v>
+      </c>
+      <c r="D9" s="8">
+        <v>75</v>
+      </c>
       <c r="E9" s="8"/>
       <c r="F9" s="33">
         <v>75</v>
@@ -10672,7 +10677,7 @@
       <c r="C4" s="10"/>
       <c r="D4" s="11">
         <f>SUM(D6:D2001)</f>
-        <v>300</v>
+        <v>450</v>
       </c>
       <c r="E4" s="11"/>
       <c r="F4" s="11">
@@ -10774,9 +10779,11 @@
         <v>3</v>
       </c>
       <c r="C8" s="51">
-        <v>46087</v>
-      </c>
-      <c r="D8" s="73"/>
+        <v>46115</v>
+      </c>
+      <c r="D8" s="73">
+        <v>150</v>
+      </c>
       <c r="E8" s="8"/>
       <c r="F8" s="73">
         <v>150</v>
@@ -11374,7 +11381,7 @@
       </c>
       <c r="C4" s="53">
         <f>SUM(C6:C2000)</f>
-        <v>6991</v>
+        <v>7216</v>
       </c>
     </row>
     <row r="5" spans="1:17" ht="18" x14ac:dyDescent="0.2">
@@ -12169,23 +12176,42 @@
       <c r="A35" s="8">
         <v>30</v>
       </c>
-      <c r="B35" s="51"/>
-      <c r="C35" s="55"/>
-      <c r="D35" s="8"/>
-      <c r="E35" s="8"/>
-      <c r="F35" s="8"/>
-      <c r="G35" s="8"/>
+      <c r="B35" s="51">
+        <v>46116</v>
+      </c>
+      <c r="C35" s="55">
+        <v>75</v>
+      </c>
+      <c r="E35" s="8" t="s">
+        <v>160</v>
+      </c>
+      <c r="F35" s="8">
+        <v>2</v>
+      </c>
+      <c r="G35" s="8" t="s">
+        <v>225</v>
+      </c>
     </row>
     <row r="36" spans="1:13" ht="18" x14ac:dyDescent="0.25">
       <c r="A36" s="8">
         <v>31</v>
       </c>
-      <c r="B36" s="51"/>
-      <c r="C36" s="55"/>
+      <c r="B36" s="51">
+        <v>46115</v>
+      </c>
+      <c r="C36" s="55">
+        <v>150</v>
+      </c>
       <c r="D36" s="8"/>
-      <c r="E36" s="8"/>
-      <c r="F36" s="8"/>
-      <c r="G36" s="8"/>
+      <c r="E36" s="8" t="s">
+        <v>186</v>
+      </c>
+      <c r="F36" s="8">
+        <v>1</v>
+      </c>
+      <c r="G36" s="8" t="s">
+        <v>224</v>
+      </c>
     </row>
     <row r="37" spans="1:13" ht="18" x14ac:dyDescent="0.25">
       <c r="A37" s="8">
@@ -12881,15 +12907,15 @@
       <c r="B5" s="9"/>
       <c r="C5" s="70">
         <f>incomes!C4</f>
-        <v>6991</v>
+        <v>7216</v>
       </c>
       <c r="D5" s="71">
         <f>outcomes!C3</f>
-        <v>10104</v>
+        <v>10504</v>
       </c>
       <c r="E5" s="72">
         <f>(C3+C5)-D5</f>
-        <v>10789</v>
+        <v>10614</v>
       </c>
       <c r="F5" s="2"/>
       <c r="G5" s="2"/>
@@ -13276,7 +13302,7 @@
       </c>
       <c r="C3" s="53">
         <f>SUM(C5:C2002)</f>
-        <v>10104</v>
+        <v>10504</v>
       </c>
     </row>
     <row r="4" spans="1:19" ht="36" x14ac:dyDescent="0.2">
@@ -13680,9 +13706,15 @@
       <c r="A23" s="33">
         <v>19</v>
       </c>
-      <c r="B23" s="60"/>
-      <c r="C23" s="55"/>
-      <c r="D23" s="8"/>
+      <c r="B23" s="60">
+        <v>46109</v>
+      </c>
+      <c r="C23" s="55">
+        <v>400</v>
+      </c>
+      <c r="D23" s="8" t="s">
+        <v>271</v>
+      </c>
       <c r="E23" s="2"/>
       <c r="F23" s="2"/>
       <c r="G23" s="2"/>
@@ -19732,7 +19764,7 @@
       </c>
       <c r="C8" s="26">
         <f>Apartment1!D8</f>
-        <v>0</v>
+        <v>150</v>
       </c>
       <c r="D8" s="26">
         <f>Apartment2!D8</f>
@@ -19798,7 +19830,7 @@
       </c>
       <c r="D9" s="26">
         <f>Apartment2!D9</f>
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="E9" s="26">
         <f>Apartment3!D9</f>
@@ -20653,12 +20685,12 @@
       </c>
       <c r="C5" s="91">
         <f>Apartment1!D4</f>
-        <v>300</v>
+        <v>450</v>
       </c>
       <c r="D5" s="92"/>
       <c r="E5" s="94">
         <f>D5-C5</f>
-        <v>-300</v>
+        <v>-450</v>
       </c>
       <c r="F5" s="2" t="s">
         <v>50</v>
@@ -20680,12 +20712,12 @@
       </c>
       <c r="C6" s="91">
         <f>Apartment2!D4</f>
-        <v>225</v>
+        <v>300</v>
       </c>
       <c r="D6" s="92"/>
       <c r="E6" s="94">
         <f t="shared" ref="E6:E18" si="0">D6-C6</f>
-        <v>-225</v>
+        <v>-300</v>
       </c>
       <c r="F6" s="2" t="s">
         <v>51</v>

--- a/Book2026.xlsx
+++ b/Book2026.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\syana05012019\2024\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{49D30609-CBCC-419A-83E7-EB099791587D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7EC80849-17F2-43D7-A201-68C76CB24A80}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" tabRatio="947" firstSheet="11" activeTab="22" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" tabRatio="947" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="monthly_elctricity" sheetId="28" r:id="rId1"/>
@@ -47,7 +47,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="782" uniqueCount="272">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="788" uniqueCount="274">
   <si>
     <t>صفحة الإيرادات</t>
   </si>
@@ -863,6 +863,12 @@
   </si>
   <si>
     <t>تحت حساب نظافة السلم لام احمد عن شهر مارس /2026</t>
+  </si>
+  <si>
+    <t>تحت حساب فوائد شهادة  رقم 1807581149146700038 بتاريخ اصدار 4- يناير - 2026 بفائدة 19.25%، عن شهر ابريل / 2026</t>
+  </si>
+  <si>
+    <t>تحت حساب فوائد شهادة  رقم 1807951149146700023 بتاريخ اصدار 21- ديسمبر - 2025 بفائدة 14%، عن شهر مارس / 2026</t>
   </si>
 </sst>
 </file>
@@ -11381,7 +11387,7 @@
       </c>
       <c r="C4" s="53">
         <f>SUM(C6:C2000)</f>
-        <v>7216</v>
+        <v>7770</v>
       </c>
     </row>
     <row r="5" spans="1:17" ht="18" x14ac:dyDescent="0.2">
@@ -12217,33 +12223,58 @@
       <c r="A37" s="8">
         <v>32</v>
       </c>
-      <c r="B37" s="51"/>
-      <c r="C37" s="55"/>
+      <c r="B37" s="51">
+        <v>46103</v>
+      </c>
+      <c r="C37" s="55">
+        <v>58</v>
+      </c>
       <c r="D37" s="8"/>
-      <c r="E37" s="8"/>
+      <c r="E37" s="8" t="s">
+        <v>262</v>
+      </c>
       <c r="F37" s="8"/>
-      <c r="G37" s="8"/>
+      <c r="G37" s="8" t="s">
+        <v>273</v>
+      </c>
     </row>
     <row r="38" spans="1:13" ht="18" x14ac:dyDescent="0.25">
       <c r="A38" s="8">
         <v>33</v>
       </c>
-      <c r="B38" s="51"/>
-      <c r="C38" s="55"/>
-      <c r="E38" s="8"/>
+      <c r="B38" s="51">
+        <v>46117</v>
+      </c>
+      <c r="C38" s="55">
+        <v>246</v>
+      </c>
+      <c r="E38" s="8" t="s">
+        <v>262</v>
+      </c>
       <c r="F38" s="8"/>
-      <c r="G38" s="8"/>
+      <c r="G38" s="8" t="s">
+        <v>272</v>
+      </c>
     </row>
     <row r="39" spans="1:13" ht="18" x14ac:dyDescent="0.25">
       <c r="A39" s="8">
         <v>34</v>
       </c>
-      <c r="B39" s="51"/>
-      <c r="C39" s="55"/>
-      <c r="D39" s="8"/>
-      <c r="E39" s="8"/>
-      <c r="F39" s="8"/>
-      <c r="G39" s="8"/>
+      <c r="B39" s="51">
+        <v>46115</v>
+      </c>
+      <c r="C39" s="55">
+        <v>250</v>
+      </c>
+      <c r="E39" s="8" t="s">
+        <v>142</v>
+      </c>
+      <c r="F39" s="8">
+        <v>12</v>
+      </c>
+      <c r="G39" s="8" t="s">
+        <v>224</v>
+      </c>
     </row>
     <row r="40" spans="1:13" ht="18" x14ac:dyDescent="0.25">
       <c r="A40" s="8">
@@ -12907,7 +12938,7 @@
       <c r="B5" s="9"/>
       <c r="C5" s="70">
         <f>incomes!C4</f>
-        <v>7216</v>
+        <v>7770</v>
       </c>
       <c r="D5" s="71">
         <f>outcomes!C3</f>
@@ -12915,7 +12946,7 @@
       </c>
       <c r="E5" s="72">
         <f>(C3+C5)-D5</f>
-        <v>10614</v>
+        <v>11168</v>
       </c>
       <c r="F5" s="2"/>
       <c r="G5" s="2"/>
@@ -19808,7 +19839,7 @@
       </c>
       <c r="N8" s="26">
         <f>Apartment12!D8</f>
-        <v>0</v>
+        <v>250</v>
       </c>
       <c r="O8" s="26">
         <f>Apartment13!D8</f>
@@ -21962,7 +21993,7 @@
       <c r="C4" s="76"/>
       <c r="D4" s="83">
         <f>SUM(D6:D2001)</f>
-        <v>500</v>
+        <v>750</v>
       </c>
       <c r="E4" s="11"/>
       <c r="F4" s="83">
@@ -22060,8 +22091,12 @@
       <c r="B8" s="73">
         <v>3</v>
       </c>
-      <c r="C8" s="77"/>
-      <c r="D8" s="33"/>
+      <c r="C8" s="77">
+        <v>46115</v>
+      </c>
+      <c r="D8" s="33">
+        <v>250</v>
+      </c>
       <c r="E8" s="8"/>
       <c r="F8" s="33">
         <v>250</v>

--- a/Book2026.xlsx
+++ b/Book2026.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\syana05012019\2024\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7EC80849-17F2-43D7-A201-68C76CB24A80}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C0DABFA8-CE3B-4AE3-9142-A8049C0E51E2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" tabRatio="947" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" tabRatio="947" firstSheet="13" activeTab="22" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="monthly_elctricity" sheetId="28" r:id="rId1"/>
@@ -47,7 +47,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="788" uniqueCount="274">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="789" uniqueCount="275">
   <si>
     <t>صفحة الإيرادات</t>
   </si>
@@ -808,12 +808,6 @@
     <t>تحت حساب تسليك المجارى لعامل المجارى</t>
   </si>
   <si>
-    <t>تحت حساب فاتورة المياه عن شهر يناير /2025</t>
-  </si>
-  <si>
-    <t>تحت حساب فاتورة المياه عن شهر فبراير /2025</t>
-  </si>
-  <si>
     <t>تحت حساب كهرباء شهر فبراير /2026</t>
   </si>
   <si>
@@ -853,9 +847,6 @@
     <t>تحت حساب شراء اوتوماتيك للموتورب 900 جنيه ومصعية تركيب وضبط ب 100 جنيه</t>
   </si>
   <si>
-    <t>تحت حساب فاتورة المياه عن شهر مارس /2025</t>
-  </si>
-  <si>
     <t>منال</t>
   </si>
   <si>
@@ -869,6 +860,18 @@
   </si>
   <si>
     <t>تحت حساب فوائد شهادة  رقم 1807951149146700023 بتاريخ اصدار 21- ديسمبر - 2025 بفائدة 14%، عن شهر مارس / 2026</t>
+  </si>
+  <si>
+    <t>تحت حساب فاتورة المياه عن شهر ابريل /2026</t>
+  </si>
+  <si>
+    <t>تحت حساب فاتورة المياه عن شهر مارس /2026</t>
+  </si>
+  <si>
+    <t>تحت حساب فاتورة المياه عن شهر يناير /2026</t>
+  </si>
+  <si>
+    <t>تحت حساب فاتورة المياه عن شهر فبراير /2026</t>
   </si>
 </sst>
 </file>
@@ -11927,13 +11930,13 @@
       </c>
       <c r="D25" s="8"/>
       <c r="E25" s="8" t="s">
-        <v>260</v>
+        <v>258</v>
       </c>
       <c r="F25" s="8">
         <v>5</v>
       </c>
       <c r="G25" s="8" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="H25" s="2"/>
       <c r="I25" s="2"/>
@@ -11954,11 +11957,11 @@
       </c>
       <c r="D26" s="8"/>
       <c r="E26" s="8" t="s">
-        <v>262</v>
+        <v>260</v>
       </c>
       <c r="F26" s="8"/>
       <c r="G26" s="8" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="H26" s="2"/>
       <c r="I26" s="2"/>
@@ -11979,11 +11982,11 @@
       </c>
       <c r="D27" s="8"/>
       <c r="E27" s="8" t="s">
-        <v>262</v>
+        <v>260</v>
       </c>
       <c r="F27" s="8"/>
       <c r="G27" s="8" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="H27" s="2"/>
       <c r="I27" s="2"/>
@@ -12089,7 +12092,7 @@
         <v>11</v>
       </c>
       <c r="G31" s="8" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="H31" s="2"/>
       <c r="I31" s="2"/>
@@ -12115,7 +12118,7 @@
         <v>9</v>
       </c>
       <c r="G32" s="8" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="H32" s="2"/>
       <c r="I32" s="2"/>
@@ -12163,13 +12166,13 @@
       </c>
       <c r="D34" s="8"/>
       <c r="E34" s="8" t="s">
-        <v>269</v>
+        <v>266</v>
       </c>
       <c r="F34" s="8" t="s">
-        <v>270</v>
+        <v>267</v>
       </c>
       <c r="G34" s="8" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="H34" s="2"/>
       <c r="I34" s="2"/>
@@ -12231,11 +12234,11 @@
       </c>
       <c r="D37" s="8"/>
       <c r="E37" s="8" t="s">
-        <v>262</v>
+        <v>260</v>
       </c>
       <c r="F37" s="8"/>
       <c r="G37" s="8" t="s">
-        <v>273</v>
+        <v>270</v>
       </c>
     </row>
     <row r="38" spans="1:13" ht="18" x14ac:dyDescent="0.25">
@@ -12249,11 +12252,11 @@
         <v>246</v>
       </c>
       <c r="E38" s="8" t="s">
-        <v>262</v>
+        <v>260</v>
       </c>
       <c r="F38" s="8"/>
       <c r="G38" s="8" t="s">
-        <v>272</v>
+        <v>269</v>
       </c>
     </row>
     <row r="39" spans="1:13" ht="18" x14ac:dyDescent="0.25">
@@ -12942,11 +12945,11 @@
       </c>
       <c r="D5" s="71">
         <f>outcomes!C3</f>
-        <v>10504</v>
+        <v>11534</v>
       </c>
       <c r="E5" s="72">
         <f>(C3+C5)-D5</f>
-        <v>11168</v>
+        <v>10138</v>
       </c>
       <c r="F5" s="2"/>
       <c r="G5" s="2"/>
@@ -13333,7 +13336,7 @@
       </c>
       <c r="C3" s="53">
         <f>SUM(C5:C2002)</f>
-        <v>10504</v>
+        <v>11534</v>
       </c>
     </row>
     <row r="4" spans="1:19" ht="36" x14ac:dyDescent="0.2">
@@ -13519,7 +13522,7 @@
         <v>930</v>
       </c>
       <c r="D12" s="8" t="s">
-        <v>253</v>
+        <v>273</v>
       </c>
       <c r="S12">
         <v>1</v>
@@ -13536,7 +13539,7 @@
         <v>930</v>
       </c>
       <c r="D13" s="8" t="s">
-        <v>254</v>
+        <v>274</v>
       </c>
       <c r="S13">
         <v>4</v>
@@ -13553,7 +13556,7 @@
         <v>683</v>
       </c>
       <c r="D14" s="8" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="S14">
         <v>1</v>
@@ -13570,7 +13573,7 @@
         <v>3</v>
       </c>
       <c r="D15" s="8" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="E15" s="2"/>
       <c r="F15" s="2"/>
@@ -13593,7 +13596,7 @@
         <v>20</v>
       </c>
       <c r="D16" s="8" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="S16">
         <v>6</v>
@@ -13610,7 +13613,7 @@
         <v>400</v>
       </c>
       <c r="D17" s="8" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="E17" s="2"/>
       <c r="F17" s="2"/>
@@ -13633,7 +13636,7 @@
         <v>1000</v>
       </c>
       <c r="D18" s="8" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="E18" s="2"/>
       <c r="F18" s="2"/>
@@ -13656,7 +13659,7 @@
         <v>10</v>
       </c>
       <c r="D19" s="8" t="s">
-        <v>259</v>
+        <v>257</v>
       </c>
       <c r="I19" s="2"/>
       <c r="J19" s="2"/>
@@ -13675,7 +13678,7 @@
         <v>675</v>
       </c>
       <c r="D20" s="8" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
       <c r="E20" s="2"/>
       <c r="F20" s="2"/>
@@ -13698,7 +13701,7 @@
         <v>1650</v>
       </c>
       <c r="D21" s="8" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
       <c r="E21" s="2"/>
       <c r="F21" s="2"/>
@@ -13721,7 +13724,7 @@
         <v>1030</v>
       </c>
       <c r="D22" s="8" t="s">
-        <v>268</v>
+        <v>272</v>
       </c>
       <c r="E22" s="2"/>
       <c r="F22" s="2"/>
@@ -13744,7 +13747,7 @@
         <v>400</v>
       </c>
       <c r="D23" s="8" t="s">
-        <v>271</v>
+        <v>268</v>
       </c>
       <c r="E23" s="2"/>
       <c r="F23" s="2"/>
@@ -13760,9 +13763,15 @@
       <c r="A24" s="33">
         <v>20</v>
       </c>
-      <c r="B24" s="60"/>
-      <c r="C24" s="55"/>
-      <c r="D24" s="8"/>
+      <c r="B24" s="60">
+        <v>46126</v>
+      </c>
+      <c r="C24" s="55">
+        <v>1030</v>
+      </c>
+      <c r="D24" s="8" t="s">
+        <v>271</v>
+      </c>
       <c r="E24" s="2"/>
       <c r="F24" s="2"/>
       <c r="G24" s="2"/>

--- a/Book2026.xlsx
+++ b/Book2026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\syana05012019\2024\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C0DABFA8-CE3B-4AE3-9142-A8049C0E51E2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{39AF81D0-B1F4-4BE1-8116-86EEEAA767A0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" tabRatio="947" firstSheet="13" activeTab="22" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -47,7 +47,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="789" uniqueCount="275">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="799" uniqueCount="279">
   <si>
     <t>صفحة الإيرادات</t>
   </si>
@@ -872,6 +872,18 @@
   </si>
   <si>
     <t>تحت حساب فاتورة المياه عن شهر فبراير /2026</t>
+  </si>
+  <si>
+    <t>اكرامية لمحصل الكهرباء</t>
+  </si>
+  <si>
+    <t>تحت حساب نظافة السلم لام احمد عن شهر ابريل /2026</t>
+  </si>
+  <si>
+    <t>تحت حساب شراء كيس ايريال</t>
+  </si>
+  <si>
+    <t>تحت حساب كهرباء شهر ابريل /2026</t>
   </si>
 </sst>
 </file>
@@ -6051,7 +6063,7 @@
       <c r="C4" s="49"/>
       <c r="D4" s="83">
         <f>SUM(D6:D2001)</f>
-        <v>1200</v>
+        <v>1500</v>
       </c>
       <c r="E4" s="11"/>
       <c r="F4" s="83">
@@ -6206,7 +6218,9 @@
       <c r="C10" s="51">
         <v>45413</v>
       </c>
-      <c r="D10" s="33"/>
+      <c r="D10" s="33">
+        <v>300</v>
+      </c>
       <c r="E10" s="8"/>
       <c r="F10" s="33">
         <v>300</v>
@@ -8044,7 +8058,7 @@
       <c r="C4" s="10"/>
       <c r="D4" s="11">
         <f>SUM(D6:D2001)</f>
-        <v>600</v>
+        <v>750</v>
       </c>
       <c r="E4" s="11"/>
       <c r="F4" s="11">
@@ -8199,7 +8213,9 @@
       <c r="C10" s="9">
         <v>45413</v>
       </c>
-      <c r="D10" s="8"/>
+      <c r="D10" s="8">
+        <v>150</v>
+      </c>
       <c r="E10" s="8"/>
       <c r="F10" s="8">
         <v>150</v>
@@ -8711,7 +8727,7 @@
       <c r="C4" s="62"/>
       <c r="D4" s="11">
         <f>SUM(D6:D2001)</f>
-        <v>600</v>
+        <v>750</v>
       </c>
       <c r="E4" s="11"/>
       <c r="F4" s="11">
@@ -8866,7 +8882,9 @@
       <c r="C10" s="63">
         <v>45413</v>
       </c>
-      <c r="D10" s="8"/>
+      <c r="D10" s="8">
+        <v>150</v>
+      </c>
       <c r="E10" s="8"/>
       <c r="F10" s="8">
         <v>150</v>
@@ -11390,7 +11408,7 @@
       </c>
       <c r="C4" s="53">
         <f>SUM(C6:C2000)</f>
-        <v>7770</v>
+        <v>8370</v>
       </c>
     </row>
     <row r="5" spans="1:17" ht="18" x14ac:dyDescent="0.2">
@@ -12283,34 +12301,64 @@
       <c r="A40" s="8">
         <v>35</v>
       </c>
-      <c r="B40" s="51"/>
-      <c r="C40" s="55"/>
-      <c r="D40" s="8"/>
-      <c r="E40" s="8"/>
-      <c r="F40" s="8"/>
-      <c r="G40" s="8"/>
+      <c r="B40" s="51">
+        <v>46142</v>
+      </c>
+      <c r="C40" s="55">
+        <v>300</v>
+      </c>
+      <c r="E40" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="F40" s="8">
+        <v>7</v>
+      </c>
+      <c r="G40" s="8" t="s">
+        <v>226</v>
+      </c>
     </row>
     <row r="41" spans="1:13" ht="18" x14ac:dyDescent="0.25">
       <c r="A41" s="8">
         <v>36</v>
       </c>
-      <c r="B41" s="51"/>
-      <c r="C41" s="55"/>
+      <c r="B41" s="51">
+        <v>46142</v>
+      </c>
+      <c r="C41" s="55">
+        <v>150</v>
+      </c>
       <c r="D41" s="8"/>
-      <c r="E41" s="8"/>
-      <c r="F41" s="8"/>
-      <c r="G41" s="8"/>
+      <c r="E41" s="8" t="s">
+        <v>244</v>
+      </c>
+      <c r="F41" s="8">
+        <v>4</v>
+      </c>
+      <c r="G41" s="8" t="s">
+        <v>226</v>
+      </c>
       <c r="H41" s="2"/>
     </row>
     <row r="42" spans="1:13" ht="18" x14ac:dyDescent="0.25">
       <c r="A42" s="8">
         <v>37</v>
       </c>
-      <c r="B42" s="51"/>
-      <c r="C42" s="55"/>
-      <c r="E42" s="8"/>
-      <c r="F42" s="8"/>
-      <c r="G42" s="8"/>
+      <c r="B42" s="51">
+        <v>46142</v>
+      </c>
+      <c r="C42" s="55">
+        <v>150</v>
+      </c>
+      <c r="D42" s="8"/>
+      <c r="E42" s="8" t="s">
+        <v>141</v>
+      </c>
+      <c r="F42" s="8">
+        <v>3</v>
+      </c>
+      <c r="G42" s="8" t="s">
+        <v>226</v>
+      </c>
       <c r="H42" s="2"/>
       <c r="I42" s="2"/>
       <c r="J42" s="2"/>
@@ -12941,15 +12989,15 @@
       <c r="B5" s="9"/>
       <c r="C5" s="70">
         <f>incomes!C4</f>
-        <v>7770</v>
+        <v>8370</v>
       </c>
       <c r="D5" s="71">
         <f>outcomes!C3</f>
-        <v>11534</v>
+        <v>12274</v>
       </c>
       <c r="E5" s="72">
         <f>(C3+C5)-D5</f>
-        <v>10138</v>
+        <v>9998</v>
       </c>
       <c r="F5" s="2"/>
       <c r="G5" s="2"/>
@@ -13336,7 +13384,7 @@
       </c>
       <c r="C3" s="53">
         <f>SUM(C5:C2002)</f>
-        <v>11534</v>
+        <v>12274</v>
       </c>
     </row>
     <row r="4" spans="1:19" ht="36" x14ac:dyDescent="0.2">
@@ -13786,9 +13834,15 @@
       <c r="A25" s="33">
         <v>21</v>
       </c>
-      <c r="B25" s="60"/>
-      <c r="C25" s="55"/>
-      <c r="D25" s="8"/>
+      <c r="B25" s="60">
+        <v>46129</v>
+      </c>
+      <c r="C25" s="55">
+        <v>285</v>
+      </c>
+      <c r="D25" s="8" t="s">
+        <v>278</v>
+      </c>
       <c r="E25" s="2"/>
       <c r="F25" s="2"/>
       <c r="G25" s="2"/>
@@ -13800,9 +13854,15 @@
       <c r="A26" s="33">
         <v>22</v>
       </c>
-      <c r="B26" s="60"/>
-      <c r="C26" s="55"/>
-      <c r="D26" s="8"/>
+      <c r="B26" s="60">
+        <v>46129</v>
+      </c>
+      <c r="C26" s="55">
+        <v>5</v>
+      </c>
+      <c r="D26" s="8" t="s">
+        <v>275</v>
+      </c>
       <c r="I26" s="2"/>
       <c r="J26" s="2"/>
     </row>
@@ -13810,9 +13870,15 @@
       <c r="A27" s="33">
         <v>23</v>
       </c>
-      <c r="B27" s="60"/>
-      <c r="C27" s="55"/>
-      <c r="D27" s="8"/>
+      <c r="B27" s="60">
+        <v>46142</v>
+      </c>
+      <c r="C27" s="55">
+        <v>400</v>
+      </c>
+      <c r="D27" s="8" t="s">
+        <v>276</v>
+      </c>
       <c r="E27" s="2"/>
       <c r="F27" s="2"/>
       <c r="G27" s="2"/>
@@ -13827,9 +13893,15 @@
       <c r="A28" s="33">
         <v>24</v>
       </c>
-      <c r="B28" s="60"/>
-      <c r="C28" s="55"/>
-      <c r="D28" s="8"/>
+      <c r="B28" s="60">
+        <v>46142</v>
+      </c>
+      <c r="C28" s="55">
+        <v>50</v>
+      </c>
+      <c r="D28" s="8" t="s">
+        <v>277</v>
+      </c>
       <c r="E28" s="2"/>
       <c r="F28" s="2"/>
       <c r="G28" s="2"/>
@@ -19936,11 +20008,11 @@
       </c>
       <c r="E10" s="26">
         <f>Apartment3!D10</f>
-        <v>0</v>
+        <v>150</v>
       </c>
       <c r="F10" s="26">
         <f>Apartment4!D10</f>
-        <v>0</v>
+        <v>150</v>
       </c>
       <c r="G10" s="26">
         <f>Apartment5!D10</f>
@@ -19952,7 +20024,7 @@
       </c>
       <c r="I10" s="26">
         <f>Apartment7!D10</f>
-        <v>0</v>
+        <v>300</v>
       </c>
       <c r="J10" s="26">
         <f>Apartment8!D10</f>
@@ -20779,12 +20851,12 @@
       </c>
       <c r="C7" s="91">
         <f>Apartment3!D4</f>
-        <v>600</v>
+        <v>750</v>
       </c>
       <c r="D7" s="92"/>
       <c r="E7" s="94">
         <f t="shared" si="0"/>
-        <v>-600</v>
+        <v>-750</v>
       </c>
       <c r="F7" s="2" t="s">
         <v>48</v>
@@ -20806,12 +20878,12 @@
       </c>
       <c r="C8" s="91">
         <f>Apartment4!D4</f>
-        <v>600</v>
+        <v>750</v>
       </c>
       <c r="D8" s="92"/>
       <c r="E8" s="94">
         <f t="shared" si="0"/>
-        <v>-600</v>
+        <v>-750</v>
       </c>
       <c r="F8" s="2" t="s">
         <v>48</v>
@@ -20886,12 +20958,12 @@
       </c>
       <c r="C11" s="91">
         <f>Apartment7!D4</f>
-        <v>1200</v>
+        <v>1500</v>
       </c>
       <c r="D11" s="92"/>
       <c r="E11" s="94">
         <f t="shared" si="0"/>
-        <v>-1200</v>
+        <v>-1500</v>
       </c>
       <c r="F11" s="2" t="s">
         <v>48</v>

--- a/Book2026.xlsx
+++ b/Book2026.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\syana05012019\2024\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{39AF81D0-B1F4-4BE1-8116-86EEEAA767A0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F048C145-26E8-4347-AAFD-0AA8E206C784}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" tabRatio="947" firstSheet="13" activeTab="22" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" tabRatio="947" firstSheet="13" activeTab="20" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="monthly_elctricity" sheetId="28" r:id="rId1"/>
@@ -47,7 +47,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="799" uniqueCount="279">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="801" uniqueCount="280">
   <si>
     <t>صفحة الإيرادات</t>
   </si>
@@ -884,6 +884,9 @@
   </si>
   <si>
     <t>تحت حساب كهرباء شهر ابريل /2026</t>
+  </si>
+  <si>
+    <t>تحت حساب فوائد شهادة  رقم 1807951149146700023 بتاريخ اصدار 21- ديسمبر - 2025 بفائدة 14%، عن شهر ابريل / 2026</t>
   </si>
 </sst>
 </file>
@@ -11408,7 +11411,7 @@
       </c>
       <c r="C4" s="53">
         <f>SUM(C6:C2000)</f>
-        <v>8370</v>
+        <v>8428</v>
       </c>
     </row>
     <row r="5" spans="1:17" ht="18" x14ac:dyDescent="0.2">
@@ -12367,12 +12370,20 @@
       <c r="A43" s="8">
         <v>38</v>
       </c>
-      <c r="B43" s="51"/>
-      <c r="C43" s="55"/>
+      <c r="B43" s="51">
+        <v>46134</v>
+      </c>
+      <c r="C43" s="55">
+        <v>58</v>
+      </c>
       <c r="D43" s="8"/>
-      <c r="E43" s="8"/>
+      <c r="E43" s="8" t="s">
+        <v>260</v>
+      </c>
       <c r="F43" s="8"/>
-      <c r="G43" s="8"/>
+      <c r="G43" s="8" t="s">
+        <v>279</v>
+      </c>
       <c r="H43" s="2"/>
       <c r="I43" s="2"/>
       <c r="J43" s="2"/>
@@ -12989,7 +13000,7 @@
       <c r="B5" s="9"/>
       <c r="C5" s="70">
         <f>incomes!C4</f>
-        <v>8370</v>
+        <v>8428</v>
       </c>
       <c r="D5" s="71">
         <f>outcomes!C3</f>
@@ -12997,7 +13008,7 @@
       </c>
       <c r="E5" s="72">
         <f>(C3+C5)-D5</f>
-        <v>9998</v>
+        <v>10056</v>
       </c>
       <c r="F5" s="2"/>
       <c r="G5" s="2"/>

--- a/Book2026.xlsx
+++ b/Book2026.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\syana05012019\2024\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F048C145-26E8-4347-AAFD-0AA8E206C784}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{87AF2457-CF9F-4925-9802-443C9CFD6D64}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" tabRatio="947" firstSheet="13" activeTab="20" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" tabRatio="947" firstSheet="13" activeTab="18" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="monthly_elctricity" sheetId="28" r:id="rId1"/>
@@ -47,7 +47,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="801" uniqueCount="280">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="803" uniqueCount="280">
   <si>
     <t>صفحة الإيرادات</t>
   </si>
@@ -9399,7 +9399,7 @@
       <c r="C4" s="76"/>
       <c r="D4" s="11">
         <f>SUM(D6:D2001)</f>
-        <v>300</v>
+        <v>375</v>
       </c>
       <c r="E4" s="11"/>
       <c r="F4" s="83">
@@ -9552,9 +9552,11 @@
         <v>5</v>
       </c>
       <c r="C10" s="77">
-        <v>46195</v>
-      </c>
-      <c r="D10" s="8"/>
+        <v>46144</v>
+      </c>
+      <c r="D10" s="8">
+        <v>75</v>
+      </c>
       <c r="E10" s="8"/>
       <c r="F10" s="33">
         <v>75</v>
@@ -11411,7 +11413,7 @@
       </c>
       <c r="C4" s="53">
         <f>SUM(C6:C2000)</f>
-        <v>8428</v>
+        <v>8503</v>
       </c>
     </row>
     <row r="5" spans="1:17" ht="18" x14ac:dyDescent="0.2">
@@ -12392,11 +12394,21 @@
       <c r="A44" s="8">
         <v>39</v>
       </c>
-      <c r="B44" s="51"/>
-      <c r="C44" s="55"/>
-      <c r="E44" s="8"/>
-      <c r="F44" s="8"/>
-      <c r="G44" s="8"/>
+      <c r="B44" s="51">
+        <v>46144</v>
+      </c>
+      <c r="C44" s="55">
+        <v>75</v>
+      </c>
+      <c r="E44" s="8" t="s">
+        <v>160</v>
+      </c>
+      <c r="F44" s="8">
+        <v>2</v>
+      </c>
+      <c r="G44" s="8" t="s">
+        <v>225</v>
+      </c>
       <c r="H44" s="2"/>
       <c r="I44" s="2"/>
       <c r="J44" s="2"/>
@@ -13000,7 +13012,7 @@
       <c r="B5" s="9"/>
       <c r="C5" s="70">
         <f>incomes!C4</f>
-        <v>8428</v>
+        <v>8503</v>
       </c>
       <c r="D5" s="71">
         <f>outcomes!C3</f>
@@ -13008,7 +13020,7 @@
       </c>
       <c r="E5" s="72">
         <f>(C3+C5)-D5</f>
-        <v>10056</v>
+        <v>10131</v>
       </c>
       <c r="F5" s="2"/>
       <c r="G5" s="2"/>
@@ -20015,7 +20027,7 @@
       </c>
       <c r="D10" s="26">
         <f>Apartment2!D10</f>
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="E10" s="26">
         <f>Apartment3!D10</f>
@@ -20835,12 +20847,12 @@
       </c>
       <c r="C6" s="91">
         <f>Apartment2!D4</f>
-        <v>300</v>
+        <v>375</v>
       </c>
       <c r="D6" s="92"/>
       <c r="E6" s="94">
         <f t="shared" ref="E6:E18" si="0">D6-C6</f>
-        <v>-300</v>
+        <v>-375</v>
       </c>
       <c r="F6" s="2" t="s">
         <v>51</v>

--- a/Book2026.xlsx
+++ b/Book2026.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\syana05012019\2024\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{87AF2457-CF9F-4925-9802-443C9CFD6D64}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E8C5EE4A-7D28-4B18-877C-5D9D20DE62A7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" tabRatio="947" firstSheet="13" activeTab="18" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" tabRatio="947" firstSheet="13" activeTab="15" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="monthly_elctricity" sheetId="28" r:id="rId1"/>
@@ -47,7 +47,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="803" uniqueCount="280">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="805" uniqueCount="281">
   <si>
     <t>صفحة الإيرادات</t>
   </si>
@@ -887,6 +887,9 @@
   </si>
   <si>
     <t>تحت حساب فوائد شهادة  رقم 1807951149146700023 بتاريخ اصدار 21- ديسمبر - 2025 بفائدة 14%، عن شهر ابريل / 2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">تحت حساب صيانة شهور ابريل ومايو / 2026 </t>
   </si>
 </sst>
 </file>
@@ -7418,7 +7421,7 @@
       <c r="C4" s="76"/>
       <c r="D4" s="80">
         <f>SUM(D6:D2001)</f>
-        <v>900</v>
+        <v>1500</v>
       </c>
       <c r="E4" s="11"/>
       <c r="F4" s="11">
@@ -7540,7 +7543,9 @@
       <c r="C9" s="77">
         <v>46335</v>
       </c>
-      <c r="D9" s="81"/>
+      <c r="D9" s="81">
+        <v>300</v>
+      </c>
       <c r="E9" s="8"/>
       <c r="F9" s="8">
         <v>300</v>
@@ -7563,7 +7568,9 @@
       <c r="C10" s="77">
         <v>46335</v>
       </c>
-      <c r="D10" s="81"/>
+      <c r="D10" s="81">
+        <v>300</v>
+      </c>
       <c r="E10" s="8"/>
       <c r="F10" s="8">
         <v>300</v>
@@ -11413,7 +11420,7 @@
       </c>
       <c r="C4" s="53">
         <f>SUM(C6:C2000)</f>
-        <v>8503</v>
+        <v>9103</v>
       </c>
     </row>
     <row r="5" spans="1:17" ht="18" x14ac:dyDescent="0.2">
@@ -12417,12 +12424,22 @@
       <c r="A45" s="8">
         <v>40</v>
       </c>
-      <c r="B45" s="51"/>
-      <c r="C45" s="55"/>
+      <c r="B45" s="51">
+        <v>46149</v>
+      </c>
+      <c r="C45" s="55">
+        <v>600</v>
+      </c>
       <c r="D45" s="8"/>
-      <c r="E45" s="8"/>
-      <c r="F45" s="8"/>
-      <c r="G45" s="8"/>
+      <c r="E45" s="8" t="s">
+        <v>258</v>
+      </c>
+      <c r="F45" s="8">
+        <v>5</v>
+      </c>
+      <c r="G45" s="8" t="s">
+        <v>280</v>
+      </c>
       <c r="H45" s="2"/>
       <c r="I45" s="2"/>
       <c r="J45" s="2"/>
@@ -13012,7 +13029,7 @@
       <c r="B5" s="9"/>
       <c r="C5" s="70">
         <f>incomes!C4</f>
-        <v>8503</v>
+        <v>9103</v>
       </c>
       <c r="D5" s="71">
         <f>outcomes!C3</f>
@@ -13020,7 +13037,7 @@
       </c>
       <c r="E5" s="72">
         <f>(C3+C5)-D5</f>
-        <v>10131</v>
+        <v>10731</v>
       </c>
       <c r="F5" s="2"/>
       <c r="G5" s="2"/>
@@ -19977,7 +19994,7 @@
       </c>
       <c r="G9" s="26">
         <f>Apartment5!D9</f>
-        <v>0</v>
+        <v>300</v>
       </c>
       <c r="H9" s="26">
         <f>Apartment6!D9</f>
@@ -20039,7 +20056,7 @@
       </c>
       <c r="G10" s="26">
         <f>Apartment5!D10</f>
-        <v>0</v>
+        <v>300</v>
       </c>
       <c r="H10" s="26">
         <f>Apartment6!D10</f>
@@ -20928,12 +20945,12 @@
       </c>
       <c r="C9" s="91">
         <f>Apartment5!D4</f>
-        <v>900</v>
+        <v>1500</v>
       </c>
       <c r="D9" s="92"/>
       <c r="E9" s="94">
         <f t="shared" si="0"/>
-        <v>-900</v>
+        <v>-1500</v>
       </c>
       <c r="F9" s="2" t="s">
         <v>119</v>

--- a/Book2026.xlsx
+++ b/Book2026.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\syana05012019\2024\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E8C5EE4A-7D28-4B18-877C-5D9D20DE62A7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F966C592-B9DE-48D0-984A-8B971E3AF903}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" tabRatio="947" firstSheet="13" activeTab="15" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" tabRatio="947" firstSheet="13" activeTab="21" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="monthly_elctricity" sheetId="28" r:id="rId1"/>
@@ -47,7 +47,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="805" uniqueCount="281">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="807" uniqueCount="282">
   <si>
     <t>صفحة الإيرادات</t>
   </si>
@@ -890,6 +890,9 @@
   </si>
   <si>
     <t xml:space="preserve">تحت حساب صيانة شهور ابريل ومايو / 2026 </t>
+  </si>
+  <si>
+    <t>تحت حساب صيانة شهر ابريل و مايو /2026</t>
   </si>
 </sst>
 </file>
@@ -11420,7 +11423,7 @@
       </c>
       <c r="C4" s="53">
         <f>SUM(C6:C2000)</f>
-        <v>9103</v>
+        <v>9603</v>
       </c>
     </row>
     <row r="5" spans="1:17" ht="18" x14ac:dyDescent="0.2">
@@ -12448,12 +12451,21 @@
       <c r="A46" s="8">
         <v>41</v>
       </c>
-      <c r="B46" s="51"/>
-      <c r="C46" s="55"/>
-      <c r="D46" s="8"/>
-      <c r="E46" s="8"/>
-      <c r="F46" s="8"/>
-      <c r="G46" s="8"/>
+      <c r="B46" s="51">
+        <v>46152</v>
+      </c>
+      <c r="C46" s="55">
+        <v>500</v>
+      </c>
+      <c r="E46" s="8" t="s">
+        <v>142</v>
+      </c>
+      <c r="F46" s="8">
+        <v>12</v>
+      </c>
+      <c r="G46" s="8" t="s">
+        <v>281</v>
+      </c>
     </row>
     <row r="47" spans="1:13" ht="18" x14ac:dyDescent="0.25">
       <c r="A47" s="8">
@@ -13029,7 +13041,7 @@
       <c r="B5" s="9"/>
       <c r="C5" s="70">
         <f>incomes!C4</f>
-        <v>9103</v>
+        <v>9603</v>
       </c>
       <c r="D5" s="71">
         <f>outcomes!C3</f>
@@ -13037,7 +13049,7 @@
       </c>
       <c r="E5" s="72">
         <f>(C3+C5)-D5</f>
-        <v>10731</v>
+        <v>11231</v>
       </c>
       <c r="F5" s="2"/>
       <c r="G5" s="2"/>
@@ -20022,7 +20034,7 @@
       </c>
       <c r="N9" s="26">
         <f>Apartment12!D9</f>
-        <v>0</v>
+        <v>250</v>
       </c>
       <c r="O9" s="26">
         <f>Apartment13!D9</f>
@@ -20084,7 +20096,7 @@
       </c>
       <c r="N10" s="26">
         <f>Apartment12!D10</f>
-        <v>0</v>
+        <v>250</v>
       </c>
       <c r="O10" s="26">
         <f>Apartment13!D10</f>
@@ -22114,7 +22126,7 @@
       <c r="C4" s="76"/>
       <c r="D4" s="83">
         <f>SUM(D6:D2001)</f>
-        <v>750</v>
+        <v>1250</v>
       </c>
       <c r="E4" s="11"/>
       <c r="F4" s="83">
@@ -22239,8 +22251,12 @@
       <c r="B9" s="73">
         <v>4</v>
       </c>
-      <c r="C9" s="77"/>
-      <c r="D9" s="33"/>
+      <c r="C9" s="77">
+        <v>46152</v>
+      </c>
+      <c r="D9" s="33">
+        <v>250</v>
+      </c>
       <c r="E9" s="8"/>
       <c r="F9" s="33">
         <v>250</v>
@@ -22262,8 +22278,12 @@
       <c r="B10" s="73">
         <v>5</v>
       </c>
-      <c r="C10" s="77"/>
-      <c r="D10" s="33"/>
+      <c r="C10" s="77">
+        <v>46152</v>
+      </c>
+      <c r="D10" s="33">
+        <v>250</v>
+      </c>
       <c r="E10" s="8"/>
       <c r="F10" s="33">
         <v>250</v>

--- a/Book2026.xlsx
+++ b/Book2026.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\syana05012019\2024\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F966C592-B9DE-48D0-984A-8B971E3AF903}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1FDB77E9-234C-4806-B157-9D149844DB0E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" tabRatio="947" firstSheet="13" activeTab="21" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" tabRatio="947" firstSheet="13" activeTab="22" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="monthly_elctricity" sheetId="28" r:id="rId1"/>
@@ -47,7 +47,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="807" uniqueCount="282">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="809" uniqueCount="284">
   <si>
     <t>صفحة الإيرادات</t>
   </si>
@@ -893,6 +893,12 @@
   </si>
   <si>
     <t>تحت حساب صيانة شهر ابريل و مايو /2026</t>
+  </si>
+  <si>
+    <t>تحت حساب فاتورة المياه عن شهر مايو /2026</t>
+  </si>
+  <si>
+    <t>تحت حساب كهرباء شهر مايو /2026</t>
   </si>
 </sst>
 </file>
@@ -13045,11 +13051,11 @@
       </c>
       <c r="D5" s="71">
         <f>outcomes!C3</f>
-        <v>12274</v>
+        <v>13767</v>
       </c>
       <c r="E5" s="72">
         <f>(C3+C5)-D5</f>
-        <v>11231</v>
+        <v>9738</v>
       </c>
       <c r="F5" s="2"/>
       <c r="G5" s="2"/>
@@ -13436,7 +13442,7 @@
       </c>
       <c r="C3" s="53">
         <f>SUM(C5:C2002)</f>
-        <v>12274</v>
+        <v>13767</v>
       </c>
     </row>
     <row r="4" spans="1:19" ht="36" x14ac:dyDescent="0.2">
@@ -13965,9 +13971,15 @@
       <c r="A29" s="33">
         <v>25</v>
       </c>
-      <c r="B29" s="60"/>
-      <c r="C29" s="55"/>
-      <c r="D29" s="8"/>
+      <c r="B29" s="60">
+        <v>46155</v>
+      </c>
+      <c r="C29" s="55">
+        <v>1030</v>
+      </c>
+      <c r="D29" s="8" t="s">
+        <v>282</v>
+      </c>
       <c r="E29" s="2"/>
       <c r="F29" s="2"/>
       <c r="G29" s="2"/>
@@ -13979,9 +13991,15 @@
       <c r="A30" s="33">
         <v>26</v>
       </c>
-      <c r="B30" s="60"/>
-      <c r="C30" s="55"/>
-      <c r="D30" s="8"/>
+      <c r="B30" s="60">
+        <v>46158</v>
+      </c>
+      <c r="C30" s="55">
+        <v>463</v>
+      </c>
+      <c r="D30" s="8" t="s">
+        <v>283</v>
+      </c>
       <c r="E30" s="2"/>
       <c r="F30" s="2"/>
       <c r="G30" s="2"/>

--- a/Book2026.xlsx
+++ b/Book2026.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\syana05012019\2024\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1FDB77E9-234C-4806-B157-9D149844DB0E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{163DA93E-4EC0-42DD-A258-10EDCE27433F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" tabRatio="947" firstSheet="13" activeTab="22" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" tabRatio="947" firstSheet="11" activeTab="21" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="monthly_elctricity" sheetId="28" r:id="rId1"/>
@@ -47,7 +47,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="809" uniqueCount="284">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="814" uniqueCount="287">
   <si>
     <t>صفحة الإيرادات</t>
   </si>
@@ -899,6 +899,15 @@
   </si>
   <si>
     <t>تحت حساب كهرباء شهر مايو /2026</t>
+  </si>
+  <si>
+    <t>تحت حساب اصلاح الموتور - شراء شيك بلف 575 ج - لاكور وكتان وحاجة ثانية وتفلون 110 ج - ومصنعية 315 ج</t>
+  </si>
+  <si>
+    <t>تحت حساب صيانة شهر ابريل ومايو /2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">تحت حساب صيانة شهور ابريل و مايو ويونية / 2026 </t>
   </si>
 </sst>
 </file>
@@ -4632,7 +4641,7 @@
       <c r="C4" s="49"/>
       <c r="D4" s="11">
         <f>SUM(D6:D2004)</f>
-        <v>450</v>
+        <v>900</v>
       </c>
       <c r="E4" s="11"/>
       <c r="F4" s="11">
@@ -4793,9 +4802,11 @@
         <v>4</v>
       </c>
       <c r="C9" s="51">
-        <v>46195</v>
-      </c>
-      <c r="D9" s="55"/>
+        <v>46158</v>
+      </c>
+      <c r="D9" s="55">
+        <v>150</v>
+      </c>
       <c r="E9" s="8"/>
       <c r="F9" s="8">
         <v>150</v>
@@ -4825,9 +4836,11 @@
         <v>5</v>
       </c>
       <c r="C10" s="51">
-        <v>46195</v>
-      </c>
-      <c r="D10" s="55"/>
+        <v>46158</v>
+      </c>
+      <c r="D10" s="55">
+        <v>150</v>
+      </c>
       <c r="E10" s="8"/>
       <c r="F10" s="8">
         <v>150</v>
@@ -4857,9 +4870,11 @@
         <v>6</v>
       </c>
       <c r="C11" s="51">
-        <v>46195</v>
-      </c>
-      <c r="D11" s="55"/>
+        <v>46158</v>
+      </c>
+      <c r="D11" s="55">
+        <v>150</v>
+      </c>
       <c r="E11" s="8"/>
       <c r="F11" s="8">
         <v>150</v>
@@ -5414,7 +5429,7 @@
       <c r="C4" s="76"/>
       <c r="D4" s="83">
         <f>SUM(D6:D2001)</f>
-        <v>900</v>
+        <v>1500</v>
       </c>
       <c r="E4" s="11"/>
       <c r="F4" s="83">
@@ -5540,9 +5555,11 @@
         <v>4</v>
       </c>
       <c r="C9" s="77">
-        <v>46152</v>
-      </c>
-      <c r="D9" s="33"/>
+        <v>46158</v>
+      </c>
+      <c r="D9" s="33">
+        <v>300</v>
+      </c>
       <c r="E9" s="8"/>
       <c r="F9" s="33">
         <v>300</v>
@@ -5565,9 +5582,11 @@
         <v>5</v>
       </c>
       <c r="C10" s="77">
-        <v>46152</v>
-      </c>
-      <c r="D10" s="33"/>
+        <v>46158</v>
+      </c>
+      <c r="D10" s="33">
+        <v>300</v>
+      </c>
       <c r="E10" s="8"/>
       <c r="F10" s="33">
         <v>300</v>
@@ -11429,7 +11448,7 @@
       </c>
       <c r="C4" s="53">
         <f>SUM(C6:C2000)</f>
-        <v>9603</v>
+        <v>10653</v>
       </c>
     </row>
     <row r="5" spans="1:17" ht="18" x14ac:dyDescent="0.2">
@@ -12477,22 +12496,42 @@
       <c r="A47" s="8">
         <v>42</v>
       </c>
-      <c r="B47" s="51"/>
-      <c r="C47" s="55"/>
-      <c r="E47" s="8"/>
-      <c r="F47" s="8"/>
-      <c r="G47" s="8"/>
+      <c r="B47" s="51">
+        <v>46158</v>
+      </c>
+      <c r="C47" s="55">
+        <v>600</v>
+      </c>
+      <c r="E47" s="8" t="s">
+        <v>249</v>
+      </c>
+      <c r="F47" s="8">
+        <v>8</v>
+      </c>
+      <c r="G47" s="8" t="s">
+        <v>285</v>
+      </c>
     </row>
     <row r="48" spans="1:13" ht="18" x14ac:dyDescent="0.25">
       <c r="A48" s="8">
         <v>43</v>
       </c>
-      <c r="B48" s="51"/>
-      <c r="C48" s="55"/>
+      <c r="B48" s="51">
+        <v>46158</v>
+      </c>
+      <c r="C48" s="55">
+        <v>450</v>
+      </c>
       <c r="D48" s="8"/>
-      <c r="E48" s="8"/>
-      <c r="F48" s="8"/>
-      <c r="G48" s="8"/>
+      <c r="E48" s="8" t="s">
+        <v>184</v>
+      </c>
+      <c r="F48" s="8">
+        <v>9</v>
+      </c>
+      <c r="G48" s="8" t="s">
+        <v>286</v>
+      </c>
     </row>
     <row r="49" spans="1:11" ht="18" x14ac:dyDescent="0.25">
       <c r="A49" s="8">
@@ -13047,15 +13086,15 @@
       <c r="B5" s="9"/>
       <c r="C5" s="70">
         <f>incomes!C4</f>
-        <v>9603</v>
+        <v>10653</v>
       </c>
       <c r="D5" s="71">
         <f>outcomes!C3</f>
-        <v>13767</v>
+        <v>14767</v>
       </c>
       <c r="E5" s="72">
         <f>(C3+C5)-D5</f>
-        <v>9738</v>
+        <v>9788</v>
       </c>
       <c r="F5" s="2"/>
       <c r="G5" s="2"/>
@@ -13442,7 +13481,7 @@
       </c>
       <c r="C3" s="53">
         <f>SUM(C5:C2002)</f>
-        <v>13767</v>
+        <v>14767</v>
       </c>
     </row>
     <row r="4" spans="1:19" ht="36" x14ac:dyDescent="0.2">
@@ -14011,9 +14050,15 @@
       <c r="A31" s="33">
         <v>27</v>
       </c>
-      <c r="B31" s="60"/>
-      <c r="C31" s="55"/>
-      <c r="D31" s="8"/>
+      <c r="B31" s="60">
+        <v>46159</v>
+      </c>
+      <c r="C31" s="55">
+        <v>1000</v>
+      </c>
+      <c r="D31" s="8" t="s">
+        <v>284</v>
+      </c>
       <c r="E31" s="2"/>
       <c r="F31" s="2"/>
       <c r="G31" s="2"/>
@@ -20036,11 +20081,11 @@
       </c>
       <c r="J9" s="26">
         <f>Apartment8!D9</f>
-        <v>0</v>
+        <v>300</v>
       </c>
       <c r="K9" s="26">
         <f>Apartment9!D9</f>
-        <v>0</v>
+        <v>150</v>
       </c>
       <c r="L9" s="26">
         <f>Apartment10!D9</f>
@@ -20098,11 +20143,11 @@
       </c>
       <c r="J10" s="26">
         <f>Apartment8!D10</f>
-        <v>0</v>
+        <v>300</v>
       </c>
       <c r="K10" s="26">
         <f>Apartment9!D10</f>
-        <v>0</v>
+        <v>150</v>
       </c>
       <c r="L10" s="26">
         <f>Apartment10!D10</f>
@@ -20164,7 +20209,7 @@
       </c>
       <c r="K11" s="26">
         <f>Apartment9!D11</f>
-        <v>0</v>
+        <v>150</v>
       </c>
       <c r="L11" s="26">
         <f>Apartment10!D11</f>
@@ -21055,12 +21100,12 @@
       </c>
       <c r="C12" s="91">
         <f>Apartment8!D4</f>
-        <v>900</v>
+        <v>1500</v>
       </c>
       <c r="D12" s="92"/>
       <c r="E12" s="94">
         <f t="shared" si="0"/>
-        <v>-900</v>
+        <v>-1500</v>
       </c>
       <c r="F12" s="2" t="s">
         <v>120</v>
@@ -21082,12 +21127,12 @@
       </c>
       <c r="C13" s="91">
         <f>Apartment9!D4</f>
-        <v>450</v>
+        <v>900</v>
       </c>
       <c r="D13" s="92"/>
       <c r="E13" s="94">
         <f t="shared" si="0"/>
-        <v>-450</v>
+        <v>-900</v>
       </c>
       <c r="F13" s="2" t="s">
         <v>53</v>

--- a/Book2026.xlsx
+++ b/Book2026.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\syana05012019\2024\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{163DA93E-4EC0-42DD-A258-10EDCE27433F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{86BBBA09-A087-4343-9E67-6DF94908CCD2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" tabRatio="947" firstSheet="11" activeTab="21" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" tabRatio="947" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="monthly_elctricity" sheetId="28" r:id="rId1"/>
@@ -47,7 +47,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="814" uniqueCount="287">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="817" uniqueCount="287">
   <si>
     <t>صفحة الإيرادات</t>
   </si>
@@ -11448,7 +11448,7 @@
       </c>
       <c r="C4" s="53">
         <f>SUM(C6:C2000)</f>
-        <v>10653</v>
+        <v>11253</v>
       </c>
     </row>
     <row r="5" spans="1:17" ht="18" x14ac:dyDescent="0.2">
@@ -12537,12 +12537,22 @@
       <c r="A49" s="8">
         <v>44</v>
       </c>
-      <c r="B49" s="51"/>
-      <c r="C49" s="55"/>
+      <c r="B49" s="51">
+        <v>46159</v>
+      </c>
+      <c r="C49" s="55">
+        <v>600</v>
+      </c>
       <c r="D49" s="8"/>
-      <c r="E49" s="8"/>
-      <c r="F49" s="8"/>
-      <c r="G49" s="8"/>
+      <c r="E49" s="8" t="s">
+        <v>266</v>
+      </c>
+      <c r="F49" s="8" t="s">
+        <v>267</v>
+      </c>
+      <c r="G49" s="8" t="s">
+        <v>280</v>
+      </c>
     </row>
     <row r="50" spans="1:11" ht="18" x14ac:dyDescent="0.25">
       <c r="A50" s="8">
@@ -13086,7 +13096,7 @@
       <c r="B5" s="9"/>
       <c r="C5" s="70">
         <f>incomes!C4</f>
-        <v>10653</v>
+        <v>11253</v>
       </c>
       <c r="D5" s="71">
         <f>outcomes!C3</f>
@@ -13094,7 +13104,7 @@
       </c>
       <c r="E5" s="72">
         <f>(C3+C5)-D5</f>
-        <v>9788</v>
+        <v>10388</v>
       </c>
       <c r="F5" s="2"/>
       <c r="G5" s="2"/>
@@ -20101,11 +20111,11 @@
       </c>
       <c r="O9" s="26">
         <f>Apartment13!D9</f>
-        <v>0</v>
+        <v>150</v>
       </c>
       <c r="P9" s="26">
         <f>Apartment14!D9</f>
-        <v>0</v>
+        <v>150</v>
       </c>
     </row>
     <row r="10" spans="1:20" ht="23.25" x14ac:dyDescent="0.35">
@@ -20163,11 +20173,11 @@
       </c>
       <c r="O10" s="26">
         <f>Apartment13!D10</f>
-        <v>0</v>
+        <v>150</v>
       </c>
       <c r="P10" s="26">
         <f>Apartment14!D10</f>
-        <v>0</v>
+        <v>150</v>
       </c>
     </row>
     <row r="11" spans="1:20" ht="23.25" x14ac:dyDescent="0.35">
@@ -21231,12 +21241,12 @@
       </c>
       <c r="C17" s="91">
         <f>Apartment13!D4</f>
-        <v>375</v>
+        <v>675</v>
       </c>
       <c r="D17" s="92"/>
       <c r="E17" s="94">
         <f t="shared" si="0"/>
-        <v>-375</v>
+        <v>-675</v>
       </c>
       <c r="F17" s="2" t="s">
         <v>56</v>
@@ -21258,12 +21268,12 @@
       </c>
       <c r="C18" s="91">
         <f>Apartment14!D4</f>
-        <v>375</v>
+        <v>675</v>
       </c>
       <c r="D18" s="92"/>
       <c r="E18" s="94">
         <f t="shared" si="0"/>
-        <v>-375</v>
+        <v>-675</v>
       </c>
       <c r="F18" s="2" t="s">
         <v>57</v>
@@ -21524,7 +21534,7 @@
       <c r="C4" s="62"/>
       <c r="D4" s="11">
         <f>SUM(D6:D2001)</f>
-        <v>375</v>
+        <v>675</v>
       </c>
       <c r="E4" s="11"/>
       <c r="F4" s="11">
@@ -21649,10 +21659,12 @@
       <c r="B9" s="8">
         <v>4</v>
       </c>
-      <c r="C9" s="63">
-        <v>46242</v>
-      </c>
-      <c r="D9" s="33"/>
+      <c r="C9" s="51">
+        <v>46159</v>
+      </c>
+      <c r="D9" s="33">
+        <v>150</v>
+      </c>
       <c r="E9" s="8"/>
       <c r="F9" s="8">
         <v>150</v>
@@ -21674,10 +21686,12 @@
       <c r="B10" s="8">
         <v>5</v>
       </c>
-      <c r="C10" s="63">
-        <v>46242</v>
-      </c>
-      <c r="D10" s="33"/>
+      <c r="C10" s="51">
+        <v>46159</v>
+      </c>
+      <c r="D10" s="33">
+        <v>150</v>
+      </c>
       <c r="E10" s="8"/>
       <c r="F10" s="8">
         <v>150</v>
@@ -22844,7 +22858,7 @@
       <c r="C4" s="49"/>
       <c r="D4" s="83">
         <f>SUM(D6:D2001)</f>
-        <v>375</v>
+        <v>675</v>
       </c>
       <c r="E4" s="11"/>
       <c r="F4" s="11">
@@ -22970,9 +22984,11 @@
         <v>4</v>
       </c>
       <c r="C9" s="51">
-        <v>46242</v>
-      </c>
-      <c r="D9" s="33"/>
+        <v>46159</v>
+      </c>
+      <c r="D9" s="33">
+        <v>150</v>
+      </c>
       <c r="E9" s="8"/>
       <c r="F9" s="8">
         <v>150</v>
@@ -22995,9 +23011,11 @@
         <v>5</v>
       </c>
       <c r="C10" s="51">
-        <v>46242</v>
-      </c>
-      <c r="D10" s="33"/>
+        <v>46159</v>
+      </c>
+      <c r="D10" s="33">
+        <v>150</v>
+      </c>
       <c r="E10" s="8"/>
       <c r="F10" s="8">
         <v>150</v>

--- a/Book2026.xlsx
+++ b/Book2026.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\syana05012019\2024\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{86BBBA09-A087-4343-9E67-6DF94908CCD2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BAC37A93-3154-46F0-8C6B-C12367E48311}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" tabRatio="947" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" tabRatio="947" firstSheet="13" activeTab="22" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="monthly_elctricity" sheetId="28" r:id="rId1"/>
@@ -47,7 +47,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="817" uniqueCount="287">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="820" uniqueCount="288">
   <si>
     <t>صفحة الإيرادات</t>
   </si>
@@ -908,6 +908,9 @@
   </si>
   <si>
     <t xml:space="preserve">تحت حساب صيانة شهور ابريل و مايو ويونية / 2026 </t>
+  </si>
+  <si>
+    <t>تحت حساب نظافة السلم لام احمد عن شهر مايو /2026</t>
   </si>
 </sst>
 </file>
@@ -10744,7 +10747,7 @@
       <c r="C4" s="10"/>
       <c r="D4" s="11">
         <f>SUM(D6:D2001)</f>
-        <v>450</v>
+        <v>750</v>
       </c>
       <c r="E4" s="11"/>
       <c r="F4" s="11">
@@ -10875,7 +10878,9 @@
       <c r="C9" s="51">
         <v>46222</v>
       </c>
-      <c r="D9" s="73"/>
+      <c r="D9" s="73">
+        <v>150</v>
+      </c>
       <c r="E9" s="8"/>
       <c r="F9" s="73">
         <v>150</v>
@@ -10900,7 +10905,9 @@
       <c r="C10" s="51">
         <v>46222</v>
       </c>
-      <c r="D10" s="73"/>
+      <c r="D10" s="73">
+        <v>150</v>
+      </c>
       <c r="E10" s="8"/>
       <c r="F10" s="73">
         <v>150</v>
@@ -11448,7 +11455,7 @@
       </c>
       <c r="C4" s="53">
         <f>SUM(C6:C2000)</f>
-        <v>11253</v>
+        <v>11553</v>
       </c>
     </row>
     <row r="5" spans="1:17" ht="18" x14ac:dyDescent="0.2">
@@ -12558,12 +12565,22 @@
       <c r="A50" s="8">
         <v>45</v>
       </c>
-      <c r="B50" s="51"/>
-      <c r="C50" s="55"/>
+      <c r="B50" s="51">
+        <v>46168</v>
+      </c>
+      <c r="C50" s="55">
+        <v>300</v>
+      </c>
       <c r="D50" s="8"/>
-      <c r="E50" s="8"/>
-      <c r="F50" s="8"/>
-      <c r="G50" s="8"/>
+      <c r="E50" s="8" t="s">
+        <v>186</v>
+      </c>
+      <c r="F50" s="8">
+        <v>1</v>
+      </c>
+      <c r="G50" s="8" t="s">
+        <v>285</v>
+      </c>
     </row>
     <row r="51" spans="1:11" ht="18" x14ac:dyDescent="0.25">
       <c r="A51" s="8">
@@ -13096,15 +13113,15 @@
       <c r="B5" s="9"/>
       <c r="C5" s="70">
         <f>incomes!C4</f>
-        <v>11253</v>
+        <v>11553</v>
       </c>
       <c r="D5" s="71">
         <f>outcomes!C3</f>
-        <v>14767</v>
+        <v>15167</v>
       </c>
       <c r="E5" s="72">
         <f>(C3+C5)-D5</f>
-        <v>10388</v>
+        <v>10288</v>
       </c>
       <c r="F5" s="2"/>
       <c r="G5" s="2"/>
@@ -13491,7 +13508,7 @@
       </c>
       <c r="C3" s="53">
         <f>SUM(C5:C2002)</f>
-        <v>14767</v>
+        <v>15167</v>
       </c>
     </row>
     <row r="4" spans="1:19" ht="36" x14ac:dyDescent="0.2">
@@ -14080,9 +14097,15 @@
       <c r="A32" s="33">
         <v>28</v>
       </c>
-      <c r="B32" s="60"/>
-      <c r="C32" s="55"/>
-      <c r="D32" s="8"/>
+      <c r="B32" s="60">
+        <v>46168</v>
+      </c>
+      <c r="C32" s="55">
+        <v>400</v>
+      </c>
+      <c r="D32" s="8" t="s">
+        <v>287</v>
+      </c>
       <c r="E32" s="2"/>
       <c r="F32" s="2"/>
       <c r="G32" s="2"/>
@@ -20063,7 +20086,7 @@
       </c>
       <c r="C9" s="26">
         <f>Apartment1!D9</f>
-        <v>0</v>
+        <v>150</v>
       </c>
       <c r="D9" s="26">
         <f>Apartment2!D9</f>
@@ -20125,7 +20148,7 @@
       </c>
       <c r="C10" s="26">
         <f>Apartment1!D10</f>
-        <v>0</v>
+        <v>150</v>
       </c>
       <c r="D10" s="26">
         <f>Apartment2!D10</f>
@@ -20922,12 +20945,12 @@
       </c>
       <c r="C5" s="91">
         <f>Apartment1!D4</f>
-        <v>450</v>
+        <v>750</v>
       </c>
       <c r="D5" s="92"/>
       <c r="E5" s="94">
         <f>D5-C5</f>
-        <v>-450</v>
+        <v>-750</v>
       </c>
       <c r="F5" s="2" t="s">
         <v>50</v>

--- a/Book2026.xlsx
+++ b/Book2026.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\syana05012019\2024\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BAC37A93-3154-46F0-8C6B-C12367E48311}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4BDB350D-BD9E-45A9-9584-C0283487C207}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" tabRatio="947" firstSheet="13" activeTab="22" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" tabRatio="947" firstSheet="13" activeTab="21" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="monthly_elctricity" sheetId="28" r:id="rId1"/>
@@ -47,7 +47,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="820" uniqueCount="288">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="830" uniqueCount="290">
   <si>
     <t>صفحة الإيرادات</t>
   </si>
@@ -911,6 +911,12 @@
   </si>
   <si>
     <t>تحت حساب نظافة السلم لام احمد عن شهر مايو /2026</t>
+  </si>
+  <si>
+    <t>تحت حساب صيانة شهر يونيه /2026</t>
+  </si>
+  <si>
+    <t>تحت حساب فوائد شهادة  رقم 1807951149146700023 بتاريخ اصدار 21- ديسمبر - 2025 بفائدة 14%، عن شهر مايو / 2026</t>
   </si>
 </sst>
 </file>
@@ -6100,7 +6106,7 @@
       <c r="C4" s="49"/>
       <c r="D4" s="83">
         <f>SUM(D6:D2001)</f>
-        <v>1500</v>
+        <v>1800</v>
       </c>
       <c r="E4" s="11"/>
       <c r="F4" s="83">
@@ -6280,9 +6286,11 @@
         <v>6</v>
       </c>
       <c r="C11" s="51">
-        <v>45444</v>
-      </c>
-      <c r="D11" s="33"/>
+        <v>45449</v>
+      </c>
+      <c r="D11" s="33">
+        <v>300</v>
+      </c>
       <c r="E11" s="8"/>
       <c r="F11" s="33">
         <v>300</v>
@@ -8099,7 +8107,7 @@
       <c r="C4" s="10"/>
       <c r="D4" s="11">
         <f>SUM(D6:D2001)</f>
-        <v>750</v>
+        <v>900</v>
       </c>
       <c r="E4" s="11"/>
       <c r="F4" s="11">
@@ -8279,9 +8287,11 @@
         <v>6</v>
       </c>
       <c r="C11" s="9">
-        <v>45444</v>
-      </c>
-      <c r="D11" s="8"/>
+        <v>45449</v>
+      </c>
+      <c r="D11" s="8">
+        <v>150</v>
+      </c>
       <c r="E11" s="8"/>
       <c r="F11" s="8">
         <v>150</v>
@@ -8768,7 +8778,7 @@
       <c r="C4" s="62"/>
       <c r="D4" s="11">
         <f>SUM(D6:D2001)</f>
-        <v>750</v>
+        <v>900</v>
       </c>
       <c r="E4" s="11"/>
       <c r="F4" s="11">
@@ -8948,9 +8958,11 @@
         <v>6</v>
       </c>
       <c r="C11" s="63">
-        <v>45444</v>
-      </c>
-      <c r="D11" s="8"/>
+        <v>45449</v>
+      </c>
+      <c r="D11" s="8">
+        <v>150</v>
+      </c>
       <c r="E11" s="8"/>
       <c r="F11" s="8">
         <v>150</v>
@@ -9437,7 +9449,7 @@
       <c r="C4" s="76"/>
       <c r="D4" s="11">
         <f>SUM(D6:D2001)</f>
-        <v>375</v>
+        <v>450</v>
       </c>
       <c r="E4" s="11"/>
       <c r="F4" s="83">
@@ -9617,9 +9629,11 @@
         <v>6</v>
       </c>
       <c r="C11" s="77">
-        <v>46195</v>
-      </c>
-      <c r="D11" s="8"/>
+        <v>46176</v>
+      </c>
+      <c r="D11" s="8">
+        <v>75</v>
+      </c>
       <c r="E11" s="8"/>
       <c r="F11" s="33">
         <v>75</v>
@@ -11455,7 +11469,7 @@
       </c>
       <c r="C4" s="53">
         <f>SUM(C6:C2000)</f>
-        <v>11553</v>
+        <v>12286</v>
       </c>
     </row>
     <row r="5" spans="1:17" ht="18" x14ac:dyDescent="0.2">
@@ -12449,7 +12463,7 @@
         <v>2</v>
       </c>
       <c r="G44" s="8" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="H44" s="2"/>
       <c r="I44" s="2"/>
@@ -12586,56 +12600,103 @@
       <c r="A51" s="8">
         <v>46</v>
       </c>
-      <c r="B51" s="51"/>
-      <c r="C51" s="55"/>
-      <c r="E51" s="8"/>
-      <c r="F51" s="8"/>
-      <c r="G51" s="8"/>
+      <c r="B51" s="51">
+        <v>46179</v>
+      </c>
+      <c r="C51" s="55">
+        <v>300</v>
+      </c>
+      <c r="E51" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="F51" s="8">
+        <v>7</v>
+      </c>
+      <c r="G51" s="8" t="s">
+        <v>288</v>
+      </c>
       <c r="H51" s="2"/>
     </row>
     <row r="52" spans="1:11" ht="18" x14ac:dyDescent="0.25">
       <c r="A52" s="8">
         <v>47</v>
       </c>
-      <c r="B52" s="51"/>
-      <c r="C52" s="55"/>
+      <c r="B52" s="51">
+        <v>46179</v>
+      </c>
+      <c r="C52" s="55">
+        <v>150</v>
+      </c>
       <c r="D52" s="8"/>
-      <c r="E52" s="8"/>
-      <c r="F52" s="8"/>
-      <c r="G52" s="8"/>
+      <c r="E52" s="8" t="s">
+        <v>244</v>
+      </c>
+      <c r="F52" s="8">
+        <v>4</v>
+      </c>
+      <c r="G52" s="8" t="s">
+        <v>288</v>
+      </c>
     </row>
     <row r="53" spans="1:11" ht="18" x14ac:dyDescent="0.25">
       <c r="A53" s="8">
         <v>48</v>
       </c>
-      <c r="B53" s="51"/>
-      <c r="C53" s="55"/>
+      <c r="B53" s="51">
+        <v>46179</v>
+      </c>
+      <c r="C53" s="55">
+        <v>150</v>
+      </c>
       <c r="D53" s="8"/>
-      <c r="E53" s="8"/>
-      <c r="F53" s="8"/>
-      <c r="G53" s="8"/>
+      <c r="E53" s="8" t="s">
+        <v>141</v>
+      </c>
+      <c r="F53" s="8">
+        <v>3</v>
+      </c>
+      <c r="G53" s="8" t="s">
+        <v>288</v>
+      </c>
     </row>
     <row r="54" spans="1:11" ht="18" x14ac:dyDescent="0.25">
       <c r="A54" s="8">
         <v>49</v>
       </c>
-      <c r="B54" s="51"/>
-      <c r="C54" s="55"/>
-      <c r="D54" s="8"/>
-      <c r="E54" s="8"/>
-      <c r="F54" s="8"/>
-      <c r="G54" s="8"/>
+      <c r="B54" s="51">
+        <v>46176</v>
+      </c>
+      <c r="C54" s="55">
+        <v>75</v>
+      </c>
+      <c r="E54" s="8" t="s">
+        <v>160</v>
+      </c>
+      <c r="F54" s="8">
+        <v>2</v>
+      </c>
+      <c r="G54" s="8" t="s">
+        <v>288</v>
+      </c>
     </row>
     <row r="55" spans="1:11" ht="18" x14ac:dyDescent="0.25">
       <c r="A55" s="8">
         <v>50</v>
       </c>
-      <c r="B55" s="51"/>
-      <c r="C55" s="55"/>
+      <c r="B55" s="51">
+        <v>46164</v>
+      </c>
+      <c r="C55" s="55">
+        <v>58</v>
+      </c>
       <c r="D55" s="8"/>
-      <c r="E55" s="8"/>
+      <c r="E55" s="8" t="s">
+        <v>260</v>
+      </c>
       <c r="F55" s="8"/>
-      <c r="G55" s="8"/>
+      <c r="G55" s="8" t="s">
+        <v>289</v>
+      </c>
     </row>
     <row r="56" spans="1:11" ht="18" x14ac:dyDescent="0.25">
       <c r="A56" s="8">
@@ -13113,7 +13174,7 @@
       <c r="B5" s="9"/>
       <c r="C5" s="70">
         <f>incomes!C4</f>
-        <v>11553</v>
+        <v>12286</v>
       </c>
       <c r="D5" s="71">
         <f>outcomes!C3</f>
@@ -13121,7 +13182,7 @@
       </c>
       <c r="E5" s="72">
         <f>(C3+C5)-D5</f>
-        <v>10288</v>
+        <v>11021</v>
       </c>
       <c r="F5" s="2"/>
       <c r="G5" s="2"/>
@@ -20214,15 +20275,15 @@
       </c>
       <c r="D11" s="26">
         <f>Apartment2!D11</f>
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="E11" s="26">
         <f>Apartment3!D11</f>
-        <v>0</v>
+        <v>150</v>
       </c>
       <c r="F11" s="26">
         <f>Apartment4!D11</f>
-        <v>0</v>
+        <v>150</v>
       </c>
       <c r="G11" s="26">
         <f>Apartment5!D11</f>
@@ -20234,7 +20295,7 @@
       </c>
       <c r="I11" s="26">
         <f>Apartment7!D11</f>
-        <v>0</v>
+        <v>300</v>
       </c>
       <c r="J11" s="26">
         <f>Apartment8!D11</f>
@@ -20972,12 +21033,12 @@
       </c>
       <c r="C6" s="91">
         <f>Apartment2!D4</f>
-        <v>375</v>
+        <v>450</v>
       </c>
       <c r="D6" s="92"/>
       <c r="E6" s="94">
         <f t="shared" ref="E6:E18" si="0">D6-C6</f>
-        <v>-375</v>
+        <v>-450</v>
       </c>
       <c r="F6" s="2" t="s">
         <v>51</v>
@@ -20999,12 +21060,12 @@
       </c>
       <c r="C7" s="91">
         <f>Apartment3!D4</f>
-        <v>750</v>
+        <v>900</v>
       </c>
       <c r="D7" s="92"/>
       <c r="E7" s="94">
         <f t="shared" si="0"/>
-        <v>-750</v>
+        <v>-900</v>
       </c>
       <c r="F7" s="2" t="s">
         <v>48</v>
@@ -21026,12 +21087,12 @@
       </c>
       <c r="C8" s="91">
         <f>Apartment4!D4</f>
-        <v>750</v>
+        <v>900</v>
       </c>
       <c r="D8" s="92"/>
       <c r="E8" s="94">
         <f t="shared" si="0"/>
-        <v>-750</v>
+        <v>-900</v>
       </c>
       <c r="F8" s="2" t="s">
         <v>48</v>
@@ -21106,12 +21167,12 @@
       </c>
       <c r="C11" s="91">
         <f>Apartment7!D4</f>
-        <v>1500</v>
+        <v>1800</v>
       </c>
       <c r="D11" s="92"/>
       <c r="E11" s="94">
         <f t="shared" si="0"/>
-        <v>-1500</v>
+        <v>-1800</v>
       </c>
       <c r="F11" s="2" t="s">
         <v>48</v>

--- a/Book2026.xlsx
+++ b/Book2026.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\syana05012019\2024\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4BDB350D-BD9E-45A9-9584-C0283487C207}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2DA2723E-47B9-4457-9141-796FF25B6164}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" tabRatio="947" firstSheet="13" activeTab="21" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" tabRatio="947" firstSheet="13" activeTab="20" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="monthly_elctricity" sheetId="28" r:id="rId1"/>
@@ -47,7 +47,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="830" uniqueCount="290">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="830" uniqueCount="291">
   <si>
     <t>صفحة الإيرادات</t>
   </si>
@@ -917,6 +917,9 @@
   </si>
   <si>
     <t>تحت حساب فوائد شهادة  رقم 1807951149146700023 بتاريخ اصدار 21- ديسمبر - 2025 بفائدة 14%، عن شهر مايو / 2026</t>
+  </si>
+  <si>
+    <t>تحت حساب صيانة شهر يونيه / 2026</t>
   </si>
 </sst>
 </file>
@@ -12676,7 +12679,7 @@
         <v>2</v>
       </c>
       <c r="G54" s="8" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
     </row>
     <row r="55" spans="1:11" ht="18" x14ac:dyDescent="0.25">

--- a/Book2026.xlsx
+++ b/Book2026.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\syana05012019\2024\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2DA2723E-47B9-4457-9141-796FF25B6164}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{68D4413E-C756-401D-B86D-B6B1349F338E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" tabRatio="947" firstSheet="13" activeTab="20" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" tabRatio="947" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="monthly_elctricity" sheetId="28" r:id="rId1"/>
@@ -47,7 +47,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="830" uniqueCount="291">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="832" uniqueCount="291">
   <si>
     <t>صفحة الإيرادات</t>
   </si>
@@ -9452,12 +9452,12 @@
       <c r="C4" s="76"/>
       <c r="D4" s="11">
         <f>SUM(D6:D2001)</f>
-        <v>450</v>
+        <v>525</v>
       </c>
       <c r="E4" s="11"/>
       <c r="F4" s="83">
         <f>SUM(F6:F2001)</f>
-        <v>900</v>
+        <v>1425</v>
       </c>
     </row>
     <row r="5" spans="1:17" ht="36" x14ac:dyDescent="0.2">
@@ -9635,11 +9635,11 @@
         <v>46176</v>
       </c>
       <c r="D11" s="8">
-        <v>75</v>
+        <v>150</v>
       </c>
       <c r="E11" s="8"/>
       <c r="F11" s="33">
-        <v>75</v>
+        <v>150</v>
       </c>
       <c r="G11" s="8" t="s">
         <v>227</v>
@@ -9664,7 +9664,7 @@
       <c r="D12" s="8"/>
       <c r="E12" s="8"/>
       <c r="F12" s="33">
-        <v>75</v>
+        <v>150</v>
       </c>
       <c r="G12" s="8" t="s">
         <v>231</v>
@@ -9689,7 +9689,7 @@
       <c r="D13" s="8"/>
       <c r="E13" s="8"/>
       <c r="F13" s="33">
-        <v>75</v>
+        <v>150</v>
       </c>
       <c r="G13" s="8" t="s">
         <v>232</v>
@@ -9714,7 +9714,7 @@
       <c r="D14" s="8"/>
       <c r="E14" s="8"/>
       <c r="F14" s="33">
-        <v>75</v>
+        <v>150</v>
       </c>
       <c r="G14" s="8" t="s">
         <v>233</v>
@@ -9739,7 +9739,7 @@
       <c r="D15" s="8"/>
       <c r="E15" s="8"/>
       <c r="F15" s="33">
-        <v>75</v>
+        <v>150</v>
       </c>
       <c r="G15" s="8" t="s">
         <v>234</v>
@@ -9764,7 +9764,7 @@
       <c r="D16" s="8"/>
       <c r="E16" s="8"/>
       <c r="F16" s="33">
-        <v>75</v>
+        <v>150</v>
       </c>
       <c r="G16" s="8" t="s">
         <v>235</v>
@@ -9789,7 +9789,7 @@
       <c r="D17" s="8"/>
       <c r="E17" s="8"/>
       <c r="F17" s="33">
-        <v>75</v>
+        <v>150</v>
       </c>
       <c r="G17" s="8" t="s">
         <v>221</v>
@@ -11472,7 +11472,7 @@
       </c>
       <c r="C4" s="53">
         <f>SUM(C6:C2000)</f>
-        <v>12286</v>
+        <v>12611</v>
       </c>
     </row>
     <row r="5" spans="1:17" ht="18" x14ac:dyDescent="0.2">
@@ -12670,7 +12670,7 @@
         <v>46176</v>
       </c>
       <c r="C54" s="55">
-        <v>75</v>
+        <v>150</v>
       </c>
       <c r="E54" s="8" t="s">
         <v>160</v>
@@ -12705,12 +12705,22 @@
       <c r="A56" s="8">
         <v>51</v>
       </c>
-      <c r="B56" s="51"/>
-      <c r="C56" s="55"/>
+      <c r="B56" s="51">
+        <v>46185</v>
+      </c>
+      <c r="C56" s="55">
+        <v>250</v>
+      </c>
       <c r="D56" s="8"/>
-      <c r="E56" s="8"/>
-      <c r="F56" s="8"/>
-      <c r="G56" s="8"/>
+      <c r="E56" s="8" t="s">
+        <v>142</v>
+      </c>
+      <c r="F56" s="8">
+        <v>12</v>
+      </c>
+      <c r="G56" s="8" t="s">
+        <v>281</v>
+      </c>
     </row>
     <row r="57" spans="1:11" ht="18" x14ac:dyDescent="0.25">
       <c r="A57" s="8">
@@ -13177,7 +13187,7 @@
       <c r="B5" s="9"/>
       <c r="C5" s="70">
         <f>incomes!C4</f>
-        <v>12286</v>
+        <v>12611</v>
       </c>
       <c r="D5" s="71">
         <f>outcomes!C3</f>
@@ -13185,7 +13195,7 @@
       </c>
       <c r="E5" s="72">
         <f>(C3+C5)-D5</f>
-        <v>11021</v>
+        <v>11346</v>
       </c>
       <c r="F5" s="2"/>
       <c r="G5" s="2"/>
@@ -20278,7 +20288,7 @@
       </c>
       <c r="D11" s="26">
         <f>Apartment2!D11</f>
-        <v>75</v>
+        <v>150</v>
       </c>
       <c r="E11" s="26">
         <f>Apartment3!D11</f>
@@ -20318,7 +20328,7 @@
       </c>
       <c r="N11" s="26">
         <f>Apartment12!D11</f>
-        <v>0</v>
+        <v>250</v>
       </c>
       <c r="O11" s="26">
         <f>Apartment13!D11</f>
@@ -21036,12 +21046,12 @@
       </c>
       <c r="C6" s="91">
         <f>Apartment2!D4</f>
-        <v>450</v>
+        <v>525</v>
       </c>
       <c r="D6" s="92"/>
       <c r="E6" s="94">
         <f t="shared" ref="E6:E18" si="0">D6-C6</f>
-        <v>-450</v>
+        <v>-525</v>
       </c>
       <c r="F6" s="2" t="s">
         <v>51</v>
@@ -22290,7 +22300,7 @@
       <c r="C4" s="76"/>
       <c r="D4" s="83">
         <f>SUM(D6:D2001)</f>
-        <v>1250</v>
+        <v>1500</v>
       </c>
       <c r="E4" s="11"/>
       <c r="F4" s="83">
@@ -22469,8 +22479,12 @@
       <c r="B11" s="73">
         <v>6</v>
       </c>
-      <c r="C11" s="77"/>
-      <c r="D11" s="33"/>
+      <c r="C11" s="77">
+        <v>46186</v>
+      </c>
+      <c r="D11" s="33">
+        <v>250</v>
+      </c>
       <c r="E11" s="8"/>
       <c r="F11" s="33">
         <v>250</v>

--- a/Book2026.xlsx
+++ b/Book2026.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\syana05012019\2024\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{68D4413E-C756-401D-B86D-B6B1349F338E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7C33281B-E2D3-4953-B6A5-AEAA6475DF62}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" tabRatio="947" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" tabRatio="947" firstSheet="12" activeTab="12" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="monthly_elctricity" sheetId="28" r:id="rId1"/>
@@ -47,7 +47,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="832" uniqueCount="291">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="836" uniqueCount="292">
   <si>
     <t>صفحة الإيرادات</t>
   </si>
@@ -920,6 +920,9 @@
   </si>
   <si>
     <t>تحت حساب صيانة شهر يونيه / 2026</t>
+  </si>
+  <si>
+    <t>تحت حساب كهرباء شهر يونيه /2026</t>
   </si>
 </sst>
 </file>
@@ -5441,7 +5444,7 @@
       <c r="C4" s="76"/>
       <c r="D4" s="83">
         <f>SUM(D6:D2001)</f>
-        <v>1500</v>
+        <v>1800</v>
       </c>
       <c r="E4" s="11"/>
       <c r="F4" s="83">
@@ -5621,9 +5624,11 @@
         <v>6</v>
       </c>
       <c r="C11" s="77">
-        <v>46232</v>
-      </c>
-      <c r="D11" s="33"/>
+        <v>46190</v>
+      </c>
+      <c r="D11" s="33">
+        <v>300</v>
+      </c>
       <c r="E11" s="8"/>
       <c r="F11" s="33">
         <v>300</v>
@@ -11472,7 +11477,7 @@
       </c>
       <c r="C4" s="53">
         <f>SUM(C6:C2000)</f>
-        <v>12611</v>
+        <v>12911</v>
       </c>
     </row>
     <row r="5" spans="1:17" ht="18" x14ac:dyDescent="0.2">
@@ -12726,12 +12731,22 @@
       <c r="A57" s="8">
         <v>52</v>
       </c>
-      <c r="B57" s="51"/>
-      <c r="C57" s="55"/>
+      <c r="B57" s="51">
+        <v>46190</v>
+      </c>
+      <c r="C57" s="55">
+        <v>300</v>
+      </c>
       <c r="D57" s="8"/>
-      <c r="E57" s="8"/>
-      <c r="F57" s="8"/>
-      <c r="G57" s="8"/>
+      <c r="E57" s="8" t="s">
+        <v>249</v>
+      </c>
+      <c r="F57" s="8">
+        <v>8</v>
+      </c>
+      <c r="G57" s="8" t="s">
+        <v>288</v>
+      </c>
       <c r="H57" s="2"/>
       <c r="I57" s="2"/>
       <c r="J57" s="2"/>
@@ -13187,15 +13202,15 @@
       <c r="B5" s="9"/>
       <c r="C5" s="70">
         <f>incomes!C4</f>
-        <v>12611</v>
+        <v>12911</v>
       </c>
       <c r="D5" s="71">
         <f>outcomes!C3</f>
-        <v>15167</v>
+        <v>15410</v>
       </c>
       <c r="E5" s="72">
         <f>(C3+C5)-D5</f>
-        <v>11346</v>
+        <v>11403</v>
       </c>
       <c r="F5" s="2"/>
       <c r="G5" s="2"/>
@@ -13582,7 +13597,7 @@
       </c>
       <c r="C3" s="53">
         <f>SUM(C5:C2002)</f>
-        <v>15167</v>
+        <v>15410</v>
       </c>
     </row>
     <row r="4" spans="1:19" ht="36" x14ac:dyDescent="0.2">
@@ -14191,9 +14206,15 @@
       <c r="A33" s="33">
         <v>29</v>
       </c>
-      <c r="B33" s="60"/>
-      <c r="C33" s="55"/>
-      <c r="D33" s="8"/>
+      <c r="B33" s="60">
+        <v>46189</v>
+      </c>
+      <c r="C33" s="55">
+        <v>238</v>
+      </c>
+      <c r="D33" s="8" t="s">
+        <v>291</v>
+      </c>
       <c r="E33" s="2"/>
       <c r="F33" s="2"/>
       <c r="G33" s="2"/>
@@ -14208,9 +14229,15 @@
       <c r="A34" s="33">
         <v>30</v>
       </c>
-      <c r="B34" s="60"/>
-      <c r="C34" s="55"/>
-      <c r="D34" s="8"/>
+      <c r="B34" s="60">
+        <v>46189</v>
+      </c>
+      <c r="C34" s="55">
+        <v>5</v>
+      </c>
+      <c r="D34" s="8" t="s">
+        <v>275</v>
+      </c>
       <c r="E34" s="2"/>
       <c r="F34" s="2"/>
       <c r="G34" s="2"/>
@@ -20312,7 +20339,7 @@
       </c>
       <c r="J11" s="26">
         <f>Apartment8!D11</f>
-        <v>0</v>
+        <v>300</v>
       </c>
       <c r="K11" s="26">
         <f>Apartment9!D11</f>
@@ -21207,12 +21234,12 @@
       </c>
       <c r="C12" s="91">
         <f>Apartment8!D4</f>
-        <v>1500</v>
+        <v>1800</v>
       </c>
       <c r="D12" s="92"/>
       <c r="E12" s="94">
         <f t="shared" si="0"/>
-        <v>-1500</v>
+        <v>-1800</v>
       </c>
       <c r="F12" s="2" t="s">
         <v>120</v>

--- a/Book2026.xlsx
+++ b/Book2026.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\syana05012019\2024\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7C33281B-E2D3-4953-B6A5-AEAA6475DF62}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{85D19D87-6828-4C3D-A6D8-79FFCC8DBD1D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" tabRatio="947" firstSheet="12" activeTab="12" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" tabRatio="947" firstSheet="12" activeTab="22" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="monthly_elctricity" sheetId="28" r:id="rId1"/>
@@ -47,7 +47,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="836" uniqueCount="292">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="838" uniqueCount="294">
   <si>
     <t>صفحة الإيرادات</t>
   </si>
@@ -923,6 +923,12 @@
   </si>
   <si>
     <t>تحت حساب كهرباء شهر يونيه /2026</t>
+  </si>
+  <si>
+    <t>تحت حساب فاتورة المياه عن شهر يونيه /2026</t>
+  </si>
+  <si>
+    <t>تحت حساب نظافة السلم لام احمد عن شهر يونيه /2026</t>
   </si>
 </sst>
 </file>
@@ -13206,11 +13212,11 @@
       </c>
       <c r="D5" s="71">
         <f>outcomes!C3</f>
-        <v>15410</v>
+        <v>16840</v>
       </c>
       <c r="E5" s="72">
         <f>(C3+C5)-D5</f>
-        <v>11403</v>
+        <v>9973</v>
       </c>
       <c r="F5" s="2"/>
       <c r="G5" s="2"/>
@@ -13597,7 +13603,7 @@
       </c>
       <c r="C3" s="53">
         <f>SUM(C5:C2002)</f>
-        <v>15410</v>
+        <v>16840</v>
       </c>
     </row>
     <row r="4" spans="1:19" ht="36" x14ac:dyDescent="0.2">
@@ -14249,17 +14255,29 @@
       <c r="A35" s="33">
         <v>31</v>
       </c>
-      <c r="B35" s="60"/>
-      <c r="C35" s="55"/>
-      <c r="D35" s="8"/>
+      <c r="B35" s="60">
+        <v>46197</v>
+      </c>
+      <c r="C35" s="55">
+        <v>1030</v>
+      </c>
+      <c r="D35" s="8" t="s">
+        <v>292</v>
+      </c>
     </row>
     <row r="36" spans="1:20" ht="18" x14ac:dyDescent="0.25">
       <c r="A36" s="33">
         <v>32</v>
       </c>
-      <c r="B36" s="60"/>
-      <c r="C36" s="55"/>
-      <c r="D36" s="8"/>
+      <c r="B36" s="60">
+        <v>46197</v>
+      </c>
+      <c r="C36" s="55">
+        <v>400</v>
+      </c>
+      <c r="D36" s="8" t="s">
+        <v>293</v>
+      </c>
     </row>
     <row r="37" spans="1:20" ht="18" x14ac:dyDescent="0.25">
       <c r="A37" s="33">

--- a/Book2026.xlsx
+++ b/Book2026.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\syana05012019\2024\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{85D19D87-6828-4C3D-A6D8-79FFCC8DBD1D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9604CB0F-86E2-4AC7-BA77-63FDDEC94F7B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" tabRatio="947" firstSheet="12" activeTab="22" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" tabRatio="947" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="monthly_elctricity" sheetId="28" r:id="rId1"/>
@@ -47,7 +47,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="838" uniqueCount="294">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="848" uniqueCount="297">
   <si>
     <t>صفحة الإيرادات</t>
   </si>
@@ -929,6 +929,15 @@
   </si>
   <si>
     <t>تحت حساب نظافة السلم لام احمد عن شهر يونيه /2026</t>
+  </si>
+  <si>
+    <t>تحت حساب فوائد شهادة  رقم 1807951149146700023 بتاريخ اصدار 21- ديسمبر - 2025 بفائدة 14%، عن شهر يونيه / 2026</t>
+  </si>
+  <si>
+    <t>تحت حساب صيانة شهر يوليه /2026</t>
+  </si>
+  <si>
+    <t>تحت حساب صيانة شهر يوليه / 2026</t>
   </si>
 </sst>
 </file>
@@ -6120,7 +6129,7 @@
       <c r="C4" s="49"/>
       <c r="D4" s="83">
         <f>SUM(D6:D2001)</f>
-        <v>1800</v>
+        <v>2100</v>
       </c>
       <c r="E4" s="11"/>
       <c r="F4" s="83">
@@ -6329,7 +6338,9 @@
       <c r="C12" s="51">
         <v>45474</v>
       </c>
-      <c r="D12" s="33"/>
+      <c r="D12" s="33">
+        <v>300</v>
+      </c>
       <c r="E12" s="8"/>
       <c r="F12" s="33">
         <v>300</v>
@@ -8121,7 +8132,7 @@
       <c r="C4" s="10"/>
       <c r="D4" s="11">
         <f>SUM(D6:D2001)</f>
-        <v>900</v>
+        <v>1050</v>
       </c>
       <c r="E4" s="11"/>
       <c r="F4" s="11">
@@ -8330,7 +8341,9 @@
       <c r="C12" s="9">
         <v>45474</v>
       </c>
-      <c r="D12" s="8"/>
+      <c r="D12" s="8">
+        <v>150</v>
+      </c>
       <c r="E12" s="8"/>
       <c r="F12" s="8">
         <v>150</v>
@@ -8792,7 +8805,7 @@
       <c r="C4" s="62"/>
       <c r="D4" s="11">
         <f>SUM(D6:D2001)</f>
-        <v>900</v>
+        <v>1050</v>
       </c>
       <c r="E4" s="11"/>
       <c r="F4" s="11">
@@ -9001,7 +9014,9 @@
       <c r="C12" s="63">
         <v>45474</v>
       </c>
-      <c r="D12" s="8"/>
+      <c r="D12" s="8">
+        <v>150</v>
+      </c>
       <c r="E12" s="8"/>
       <c r="F12" s="8">
         <v>150</v>
@@ -9463,7 +9478,7 @@
       <c r="C4" s="76"/>
       <c r="D4" s="11">
         <f>SUM(D6:D2001)</f>
-        <v>525</v>
+        <v>675</v>
       </c>
       <c r="E4" s="11"/>
       <c r="F4" s="83">
@@ -9672,7 +9687,9 @@
       <c r="C12" s="77">
         <v>46266</v>
       </c>
-      <c r="D12" s="8"/>
+      <c r="D12" s="8">
+        <v>150</v>
+      </c>
       <c r="E12" s="8"/>
       <c r="F12" s="33">
         <v>150</v>
@@ -11483,7 +11500,7 @@
       </c>
       <c r="C4" s="53">
         <f>SUM(C6:C2000)</f>
-        <v>12911</v>
+        <v>13719</v>
       </c>
     </row>
     <row r="5" spans="1:17" ht="18" x14ac:dyDescent="0.2">
@@ -12762,54 +12779,102 @@
       <c r="A58" s="8">
         <v>53</v>
       </c>
-      <c r="B58" s="51"/>
-      <c r="C58" s="55"/>
-      <c r="E58" s="8"/>
+      <c r="B58" s="51">
+        <v>46195</v>
+      </c>
+      <c r="C58" s="55">
+        <v>58</v>
+      </c>
+      <c r="D58" s="8"/>
+      <c r="E58" s="8" t="s">
+        <v>260</v>
+      </c>
       <c r="F58" s="8"/>
-      <c r="G58" s="8"/>
+      <c r="G58" s="8" t="s">
+        <v>294</v>
+      </c>
     </row>
     <row r="59" spans="1:11" ht="18" x14ac:dyDescent="0.25">
       <c r="A59" s="8">
         <v>54</v>
       </c>
-      <c r="B59" s="51"/>
-      <c r="C59" s="55"/>
-      <c r="D59" s="8"/>
-      <c r="E59" s="8"/>
-      <c r="F59" s="8"/>
-      <c r="G59" s="8"/>
+      <c r="B59" s="51">
+        <v>46204</v>
+      </c>
+      <c r="C59" s="55">
+        <v>300</v>
+      </c>
+      <c r="E59" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="F59" s="8">
+        <v>7</v>
+      </c>
+      <c r="G59" s="8" t="s">
+        <v>295</v>
+      </c>
     </row>
     <row r="60" spans="1:11" ht="18" x14ac:dyDescent="0.25">
       <c r="A60" s="8">
         <v>55</v>
       </c>
-      <c r="B60" s="51"/>
-      <c r="C60" s="55"/>
+      <c r="B60" s="51">
+        <v>46204</v>
+      </c>
+      <c r="C60" s="55">
+        <v>150</v>
+      </c>
       <c r="D60" s="8"/>
-      <c r="E60" s="8"/>
-      <c r="F60" s="8"/>
-      <c r="G60" s="8"/>
+      <c r="E60" s="8" t="s">
+        <v>244</v>
+      </c>
+      <c r="F60" s="8">
+        <v>4</v>
+      </c>
+      <c r="G60" s="8" t="s">
+        <v>295</v>
+      </c>
     </row>
     <row r="61" spans="1:11" ht="18" x14ac:dyDescent="0.25">
       <c r="A61" s="8">
         <v>56</v>
       </c>
-      <c r="B61" s="51"/>
-      <c r="C61" s="55"/>
+      <c r="B61" s="51">
+        <v>46204</v>
+      </c>
+      <c r="C61" s="55">
+        <v>150</v>
+      </c>
       <c r="D61" s="8"/>
-      <c r="E61" s="8"/>
-      <c r="F61" s="8"/>
-      <c r="G61" s="8"/>
+      <c r="E61" s="8" t="s">
+        <v>141</v>
+      </c>
+      <c r="F61" s="8">
+        <v>3</v>
+      </c>
+      <c r="G61" s="8" t="s">
+        <v>295</v>
+      </c>
     </row>
     <row r="62" spans="1:11" ht="18" x14ac:dyDescent="0.25">
       <c r="A62" s="8">
         <v>57</v>
       </c>
-      <c r="B62" s="51"/>
-      <c r="C62" s="55"/>
-      <c r="E62" s="8"/>
-      <c r="F62" s="8"/>
-      <c r="G62" s="8"/>
+      <c r="B62" s="51">
+        <v>46204</v>
+      </c>
+      <c r="C62" s="55">
+        <v>150</v>
+      </c>
+      <c r="E62" s="8" t="s">
+        <v>160</v>
+      </c>
+      <c r="F62" s="8">
+        <v>2</v>
+      </c>
+      <c r="G62" s="8" t="s">
+        <v>296</v>
+      </c>
     </row>
     <row r="63" spans="1:11" ht="18" x14ac:dyDescent="0.25">
       <c r="A63" s="8">
@@ -13208,7 +13273,7 @@
       <c r="B5" s="9"/>
       <c r="C5" s="70">
         <f>incomes!C4</f>
-        <v>12911</v>
+        <v>13719</v>
       </c>
       <c r="D5" s="71">
         <f>outcomes!C3</f>
@@ -13216,7 +13281,7 @@
       </c>
       <c r="E5" s="72">
         <f>(C3+C5)-D5</f>
-        <v>9973</v>
+        <v>10781</v>
       </c>
       <c r="F5" s="2"/>
       <c r="G5" s="2"/>
@@ -20395,15 +20460,15 @@
       </c>
       <c r="D12" s="26">
         <f>Apartment2!D12</f>
-        <v>0</v>
+        <v>150</v>
       </c>
       <c r="E12" s="26">
         <f>Apartment3!D12</f>
-        <v>0</v>
+        <v>150</v>
       </c>
       <c r="F12" s="26">
         <f>Apartment4!D12</f>
-        <v>0</v>
+        <v>150</v>
       </c>
       <c r="G12" s="26">
         <f>Apartment5!D12</f>
@@ -20415,7 +20480,7 @@
       </c>
       <c r="I12" s="26">
         <f>Apartment7!D12</f>
-        <v>0</v>
+        <v>300</v>
       </c>
       <c r="J12" s="26">
         <f>Apartment8!D12</f>
@@ -21091,12 +21156,12 @@
       </c>
       <c r="C6" s="91">
         <f>Apartment2!D4</f>
-        <v>525</v>
+        <v>675</v>
       </c>
       <c r="D6" s="92"/>
       <c r="E6" s="94">
         <f t="shared" ref="E6:E18" si="0">D6-C6</f>
-        <v>-525</v>
+        <v>-675</v>
       </c>
       <c r="F6" s="2" t="s">
         <v>51</v>
@@ -21118,12 +21183,12 @@
       </c>
       <c r="C7" s="91">
         <f>Apartment3!D4</f>
-        <v>900</v>
+        <v>1050</v>
       </c>
       <c r="D7" s="92"/>
       <c r="E7" s="94">
         <f t="shared" si="0"/>
-        <v>-900</v>
+        <v>-1050</v>
       </c>
       <c r="F7" s="2" t="s">
         <v>48</v>
@@ -21145,12 +21210,12 @@
       </c>
       <c r="C8" s="91">
         <f>Apartment4!D4</f>
-        <v>900</v>
+        <v>1050</v>
       </c>
       <c r="D8" s="92"/>
       <c r="E8" s="94">
         <f t="shared" si="0"/>
-        <v>-900</v>
+        <v>-1050</v>
       </c>
       <c r="F8" s="2" t="s">
         <v>48</v>
@@ -21225,12 +21290,12 @@
       </c>
       <c r="C11" s="91">
         <f>Apartment7!D4</f>
-        <v>1800</v>
+        <v>2100</v>
       </c>
       <c r="D11" s="92"/>
       <c r="E11" s="94">
         <f t="shared" si="0"/>
-        <v>-1800</v>
+        <v>-2100</v>
       </c>
       <c r="F11" s="2" t="s">
         <v>48</v>

--- a/Book2026.xlsx
+++ b/Book2026.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\syana05012019\2024\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9604CB0F-86E2-4AC7-BA77-63FDDEC94F7B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B3DF47CA-A068-495B-A015-2447C0F0CDFB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" tabRatio="947" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" tabRatio="947" firstSheet="13" activeTab="21" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="monthly_elctricity" sheetId="28" r:id="rId1"/>
@@ -47,7 +47,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="848" uniqueCount="297">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="851" uniqueCount="298">
   <si>
     <t>صفحة الإيرادات</t>
   </si>
@@ -938,6 +938,9 @@
   </si>
   <si>
     <t>تحت حساب صيانة شهر يوليه / 2026</t>
+  </si>
+  <si>
+    <t>تحت حساب نظافة امام العمارة</t>
   </si>
 </sst>
 </file>
@@ -1508,14 +1511,14 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" readingOrder="2"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" readingOrder="2"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -4656,16 +4659,16 @@
       <c r="L3" s="1"/>
       <c r="M3" s="1"/>
       <c r="N3" s="1"/>
-      <c r="O3" s="99" t="s">
+      <c r="O3" s="100" t="s">
         <v>97</v>
       </c>
-      <c r="P3" s="99"/>
-      <c r="Q3" s="99"/>
-      <c r="R3" s="99"/>
-      <c r="S3" s="99"/>
-      <c r="T3" s="99"/>
-      <c r="U3" s="99"/>
-      <c r="V3" s="99"/>
+      <c r="P3" s="100"/>
+      <c r="Q3" s="100"/>
+      <c r="R3" s="100"/>
+      <c r="S3" s="100"/>
+      <c r="T3" s="100"/>
+      <c r="U3" s="100"/>
+      <c r="V3" s="100"/>
     </row>
     <row r="4" spans="1:22" ht="18" x14ac:dyDescent="0.25">
       <c r="C4" s="49"/>
@@ -10108,38 +10111,38 @@
   <sheetData>
     <row r="1" spans="1:17" ht="8.25" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="2" spans="1:17" ht="59.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="C2" s="99" t="s">
+      <c r="C2" s="100" t="s">
         <v>212</v>
       </c>
-      <c r="D2" s="99"/>
-      <c r="E2" s="99"/>
-      <c r="F2" s="99"/>
-      <c r="G2" s="99"/>
-      <c r="H2" s="99"/>
-      <c r="I2" s="99"/>
-      <c r="J2" s="99"/>
-      <c r="K2" s="99"/>
-      <c r="L2" s="99"/>
-      <c r="M2" s="99"/>
-      <c r="N2" s="99"/>
+      <c r="D2" s="100"/>
+      <c r="E2" s="100"/>
+      <c r="F2" s="100"/>
+      <c r="G2" s="100"/>
+      <c r="H2" s="100"/>
+      <c r="I2" s="100"/>
+      <c r="J2" s="100"/>
+      <c r="K2" s="100"/>
+      <c r="L2" s="100"/>
+      <c r="M2" s="100"/>
+      <c r="N2" s="100"/>
       <c r="O2" s="19"/>
     </row>
     <row r="3" spans="1:17" ht="20.25" x14ac:dyDescent="0.25">
       <c r="C3" s="83"/>
-      <c r="F3" s="100" t="s">
+      <c r="F3" s="101" t="s">
         <v>236</v>
       </c>
-      <c r="G3" s="100"/>
-      <c r="H3" s="100"/>
-      <c r="I3" s="100"/>
-      <c r="J3" s="100"/>
-      <c r="K3" s="100"/>
-      <c r="L3" s="100"/>
-      <c r="M3" s="100"/>
-      <c r="N3" s="100"/>
-      <c r="O3" s="100"/>
-      <c r="P3" s="100"/>
-      <c r="Q3" s="100"/>
+      <c r="G3" s="101"/>
+      <c r="H3" s="101"/>
+      <c r="I3" s="101"/>
+      <c r="J3" s="101"/>
+      <c r="K3" s="101"/>
+      <c r="L3" s="101"/>
+      <c r="M3" s="101"/>
+      <c r="N3" s="101"/>
+      <c r="O3" s="101"/>
+      <c r="P3" s="101"/>
+      <c r="Q3" s="101"/>
     </row>
     <row r="4" spans="1:17" ht="36" x14ac:dyDescent="0.2">
       <c r="A4" s="12" t="s">
@@ -11500,7 +11503,7 @@
       </c>
       <c r="C4" s="53">
         <f>SUM(C6:C2000)</f>
-        <v>13719</v>
+        <v>13969</v>
       </c>
     </row>
     <row r="5" spans="1:17" ht="18" x14ac:dyDescent="0.2">
@@ -12747,7 +12750,7 @@
         <v>12</v>
       </c>
       <c r="G56" s="8" t="s">
-        <v>281</v>
+        <v>288</v>
       </c>
     </row>
     <row r="57" spans="1:11" ht="18" x14ac:dyDescent="0.25">
@@ -12880,11 +12883,22 @@
       <c r="A63" s="8">
         <v>58</v>
       </c>
-      <c r="B63" s="51"/>
-      <c r="C63" s="55"/>
-      <c r="E63" s="8"/>
-      <c r="F63" s="8"/>
-      <c r="G63" s="8"/>
+      <c r="B63" s="51">
+        <v>46216</v>
+      </c>
+      <c r="C63" s="55">
+        <v>250</v>
+      </c>
+      <c r="D63" s="8"/>
+      <c r="E63" s="8" t="s">
+        <v>142</v>
+      </c>
+      <c r="F63" s="8">
+        <v>12</v>
+      </c>
+      <c r="G63" s="8" t="s">
+        <v>295</v>
+      </c>
     </row>
     <row r="64" spans="1:11" ht="18" x14ac:dyDescent="0.25">
       <c r="A64" s="8">
@@ -13273,15 +13287,15 @@
       <c r="B5" s="9"/>
       <c r="C5" s="70">
         <f>incomes!C4</f>
-        <v>13719</v>
+        <v>13969</v>
       </c>
       <c r="D5" s="71">
         <f>outcomes!C3</f>
-        <v>16840</v>
+        <v>16860</v>
       </c>
       <c r="E5" s="72">
         <f>(C3+C5)-D5</f>
-        <v>10781</v>
+        <v>11011</v>
       </c>
       <c r="F5" s="2"/>
       <c r="G5" s="2"/>
@@ -13668,7 +13682,7 @@
       </c>
       <c r="C3" s="53">
         <f>SUM(C5:C2002)</f>
-        <v>16840</v>
+        <v>16860</v>
       </c>
     </row>
     <row r="4" spans="1:19" ht="36" x14ac:dyDescent="0.2">
@@ -14348,9 +14362,15 @@
       <c r="A37" s="33">
         <v>33</v>
       </c>
-      <c r="B37" s="96"/>
-      <c r="C37" s="55"/>
-      <c r="D37" s="8"/>
+      <c r="B37" s="96">
+        <v>46217</v>
+      </c>
+      <c r="C37" s="55">
+        <v>20</v>
+      </c>
+      <c r="D37" s="8" t="s">
+        <v>297</v>
+      </c>
     </row>
     <row r="38" spans="1:20" ht="18" x14ac:dyDescent="0.25">
       <c r="A38" s="33">
@@ -15097,38 +15117,38 @@
   <sheetData>
     <row r="1" spans="1:17" ht="8.25" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="2" spans="1:17" ht="59.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="C2" s="99" t="s">
+      <c r="C2" s="100" t="s">
         <v>185</v>
       </c>
-      <c r="D2" s="99"/>
-      <c r="E2" s="99"/>
-      <c r="F2" s="99"/>
-      <c r="G2" s="99"/>
-      <c r="H2" s="99"/>
-      <c r="I2" s="99"/>
-      <c r="J2" s="99"/>
-      <c r="K2" s="99"/>
-      <c r="L2" s="99"/>
-      <c r="M2" s="99"/>
-      <c r="N2" s="99"/>
+      <c r="D2" s="100"/>
+      <c r="E2" s="100"/>
+      <c r="F2" s="100"/>
+      <c r="G2" s="100"/>
+      <c r="H2" s="100"/>
+      <c r="I2" s="100"/>
+      <c r="J2" s="100"/>
+      <c r="K2" s="100"/>
+      <c r="L2" s="100"/>
+      <c r="M2" s="100"/>
+      <c r="N2" s="100"/>
       <c r="O2" s="19"/>
     </row>
     <row r="3" spans="1:17" ht="20.25" x14ac:dyDescent="0.25">
       <c r="C3" s="83"/>
-      <c r="F3" s="100" t="s">
+      <c r="F3" s="101" t="s">
         <v>188</v>
       </c>
-      <c r="G3" s="100"/>
-      <c r="H3" s="100"/>
-      <c r="I3" s="100"/>
-      <c r="J3" s="100"/>
-      <c r="K3" s="100"/>
-      <c r="L3" s="100"/>
-      <c r="M3" s="100"/>
-      <c r="N3" s="100"/>
-      <c r="O3" s="100"/>
-      <c r="P3" s="100"/>
-      <c r="Q3" s="100"/>
+      <c r="G3" s="101"/>
+      <c r="H3" s="101"/>
+      <c r="I3" s="101"/>
+      <c r="J3" s="101"/>
+      <c r="K3" s="101"/>
+      <c r="L3" s="101"/>
+      <c r="M3" s="101"/>
+      <c r="N3" s="101"/>
+      <c r="O3" s="101"/>
+      <c r="P3" s="101"/>
+      <c r="Q3" s="101"/>
     </row>
     <row r="4" spans="1:17" ht="36" x14ac:dyDescent="0.2">
       <c r="A4" s="12" t="s">
@@ -19976,21 +19996,21 @@
   <sheetData>
     <row r="1" spans="1:20" ht="26.25" x14ac:dyDescent="0.4">
       <c r="B1" s="18"/>
-      <c r="C1" s="101" t="s">
+      <c r="C1" s="99" t="s">
         <v>140</v>
       </c>
-      <c r="D1" s="101"/>
-      <c r="E1" s="101"/>
-      <c r="F1" s="101"/>
-      <c r="G1" s="101"/>
-      <c r="H1" s="101"/>
-      <c r="I1" s="101"/>
-      <c r="J1" s="101"/>
-      <c r="K1" s="101"/>
-      <c r="L1" s="101"/>
-      <c r="M1" s="101"/>
-      <c r="N1" s="101"/>
-      <c r="O1" s="101"/>
+      <c r="D1" s="99"/>
+      <c r="E1" s="99"/>
+      <c r="F1" s="99"/>
+      <c r="G1" s="99"/>
+      <c r="H1" s="99"/>
+      <c r="I1" s="99"/>
+      <c r="J1" s="99"/>
+      <c r="K1" s="99"/>
+      <c r="L1" s="99"/>
+      <c r="M1" s="99"/>
+      <c r="N1" s="99"/>
+      <c r="O1" s="99"/>
     </row>
     <row r="2" spans="1:20" ht="26.25" x14ac:dyDescent="0.4">
       <c r="B2" s="18"/>
@@ -20500,7 +20520,7 @@
       </c>
       <c r="N12" s="26">
         <f>Apartment12!D12</f>
-        <v>0</v>
+        <v>250</v>
       </c>
       <c r="O12" s="26">
         <f>Apartment13!D12</f>
@@ -22410,7 +22430,7 @@
       <c r="C4" s="76"/>
       <c r="D4" s="83">
         <f>SUM(D6:D2001)</f>
-        <v>1500</v>
+        <v>1750</v>
       </c>
       <c r="E4" s="11"/>
       <c r="F4" s="83">
@@ -22616,8 +22636,12 @@
       <c r="B12" s="73">
         <v>7</v>
       </c>
-      <c r="C12" s="77"/>
-      <c r="D12" s="33"/>
+      <c r="C12" s="77">
+        <v>46216</v>
+      </c>
+      <c r="D12" s="33">
+        <v>250</v>
+      </c>
       <c r="E12" s="8"/>
       <c r="F12" s="33">
         <v>250</v>

--- a/Book2026.xlsx
+++ b/Book2026.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\syana05012019\2024\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B3DF47CA-A068-495B-A015-2447C0F0CDFB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A05F9EEB-DF6A-4B4F-A0BE-99C326645580}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" tabRatio="947" firstSheet="13" activeTab="21" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" tabRatio="947" firstSheet="13" activeTab="22" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="monthly_elctricity" sheetId="28" r:id="rId1"/>
@@ -47,7 +47,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="851" uniqueCount="298">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="852" uniqueCount="299">
   <si>
     <t>صفحة الإيرادات</t>
   </si>
@@ -941,6 +941,9 @@
   </si>
   <si>
     <t>تحت حساب نظافة امام العمارة</t>
+  </si>
+  <si>
+    <t>تحت حساب كهرباء شهر يوليه /2026</t>
   </si>
 </sst>
 </file>
@@ -1511,14 +1514,14 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" readingOrder="2"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" readingOrder="2"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -4659,16 +4662,16 @@
       <c r="L3" s="1"/>
       <c r="M3" s="1"/>
       <c r="N3" s="1"/>
-      <c r="O3" s="100" t="s">
+      <c r="O3" s="99" t="s">
         <v>97</v>
       </c>
-      <c r="P3" s="100"/>
-      <c r="Q3" s="100"/>
-      <c r="R3" s="100"/>
-      <c r="S3" s="100"/>
-      <c r="T3" s="100"/>
-      <c r="U3" s="100"/>
-      <c r="V3" s="100"/>
+      <c r="P3" s="99"/>
+      <c r="Q3" s="99"/>
+      <c r="R3" s="99"/>
+      <c r="S3" s="99"/>
+      <c r="T3" s="99"/>
+      <c r="U3" s="99"/>
+      <c r="V3" s="99"/>
     </row>
     <row r="4" spans="1:22" ht="18" x14ac:dyDescent="0.25">
       <c r="C4" s="49"/>
@@ -10111,38 +10114,38 @@
   <sheetData>
     <row r="1" spans="1:17" ht="8.25" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="2" spans="1:17" ht="59.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="C2" s="100" t="s">
+      <c r="C2" s="99" t="s">
         <v>212</v>
       </c>
-      <c r="D2" s="100"/>
-      <c r="E2" s="100"/>
-      <c r="F2" s="100"/>
-      <c r="G2" s="100"/>
-      <c r="H2" s="100"/>
-      <c r="I2" s="100"/>
-      <c r="J2" s="100"/>
-      <c r="K2" s="100"/>
-      <c r="L2" s="100"/>
-      <c r="M2" s="100"/>
-      <c r="N2" s="100"/>
+      <c r="D2" s="99"/>
+      <c r="E2" s="99"/>
+      <c r="F2" s="99"/>
+      <c r="G2" s="99"/>
+      <c r="H2" s="99"/>
+      <c r="I2" s="99"/>
+      <c r="J2" s="99"/>
+      <c r="K2" s="99"/>
+      <c r="L2" s="99"/>
+      <c r="M2" s="99"/>
+      <c r="N2" s="99"/>
       <c r="O2" s="19"/>
     </row>
     <row r="3" spans="1:17" ht="20.25" x14ac:dyDescent="0.25">
       <c r="C3" s="83"/>
-      <c r="F3" s="101" t="s">
+      <c r="F3" s="100" t="s">
         <v>236</v>
       </c>
-      <c r="G3" s="101"/>
-      <c r="H3" s="101"/>
-      <c r="I3" s="101"/>
-      <c r="J3" s="101"/>
-      <c r="K3" s="101"/>
-      <c r="L3" s="101"/>
-      <c r="M3" s="101"/>
-      <c r="N3" s="101"/>
-      <c r="O3" s="101"/>
-      <c r="P3" s="101"/>
-      <c r="Q3" s="101"/>
+      <c r="G3" s="100"/>
+      <c r="H3" s="100"/>
+      <c r="I3" s="100"/>
+      <c r="J3" s="100"/>
+      <c r="K3" s="100"/>
+      <c r="L3" s="100"/>
+      <c r="M3" s="100"/>
+      <c r="N3" s="100"/>
+      <c r="O3" s="100"/>
+      <c r="P3" s="100"/>
+      <c r="Q3" s="100"/>
     </row>
     <row r="4" spans="1:17" ht="36" x14ac:dyDescent="0.2">
       <c r="A4" s="12" t="s">
@@ -13291,11 +13294,11 @@
       </c>
       <c r="D5" s="71">
         <f>outcomes!C3</f>
-        <v>16860</v>
+        <v>17091</v>
       </c>
       <c r="E5" s="72">
         <f>(C3+C5)-D5</f>
-        <v>11011</v>
+        <v>10780</v>
       </c>
       <c r="F5" s="2"/>
       <c r="G5" s="2"/>
@@ -13682,7 +13685,7 @@
       </c>
       <c r="C3" s="53">
         <f>SUM(C5:C2002)</f>
-        <v>16860</v>
+        <v>17091</v>
       </c>
     </row>
     <row r="4" spans="1:19" ht="36" x14ac:dyDescent="0.2">
@@ -14376,9 +14379,15 @@
       <c r="A38" s="33">
         <v>34</v>
       </c>
-      <c r="B38" s="60"/>
-      <c r="C38" s="55"/>
-      <c r="D38" s="8"/>
+      <c r="B38" s="60">
+        <v>46220</v>
+      </c>
+      <c r="C38" s="55">
+        <v>231</v>
+      </c>
+      <c r="D38" s="8" t="s">
+        <v>298</v>
+      </c>
     </row>
     <row r="39" spans="1:20" ht="18" x14ac:dyDescent="0.25">
       <c r="A39" s="33">
@@ -15117,38 +15126,38 @@
   <sheetData>
     <row r="1" spans="1:17" ht="8.25" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="2" spans="1:17" ht="59.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="C2" s="100" t="s">
+      <c r="C2" s="99" t="s">
         <v>185</v>
       </c>
-      <c r="D2" s="100"/>
-      <c r="E2" s="100"/>
-      <c r="F2" s="100"/>
-      <c r="G2" s="100"/>
-      <c r="H2" s="100"/>
-      <c r="I2" s="100"/>
-      <c r="J2" s="100"/>
-      <c r="K2" s="100"/>
-      <c r="L2" s="100"/>
-      <c r="M2" s="100"/>
-      <c r="N2" s="100"/>
+      <c r="D2" s="99"/>
+      <c r="E2" s="99"/>
+      <c r="F2" s="99"/>
+      <c r="G2" s="99"/>
+      <c r="H2" s="99"/>
+      <c r="I2" s="99"/>
+      <c r="J2" s="99"/>
+      <c r="K2" s="99"/>
+      <c r="L2" s="99"/>
+      <c r="M2" s="99"/>
+      <c r="N2" s="99"/>
       <c r="O2" s="19"/>
     </row>
     <row r="3" spans="1:17" ht="20.25" x14ac:dyDescent="0.25">
       <c r="C3" s="83"/>
-      <c r="F3" s="101" t="s">
+      <c r="F3" s="100" t="s">
         <v>188</v>
       </c>
-      <c r="G3" s="101"/>
-      <c r="H3" s="101"/>
-      <c r="I3" s="101"/>
-      <c r="J3" s="101"/>
-      <c r="K3" s="101"/>
-      <c r="L3" s="101"/>
-      <c r="M3" s="101"/>
-      <c r="N3" s="101"/>
-      <c r="O3" s="101"/>
-      <c r="P3" s="101"/>
-      <c r="Q3" s="101"/>
+      <c r="G3" s="100"/>
+      <c r="H3" s="100"/>
+      <c r="I3" s="100"/>
+      <c r="J3" s="100"/>
+      <c r="K3" s="100"/>
+      <c r="L3" s="100"/>
+      <c r="M3" s="100"/>
+      <c r="N3" s="100"/>
+      <c r="O3" s="100"/>
+      <c r="P3" s="100"/>
+      <c r="Q3" s="100"/>
     </row>
     <row r="4" spans="1:17" ht="36" x14ac:dyDescent="0.2">
       <c r="A4" s="12" t="s">
@@ -19996,21 +20005,21 @@
   <sheetData>
     <row r="1" spans="1:20" ht="26.25" x14ac:dyDescent="0.4">
       <c r="B1" s="18"/>
-      <c r="C1" s="99" t="s">
+      <c r="C1" s="101" t="s">
         <v>140</v>
       </c>
-      <c r="D1" s="99"/>
-      <c r="E1" s="99"/>
-      <c r="F1" s="99"/>
-      <c r="G1" s="99"/>
-      <c r="H1" s="99"/>
-      <c r="I1" s="99"/>
-      <c r="J1" s="99"/>
-      <c r="K1" s="99"/>
-      <c r="L1" s="99"/>
-      <c r="M1" s="99"/>
-      <c r="N1" s="99"/>
-      <c r="O1" s="99"/>
+      <c r="D1" s="101"/>
+      <c r="E1" s="101"/>
+      <c r="F1" s="101"/>
+      <c r="G1" s="101"/>
+      <c r="H1" s="101"/>
+      <c r="I1" s="101"/>
+      <c r="J1" s="101"/>
+      <c r="K1" s="101"/>
+      <c r="L1" s="101"/>
+      <c r="M1" s="101"/>
+      <c r="N1" s="101"/>
+      <c r="O1" s="101"/>
     </row>
     <row r="2" spans="1:20" ht="26.25" x14ac:dyDescent="0.4">
       <c r="B2" s="18"/>

--- a/Book2026.xlsx
+++ b/Book2026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\syana05012019\2024\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A05F9EEB-DF6A-4B4F-A0BE-99C326645580}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{34011929-8091-4F8A-9A2A-450E898F9570}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" tabRatio="947" firstSheet="13" activeTab="22" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -47,7 +47,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="852" uniqueCount="299">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="853" uniqueCount="300">
   <si>
     <t>صفحة الإيرادات</t>
   </si>
@@ -944,6 +944,9 @@
   </si>
   <si>
     <t>تحت حساب كهرباء شهر يوليه /2026</t>
+  </si>
+  <si>
+    <t>تحت حساب فاتورة المياه عن شهر يوليه /2026</t>
   </si>
 </sst>
 </file>
@@ -13294,11 +13297,11 @@
       </c>
       <c r="D5" s="71">
         <f>outcomes!C3</f>
-        <v>17091</v>
+        <v>18121</v>
       </c>
       <c r="E5" s="72">
         <f>(C3+C5)-D5</f>
-        <v>10780</v>
+        <v>9750</v>
       </c>
       <c r="F5" s="2"/>
       <c r="G5" s="2"/>
@@ -13685,7 +13688,7 @@
       </c>
       <c r="C3" s="53">
         <f>SUM(C5:C2002)</f>
-        <v>17091</v>
+        <v>18121</v>
       </c>
     </row>
     <row r="4" spans="1:19" ht="36" x14ac:dyDescent="0.2">
@@ -14393,9 +14396,15 @@
       <c r="A39" s="33">
         <v>35</v>
       </c>
-      <c r="B39" s="60"/>
-      <c r="C39" s="55"/>
-      <c r="D39" s="8"/>
+      <c r="B39" s="60">
+        <v>46225</v>
+      </c>
+      <c r="C39" s="55">
+        <v>1030</v>
+      </c>
+      <c r="D39" s="8" t="s">
+        <v>299</v>
+      </c>
     </row>
     <row r="40" spans="1:20" ht="18" x14ac:dyDescent="0.25">
       <c r="A40" s="33">

--- a/Book2026.xlsx
+++ b/Book2026.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\syana05012019\2024\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{34011929-8091-4F8A-9A2A-450E898F9570}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D4DA84B8-D0D7-4C21-8B3D-2FA50F3837E2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" tabRatio="947" firstSheet="13" activeTab="22" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" tabRatio="947" activeTab="9" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="monthly_elctricity" sheetId="28" r:id="rId1"/>
@@ -47,7 +47,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="853" uniqueCount="300">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="855" uniqueCount="301">
   <si>
     <t>صفحة الإيرادات</t>
   </si>
@@ -947,6 +947,9 @@
   </si>
   <si>
     <t>تحت حساب فاتورة المياه عن شهر يوليه /2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">تحت حساب صيانة شهور ابريل - مايو - يونية - يولية / 2026 </t>
   </si>
 </sst>
 </file>
@@ -3326,7 +3329,7 @@
       <c r="C4" s="10"/>
       <c r="D4" s="89">
         <f>SUM(D6:D2001)</f>
-        <v>450</v>
+        <v>1050</v>
       </c>
       <c r="E4" s="11"/>
       <c r="F4" s="11">
@@ -3452,9 +3455,11 @@
         <v>4</v>
       </c>
       <c r="C9" s="9">
-        <v>46372</v>
-      </c>
-      <c r="D9" s="90"/>
+        <v>46225</v>
+      </c>
+      <c r="D9" s="90">
+        <v>150</v>
+      </c>
       <c r="E9" s="8"/>
       <c r="F9" s="8">
         <v>150</v>
@@ -3477,9 +3482,11 @@
         <v>5</v>
       </c>
       <c r="C10" s="9">
-        <v>46372</v>
-      </c>
-      <c r="D10" s="90"/>
+        <v>46225</v>
+      </c>
+      <c r="D10" s="90">
+        <v>150</v>
+      </c>
       <c r="E10" s="8"/>
       <c r="F10" s="8">
         <v>150</v>
@@ -3502,9 +3509,11 @@
         <v>6</v>
       </c>
       <c r="C11" s="9">
-        <v>46372</v>
-      </c>
-      <c r="D11" s="90"/>
+        <v>46225</v>
+      </c>
+      <c r="D11" s="90">
+        <v>150</v>
+      </c>
       <c r="E11" s="8"/>
       <c r="F11" s="8">
         <v>150</v>
@@ -3527,9 +3536,11 @@
         <v>7</v>
       </c>
       <c r="C12" s="9">
-        <v>46372</v>
-      </c>
-      <c r="D12" s="90"/>
+        <v>46225</v>
+      </c>
+      <c r="D12" s="90">
+        <v>150</v>
+      </c>
       <c r="E12" s="8"/>
       <c r="F12" s="8">
         <v>150</v>
@@ -11509,7 +11520,7 @@
       </c>
       <c r="C4" s="53">
         <f>SUM(C6:C2000)</f>
-        <v>13969</v>
+        <v>14569</v>
       </c>
     </row>
     <row r="5" spans="1:17" ht="18" x14ac:dyDescent="0.2">
@@ -12910,12 +12921,21 @@
       <c r="A64" s="8">
         <v>59</v>
       </c>
-      <c r="B64" s="51"/>
-      <c r="C64" s="55"/>
-      <c r="D64" s="8"/>
-      <c r="E64" s="8"/>
-      <c r="F64" s="8"/>
-      <c r="G64" s="8"/>
+      <c r="B64" s="51">
+        <v>46225</v>
+      </c>
+      <c r="C64" s="55">
+        <v>600</v>
+      </c>
+      <c r="E64" s="8" t="s">
+        <v>187</v>
+      </c>
+      <c r="F64" s="8">
+        <v>11</v>
+      </c>
+      <c r="G64" s="8" t="s">
+        <v>300</v>
+      </c>
     </row>
     <row r="65" spans="1:7" ht="18" x14ac:dyDescent="0.25">
       <c r="A65" s="8">
@@ -13293,7 +13313,7 @@
       <c r="B5" s="9"/>
       <c r="C5" s="70">
         <f>incomes!C4</f>
-        <v>13969</v>
+        <v>14569</v>
       </c>
       <c r="D5" s="71">
         <f>outcomes!C3</f>
@@ -13301,7 +13321,7 @@
       </c>
       <c r="E5" s="72">
         <f>(C3+C5)-D5</f>
-        <v>9750</v>
+        <v>10350</v>
       </c>
       <c r="F5" s="2"/>
       <c r="G5" s="2"/>
@@ -20348,7 +20368,7 @@
       </c>
       <c r="M9" s="26">
         <f>Apartment11!D9</f>
-        <v>0</v>
+        <v>150</v>
       </c>
       <c r="N9" s="26">
         <f>Apartment12!D9</f>
@@ -20410,7 +20430,7 @@
       </c>
       <c r="M10" s="26">
         <f>Apartment11!D10</f>
-        <v>0</v>
+        <v>150</v>
       </c>
       <c r="N10" s="26">
         <f>Apartment12!D10</f>
@@ -20472,7 +20492,7 @@
       </c>
       <c r="M11" s="26">
         <f>Apartment11!D11</f>
-        <v>0</v>
+        <v>150</v>
       </c>
       <c r="N11" s="26">
         <f>Apartment12!D11</f>
@@ -20534,7 +20554,7 @@
       </c>
       <c r="M12" s="26">
         <f>Apartment11!D12</f>
-        <v>0</v>
+        <v>150</v>
       </c>
       <c r="N12" s="26">
         <f>Apartment12!D12</f>
@@ -21433,12 +21453,12 @@
       </c>
       <c r="C15" s="91">
         <f>Apartment11!D4</f>
-        <v>450</v>
+        <v>1050</v>
       </c>
       <c r="D15" s="92"/>
       <c r="E15" s="94">
         <f t="shared" si="0"/>
-        <v>-450</v>
+        <v>-1050</v>
       </c>
       <c r="F15" s="2" t="s">
         <v>54</v>

--- a/Book2026.xlsx
+++ b/Book2026.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\syana05012019\2024\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D4DA84B8-D0D7-4C21-8B3D-2FA50F3837E2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A2A11146-EDAA-47C7-BD3F-0DE89C1A5089}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" tabRatio="947" activeTab="9" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" tabRatio="947" firstSheet="13" activeTab="20" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="monthly_elctricity" sheetId="28" r:id="rId1"/>
@@ -47,7 +47,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="855" uniqueCount="301">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="859" uniqueCount="303">
   <si>
     <t>صفحة الإيرادات</t>
   </si>
@@ -950,6 +950,12 @@
   </si>
   <si>
     <t xml:space="preserve">تحت حساب صيانة شهور ابريل - مايو - يونية - يولية / 2026 </t>
+  </si>
+  <si>
+    <t>تحت حساب فوائد شهادة  رقم 1807951149146700023 بتاريخ اصدار 21- ديسمبر - 2025 بفائدة 14%، عن شهر يولية / 2026</t>
+  </si>
+  <si>
+    <t>تحت حساب فوائد شهادة  رقم 1807581149146700038 بتاريخ اصدار 4- يناير - 2026 بفائدة 19.25%، عن شهر يوليه / 2026</t>
   </si>
 </sst>
 </file>
@@ -11520,7 +11526,7 @@
       </c>
       <c r="C4" s="53">
         <f>SUM(C6:C2000)</f>
-        <v>14569</v>
+        <v>14867</v>
       </c>
     </row>
     <row r="5" spans="1:17" ht="18" x14ac:dyDescent="0.2">
@@ -12941,23 +12947,38 @@
       <c r="A65" s="8">
         <v>60</v>
       </c>
-      <c r="B65" s="51"/>
-      <c r="C65" s="55"/>
+      <c r="B65" s="51">
+        <v>46228</v>
+      </c>
+      <c r="C65" s="55">
+        <v>58</v>
+      </c>
       <c r="D65" s="8"/>
-      <c r="E65" s="8"/>
+      <c r="E65" s="8" t="s">
+        <v>260</v>
+      </c>
       <c r="F65" s="8"/>
-      <c r="G65" s="8"/>
+      <c r="G65" s="8" t="s">
+        <v>301</v>
+      </c>
     </row>
     <row r="66" spans="1:7" ht="18" x14ac:dyDescent="0.25">
       <c r="A66" s="8">
         <v>61</v>
       </c>
-      <c r="B66" s="51"/>
-      <c r="C66" s="55"/>
-      <c r="D66" s="8"/>
-      <c r="E66" s="8"/>
+      <c r="B66" s="51">
+        <v>46228</v>
+      </c>
+      <c r="C66" s="55">
+        <v>240</v>
+      </c>
+      <c r="E66" s="8" t="s">
+        <v>260</v>
+      </c>
       <c r="F66" s="8"/>
-      <c r="G66" s="8"/>
+      <c r="G66" s="8" t="s">
+        <v>302</v>
+      </c>
     </row>
     <row r="67" spans="1:7" ht="18" x14ac:dyDescent="0.25">
       <c r="A67" s="8">
@@ -13313,7 +13334,7 @@
       <c r="B5" s="9"/>
       <c r="C5" s="70">
         <f>incomes!C4</f>
-        <v>14569</v>
+        <v>14867</v>
       </c>
       <c r="D5" s="71">
         <f>outcomes!C3</f>
@@ -13321,7 +13342,7 @@
       </c>
       <c r="E5" s="72">
         <f>(C3+C5)-D5</f>
-        <v>10350</v>
+        <v>10648</v>
       </c>
       <c r="F5" s="2"/>
       <c r="G5" s="2"/>

--- a/Book2026.xlsx
+++ b/Book2026.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\syana05012019\2024\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A2A11146-EDAA-47C7-BD3F-0DE89C1A5089}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{89B006AA-614F-47AE-943F-147BE6E2D702}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" tabRatio="947" firstSheet="13" activeTab="20" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" tabRatio="947" firstSheet="13" activeTab="21" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="monthly_elctricity" sheetId="28" r:id="rId1"/>
@@ -47,7 +47,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="859" uniqueCount="303">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="869" uniqueCount="306">
   <si>
     <t>صفحة الإيرادات</t>
   </si>
@@ -956,6 +956,15 @@
   </si>
   <si>
     <t>تحت حساب فوائد شهادة  رقم 1807581149146700038 بتاريخ اصدار 4- يناير - 2026 بفائدة 19.25%، عن شهر يوليه / 2026</t>
+  </si>
+  <si>
+    <t>تحت حساب نظافة السلم لام احمد عن شهر يولية /2026</t>
+  </si>
+  <si>
+    <t>تحت حساب صيانة شهر يونية ويولية /2026</t>
+  </si>
+  <si>
+    <t>تحت حساب صيانة شهر أغسطس /2026</t>
   </si>
 </sst>
 </file>
@@ -1116,7 +1125,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="8">
+  <fills count="9">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1159,8 +1168,14 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.59999389629810485"/>
+        <bgColor theme="4" tint="0.59999389629810485"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="7">
+  <borders count="8">
     <border>
       <left/>
       <right/>
@@ -1238,11 +1253,26 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color theme="0"/>
+      </left>
+      <right style="thin">
+        <color theme="0"/>
+      </right>
+      <top style="thin">
+        <color theme="0"/>
+      </top>
+      <bottom style="thin">
+        <color theme="0"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="111">
+  <cellXfs count="112">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1561,6 +1591,9 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="1" fillId="8" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" readingOrder="2"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -6155,7 +6188,7 @@
       <c r="C4" s="49"/>
       <c r="D4" s="83">
         <f>SUM(D6:D2001)</f>
-        <v>2100</v>
+        <v>2400</v>
       </c>
       <c r="E4" s="11"/>
       <c r="F4" s="83">
@@ -6389,9 +6422,11 @@
         <v>8</v>
       </c>
       <c r="C13" s="51">
-        <v>46247</v>
-      </c>
-      <c r="D13" s="33"/>
+        <v>46235</v>
+      </c>
+      <c r="D13" s="33">
+        <v>300</v>
+      </c>
       <c r="E13" s="8"/>
       <c r="F13" s="33">
         <v>300</v>
@@ -8158,7 +8193,7 @@
       <c r="C4" s="10"/>
       <c r="D4" s="11">
         <f>SUM(D6:D2001)</f>
-        <v>1050</v>
+        <v>1200</v>
       </c>
       <c r="E4" s="11"/>
       <c r="F4" s="11">
@@ -8392,9 +8427,11 @@
         <v>8</v>
       </c>
       <c r="C13" s="51">
-        <v>46247</v>
-      </c>
-      <c r="D13" s="8"/>
+        <v>46235</v>
+      </c>
+      <c r="D13" s="8">
+        <v>150</v>
+      </c>
       <c r="E13" s="8"/>
       <c r="F13" s="8">
         <v>150</v>
@@ -8831,7 +8868,7 @@
       <c r="C4" s="62"/>
       <c r="D4" s="11">
         <f>SUM(D6:D2001)</f>
-        <v>1050</v>
+        <v>1200</v>
       </c>
       <c r="E4" s="11"/>
       <c r="F4" s="11">
@@ -9065,9 +9102,11 @@
         <v>8</v>
       </c>
       <c r="C13" s="51">
-        <v>46247</v>
-      </c>
-      <c r="D13" s="8"/>
+        <v>46235</v>
+      </c>
+      <c r="D13" s="8">
+        <v>150</v>
+      </c>
       <c r="E13" s="8"/>
       <c r="F13" s="8">
         <v>150</v>
@@ -10818,7 +10857,7 @@
       <c r="C4" s="10"/>
       <c r="D4" s="11">
         <f>SUM(D6:D2001)</f>
-        <v>750</v>
+        <v>1050</v>
       </c>
       <c r="E4" s="11"/>
       <c r="F4" s="11">
@@ -11000,10 +11039,12 @@
       <c r="B11" s="73">
         <v>6</v>
       </c>
-      <c r="C11" s="51">
-        <v>46222</v>
-      </c>
-      <c r="D11" s="73"/>
+      <c r="C11" s="111">
+        <v>46232</v>
+      </c>
+      <c r="D11" s="73">
+        <v>150</v>
+      </c>
       <c r="E11" s="8"/>
       <c r="F11" s="73">
         <v>150</v>
@@ -11025,10 +11066,12 @@
       <c r="B12" s="73">
         <v>7</v>
       </c>
-      <c r="C12" s="51">
-        <v>46222</v>
-      </c>
-      <c r="D12" s="73"/>
+      <c r="C12" s="111">
+        <v>46232</v>
+      </c>
+      <c r="D12" s="73">
+        <v>150</v>
+      </c>
       <c r="E12" s="8"/>
       <c r="F12" s="73">
         <v>150</v>
@@ -11526,7 +11569,7 @@
       </c>
       <c r="C4" s="53">
         <f>SUM(C6:C2000)</f>
-        <v>14867</v>
+        <v>15767</v>
       </c>
     </row>
     <row r="5" spans="1:17" ht="18" x14ac:dyDescent="0.2">
@@ -12984,45 +13027,84 @@
       <c r="A67" s="8">
         <v>62</v>
       </c>
-      <c r="B67" s="51"/>
-      <c r="C67" s="55"/>
+      <c r="B67" s="51">
+        <v>46232</v>
+      </c>
+      <c r="C67" s="55">
+        <v>300</v>
+      </c>
       <c r="D67" s="8"/>
-      <c r="E67" s="8"/>
-      <c r="F67" s="8"/>
-      <c r="G67" s="8"/>
+      <c r="E67" s="8" t="s">
+        <v>186</v>
+      </c>
+      <c r="F67" s="8">
+        <v>1</v>
+      </c>
+      <c r="G67" s="8" t="s">
+        <v>304</v>
+      </c>
     </row>
     <row r="68" spans="1:7" ht="18" x14ac:dyDescent="0.25">
       <c r="A68" s="8">
         <v>63</v>
       </c>
-      <c r="B68" s="51"/>
-      <c r="C68" s="55"/>
-      <c r="D68" s="8"/>
-      <c r="E68" s="8"/>
-      <c r="F68" s="8"/>
-      <c r="G68" s="8"/>
+      <c r="B68" s="51">
+        <v>46235</v>
+      </c>
+      <c r="C68" s="55">
+        <v>300</v>
+      </c>
+      <c r="E68" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="F68" s="8">
+        <v>7</v>
+      </c>
+      <c r="G68" s="8" t="s">
+        <v>305</v>
+      </c>
     </row>
     <row r="69" spans="1:7" ht="18" x14ac:dyDescent="0.25">
       <c r="A69" s="8">
         <v>64</v>
       </c>
-      <c r="B69" s="51"/>
-      <c r="C69" s="55"/>
+      <c r="B69" s="51">
+        <v>46235</v>
+      </c>
+      <c r="C69" s="55">
+        <v>150</v>
+      </c>
       <c r="D69" s="8"/>
-      <c r="E69" s="8"/>
-      <c r="F69" s="8"/>
-      <c r="G69" s="8"/>
+      <c r="E69" s="8" t="s">
+        <v>244</v>
+      </c>
+      <c r="F69" s="8">
+        <v>4</v>
+      </c>
+      <c r="G69" s="8" t="s">
+        <v>305</v>
+      </c>
     </row>
     <row r="70" spans="1:7" ht="18" x14ac:dyDescent="0.25">
       <c r="A70" s="8">
         <v>65</v>
       </c>
-      <c r="B70" s="51"/>
-      <c r="C70" s="55"/>
+      <c r="B70" s="51">
+        <v>46235</v>
+      </c>
+      <c r="C70" s="55">
+        <v>150</v>
+      </c>
       <c r="D70" s="8"/>
-      <c r="E70" s="8"/>
-      <c r="F70" s="8"/>
-      <c r="G70" s="8"/>
+      <c r="E70" s="8" t="s">
+        <v>141</v>
+      </c>
+      <c r="F70" s="8">
+        <v>3</v>
+      </c>
+      <c r="G70" s="8" t="s">
+        <v>305</v>
+      </c>
     </row>
     <row r="71" spans="1:7" ht="18" x14ac:dyDescent="0.25">
       <c r="A71" s="8">
@@ -13334,15 +13416,15 @@
       <c r="B5" s="9"/>
       <c r="C5" s="70">
         <f>incomes!C4</f>
-        <v>14867</v>
+        <v>15767</v>
       </c>
       <c r="D5" s="71">
         <f>outcomes!C3</f>
-        <v>18121</v>
+        <v>18571</v>
       </c>
       <c r="E5" s="72">
         <f>(C3+C5)-D5</f>
-        <v>10648</v>
+        <v>11098</v>
       </c>
       <c r="F5" s="2"/>
       <c r="G5" s="2"/>
@@ -13729,7 +13811,7 @@
       </c>
       <c r="C3" s="53">
         <f>SUM(C5:C2002)</f>
-        <v>18121</v>
+        <v>18571</v>
       </c>
     </row>
     <row r="4" spans="1:19" ht="36" x14ac:dyDescent="0.2">
@@ -14451,18 +14533,30 @@
       <c r="A40" s="33">
         <v>36</v>
       </c>
-      <c r="B40" s="60"/>
-      <c r="C40" s="55"/>
-      <c r="D40" s="8"/>
+      <c r="B40" s="60">
+        <v>46234</v>
+      </c>
+      <c r="C40" s="55">
+        <v>400</v>
+      </c>
+      <c r="D40" s="8" t="s">
+        <v>303</v>
+      </c>
       <c r="E40" s="2"/>
     </row>
     <row r="41" spans="1:20" ht="18" x14ac:dyDescent="0.25">
       <c r="A41" s="33">
         <v>37</v>
       </c>
-      <c r="B41" s="60"/>
-      <c r="C41" s="55"/>
-      <c r="D41" s="8"/>
+      <c r="B41" s="60">
+        <v>46234</v>
+      </c>
+      <c r="C41" s="55">
+        <v>50</v>
+      </c>
+      <c r="D41" s="8" t="s">
+        <v>277</v>
+      </c>
     </row>
     <row r="42" spans="1:20" ht="18" x14ac:dyDescent="0.25">
       <c r="A42" s="33">
@@ -20473,7 +20567,7 @@
       </c>
       <c r="C11" s="26">
         <f>Apartment1!D11</f>
-        <v>0</v>
+        <v>150</v>
       </c>
       <c r="D11" s="26">
         <f>Apartment2!D11</f>
@@ -20535,7 +20629,7 @@
       </c>
       <c r="C12" s="26">
         <f>Apartment1!D12</f>
-        <v>0</v>
+        <v>150</v>
       </c>
       <c r="D12" s="26">
         <f>Apartment2!D12</f>
@@ -20605,11 +20699,11 @@
       </c>
       <c r="E13" s="26">
         <f>Apartment3!D13</f>
-        <v>0</v>
+        <v>150</v>
       </c>
       <c r="F13" s="26">
         <f>Apartment4!D13</f>
-        <v>0</v>
+        <v>150</v>
       </c>
       <c r="G13" s="26">
         <f>Apartment5!D13</f>
@@ -20621,7 +20715,7 @@
       </c>
       <c r="I13" s="26">
         <f>Apartment7!D13</f>
-        <v>0</v>
+        <v>300</v>
       </c>
       <c r="J13" s="26">
         <f>Apartment8!D13</f>
@@ -21208,12 +21302,12 @@
       </c>
       <c r="C5" s="91">
         <f>Apartment1!D4</f>
-        <v>750</v>
+        <v>1050</v>
       </c>
       <c r="D5" s="92"/>
       <c r="E5" s="94">
         <f>D5-C5</f>
-        <v>-750</v>
+        <v>-1050</v>
       </c>
       <c r="F5" s="2" t="s">
         <v>50</v>
@@ -21262,12 +21356,12 @@
       </c>
       <c r="C7" s="91">
         <f>Apartment3!D4</f>
-        <v>1050</v>
+        <v>1200</v>
       </c>
       <c r="D7" s="92"/>
       <c r="E7" s="94">
         <f t="shared" si="0"/>
-        <v>-1050</v>
+        <v>-1200</v>
       </c>
       <c r="F7" s="2" t="s">
         <v>48</v>
@@ -21289,12 +21383,12 @@
       </c>
       <c r="C8" s="91">
         <f>Apartment4!D4</f>
-        <v>1050</v>
+        <v>1200</v>
       </c>
       <c r="D8" s="92"/>
       <c r="E8" s="94">
         <f t="shared" si="0"/>
-        <v>-1050</v>
+        <v>-1200</v>
       </c>
       <c r="F8" s="2" t="s">
         <v>48</v>
@@ -21369,12 +21463,12 @@
       </c>
       <c r="C11" s="91">
         <f>Apartment7!D4</f>
-        <v>2100</v>
+        <v>2400</v>
       </c>
       <c r="D11" s="92"/>
       <c r="E11" s="94">
         <f t="shared" si="0"/>
-        <v>-2100</v>
+        <v>-2400</v>
       </c>
       <c r="F11" s="2" t="s">
         <v>48</v>

--- a/Book2026.xlsx
+++ b/Book2026.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\syana05012019\2024\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{89B006AA-614F-47AE-943F-147BE6E2D702}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{14E5E6B0-8E0A-4E7B-A69D-CA1EA50534BF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" tabRatio="947" firstSheet="13" activeTab="21" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" tabRatio="947" firstSheet="13" activeTab="20" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="monthly_elctricity" sheetId="28" r:id="rId1"/>
@@ -47,7 +47,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="869" uniqueCount="306">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="873" uniqueCount="307">
   <si>
     <t>صفحة الإيرادات</t>
   </si>
@@ -965,6 +965,9 @@
   </si>
   <si>
     <t>تحت حساب صيانة شهر أغسطس /2026</t>
+  </si>
+  <si>
+    <t>تحت حساب فوائد شهادة  رقم 1807951149146700023 بتاريخ اصدار 21- ديسمبر - 2025 بفائدة 14%، عن شهر اغسطس / 2026</t>
   </si>
 </sst>
 </file>
@@ -1553,6 +1556,9 @@
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" readingOrder="2"/>
     </xf>
+    <xf numFmtId="164" fontId="1" fillId="8" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" readingOrder="2"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1591,9 +1597,6 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="1" fillId="8" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" readingOrder="2"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -2620,23 +2623,23 @@
   </cols>
   <sheetData>
     <row r="2" spans="1:17" ht="26.25" x14ac:dyDescent="0.4">
-      <c r="C2" s="98" t="s">
+      <c r="C2" s="99" t="s">
         <v>117</v>
       </c>
-      <c r="D2" s="98"/>
-      <c r="E2" s="98"/>
-      <c r="F2" s="98"/>
-      <c r="G2" s="98"/>
-      <c r="H2" s="98"/>
-      <c r="I2" s="98"/>
-      <c r="J2" s="98"/>
-      <c r="K2" s="98"/>
-      <c r="L2" s="98"/>
-      <c r="M2" s="98"/>
-      <c r="N2" s="98"/>
-      <c r="O2" s="98"/>
-      <c r="P2" s="98"/>
-      <c r="Q2" s="98"/>
+      <c r="D2" s="99"/>
+      <c r="E2" s="99"/>
+      <c r="F2" s="99"/>
+      <c r="G2" s="99"/>
+      <c r="H2" s="99"/>
+      <c r="I2" s="99"/>
+      <c r="J2" s="99"/>
+      <c r="K2" s="99"/>
+      <c r="L2" s="99"/>
+      <c r="M2" s="99"/>
+      <c r="N2" s="99"/>
+      <c r="O2" s="99"/>
+      <c r="P2" s="99"/>
+      <c r="Q2" s="99"/>
     </row>
     <row r="3" spans="1:17" ht="56.25" x14ac:dyDescent="0.4">
       <c r="C3" s="1"/>
@@ -3325,23 +3328,23 @@
   </cols>
   <sheetData>
     <row r="2" spans="1:17" ht="26.25" x14ac:dyDescent="0.4">
-      <c r="C2" s="98" t="s">
+      <c r="C2" s="99" t="s">
         <v>22</v>
       </c>
-      <c r="D2" s="98"/>
-      <c r="E2" s="98"/>
-      <c r="F2" s="98"/>
-      <c r="G2" s="98"/>
-      <c r="H2" s="98"/>
-      <c r="I2" s="98"/>
-      <c r="J2" s="98"/>
-      <c r="K2" s="98"/>
-      <c r="L2" s="98"/>
-      <c r="M2" s="98"/>
-      <c r="N2" s="98"/>
-      <c r="O2" s="98"/>
-      <c r="P2" s="98"/>
-      <c r="Q2" s="98"/>
+      <c r="D2" s="99"/>
+      <c r="E2" s="99"/>
+      <c r="F2" s="99"/>
+      <c r="G2" s="99"/>
+      <c r="H2" s="99"/>
+      <c r="I2" s="99"/>
+      <c r="J2" s="99"/>
+      <c r="K2" s="99"/>
+      <c r="L2" s="99"/>
+      <c r="M2" s="99"/>
+      <c r="N2" s="99"/>
+      <c r="O2" s="99"/>
+      <c r="P2" s="99"/>
+      <c r="Q2" s="99"/>
     </row>
     <row r="3" spans="1:17" ht="56.25" x14ac:dyDescent="0.4">
       <c r="C3" s="1"/>
@@ -3998,23 +4001,23 @@
   </cols>
   <sheetData>
     <row r="2" spans="1:17" ht="26.25" x14ac:dyDescent="0.4">
-      <c r="C2" s="98" t="s">
+      <c r="C2" s="99" t="s">
         <v>23</v>
       </c>
-      <c r="D2" s="98"/>
-      <c r="E2" s="98"/>
-      <c r="F2" s="98"/>
-      <c r="G2" s="98"/>
-      <c r="H2" s="98"/>
-      <c r="I2" s="98"/>
-      <c r="J2" s="98"/>
-      <c r="K2" s="98"/>
-      <c r="L2" s="98"/>
-      <c r="M2" s="98"/>
-      <c r="N2" s="98"/>
-      <c r="O2" s="98"/>
-      <c r="P2" s="98"/>
-      <c r="Q2" s="98"/>
+      <c r="D2" s="99"/>
+      <c r="E2" s="99"/>
+      <c r="F2" s="99"/>
+      <c r="G2" s="99"/>
+      <c r="H2" s="99"/>
+      <c r="I2" s="99"/>
+      <c r="J2" s="99"/>
+      <c r="K2" s="99"/>
+      <c r="L2" s="99"/>
+      <c r="M2" s="99"/>
+      <c r="N2" s="99"/>
+      <c r="O2" s="99"/>
+      <c r="P2" s="99"/>
+      <c r="Q2" s="99"/>
     </row>
     <row r="3" spans="1:17" ht="56.25" x14ac:dyDescent="0.4">
       <c r="C3" s="1"/>
@@ -4680,23 +4683,23 @@
   </cols>
   <sheetData>
     <row r="2" spans="1:22" ht="26.25" x14ac:dyDescent="0.4">
-      <c r="C2" s="98" t="s">
+      <c r="C2" s="99" t="s">
         <v>24</v>
       </c>
-      <c r="D2" s="98"/>
-      <c r="E2" s="98"/>
-      <c r="F2" s="98"/>
-      <c r="G2" s="98"/>
-      <c r="H2" s="98"/>
-      <c r="I2" s="98"/>
-      <c r="J2" s="98"/>
-      <c r="K2" s="98"/>
-      <c r="L2" s="98"/>
-      <c r="M2" s="98"/>
-      <c r="N2" s="98"/>
-      <c r="O2" s="98"/>
-      <c r="P2" s="98"/>
-      <c r="Q2" s="98"/>
+      <c r="D2" s="99"/>
+      <c r="E2" s="99"/>
+      <c r="F2" s="99"/>
+      <c r="G2" s="99"/>
+      <c r="H2" s="99"/>
+      <c r="I2" s="99"/>
+      <c r="J2" s="99"/>
+      <c r="K2" s="99"/>
+      <c r="L2" s="99"/>
+      <c r="M2" s="99"/>
+      <c r="N2" s="99"/>
+      <c r="O2" s="99"/>
+      <c r="P2" s="99"/>
+      <c r="Q2" s="99"/>
     </row>
     <row r="3" spans="1:22" ht="56.25" x14ac:dyDescent="0.4">
       <c r="C3" s="57"/>
@@ -4715,16 +4718,16 @@
       <c r="L3" s="1"/>
       <c r="M3" s="1"/>
       <c r="N3" s="1"/>
-      <c r="O3" s="99" t="s">
+      <c r="O3" s="100" t="s">
         <v>97</v>
       </c>
-      <c r="P3" s="99"/>
-      <c r="Q3" s="99"/>
-      <c r="R3" s="99"/>
-      <c r="S3" s="99"/>
-      <c r="T3" s="99"/>
-      <c r="U3" s="99"/>
-      <c r="V3" s="99"/>
+      <c r="P3" s="100"/>
+      <c r="Q3" s="100"/>
+      <c r="R3" s="100"/>
+      <c r="S3" s="100"/>
+      <c r="T3" s="100"/>
+      <c r="U3" s="100"/>
+      <c r="V3" s="100"/>
     </row>
     <row r="4" spans="1:22" ht="18" x14ac:dyDescent="0.25">
       <c r="C4" s="49"/>
@@ -4774,12 +4777,12 @@
       <c r="Q5" s="12" t="s">
         <v>37</v>
       </c>
-      <c r="R5" s="105" t="s">
+      <c r="R5" s="106" t="s">
         <v>77</v>
       </c>
-      <c r="S5" s="106"/>
-      <c r="T5" s="106"/>
-      <c r="U5" s="107"/>
+      <c r="S5" s="107"/>
+      <c r="T5" s="107"/>
+      <c r="U5" s="108"/>
     </row>
     <row r="6" spans="1:22" ht="18" x14ac:dyDescent="0.25">
       <c r="A6" s="8">
@@ -5016,10 +5019,10 @@
         <f>SUM(Q6:Q11)</f>
         <v>0</v>
       </c>
-      <c r="R12" s="108"/>
-      <c r="S12" s="109"/>
-      <c r="T12" s="109"/>
-      <c r="U12" s="110"/>
+      <c r="R12" s="109"/>
+      <c r="S12" s="110"/>
+      <c r="T12" s="110"/>
+      <c r="U12" s="111"/>
     </row>
     <row r="13" spans="1:22" ht="18" x14ac:dyDescent="0.25">
       <c r="A13" s="8">
@@ -5475,23 +5478,23 @@
   </cols>
   <sheetData>
     <row r="2" spans="1:17" ht="26.25" x14ac:dyDescent="0.4">
-      <c r="C2" s="98" t="s">
+      <c r="C2" s="99" t="s">
         <v>115</v>
       </c>
-      <c r="D2" s="98"/>
-      <c r="E2" s="98"/>
-      <c r="F2" s="98"/>
-      <c r="G2" s="98"/>
-      <c r="H2" s="98"/>
-      <c r="I2" s="98"/>
-      <c r="J2" s="98"/>
-      <c r="K2" s="98"/>
-      <c r="L2" s="98"/>
-      <c r="M2" s="98"/>
-      <c r="N2" s="98"/>
-      <c r="O2" s="98"/>
-      <c r="P2" s="98"/>
-      <c r="Q2" s="98"/>
+      <c r="D2" s="99"/>
+      <c r="E2" s="99"/>
+      <c r="F2" s="99"/>
+      <c r="G2" s="99"/>
+      <c r="H2" s="99"/>
+      <c r="I2" s="99"/>
+      <c r="J2" s="99"/>
+      <c r="K2" s="99"/>
+      <c r="L2" s="99"/>
+      <c r="M2" s="99"/>
+      <c r="N2" s="99"/>
+      <c r="O2" s="99"/>
+      <c r="P2" s="99"/>
+      <c r="Q2" s="99"/>
     </row>
     <row r="3" spans="1:17" ht="56.25" x14ac:dyDescent="0.4">
       <c r="C3" s="75"/>
@@ -6145,23 +6148,23 @@
   </cols>
   <sheetData>
     <row r="2" spans="1:17" ht="26.25" x14ac:dyDescent="0.4">
-      <c r="C2" s="98" t="s">
+      <c r="C2" s="99" t="s">
         <v>25</v>
       </c>
-      <c r="D2" s="98"/>
-      <c r="E2" s="98"/>
-      <c r="F2" s="98"/>
-      <c r="G2" s="98"/>
-      <c r="H2" s="98"/>
-      <c r="I2" s="98"/>
-      <c r="J2" s="98"/>
-      <c r="K2" s="98"/>
-      <c r="L2" s="98"/>
-      <c r="M2" s="98"/>
-      <c r="N2" s="98"/>
-      <c r="O2" s="98"/>
-      <c r="P2" s="98"/>
-      <c r="Q2" s="98"/>
+      <c r="D2" s="99"/>
+      <c r="E2" s="99"/>
+      <c r="F2" s="99"/>
+      <c r="G2" s="99"/>
+      <c r="H2" s="99"/>
+      <c r="I2" s="99"/>
+      <c r="J2" s="99"/>
+      <c r="K2" s="99"/>
+      <c r="L2" s="99"/>
+      <c r="M2" s="99"/>
+      <c r="N2" s="99"/>
+      <c r="O2" s="99"/>
+      <c r="P2" s="99"/>
+      <c r="Q2" s="99"/>
     </row>
     <row r="3" spans="1:17" ht="56.25" x14ac:dyDescent="0.4">
       <c r="C3" s="57"/>
@@ -6819,23 +6822,23 @@
   </cols>
   <sheetData>
     <row r="2" spans="1:17" ht="26.25" x14ac:dyDescent="0.4">
-      <c r="C2" s="98" t="s">
+      <c r="C2" s="99" t="s">
         <v>26</v>
       </c>
-      <c r="D2" s="98"/>
-      <c r="E2" s="98"/>
-      <c r="F2" s="98"/>
-      <c r="G2" s="98"/>
-      <c r="H2" s="98"/>
-      <c r="I2" s="98"/>
-      <c r="J2" s="98"/>
-      <c r="K2" s="98"/>
-      <c r="L2" s="98"/>
-      <c r="M2" s="98"/>
-      <c r="N2" s="98"/>
-      <c r="O2" s="98"/>
-      <c r="P2" s="98"/>
-      <c r="Q2" s="98"/>
+      <c r="D2" s="99"/>
+      <c r="E2" s="99"/>
+      <c r="F2" s="99"/>
+      <c r="G2" s="99"/>
+      <c r="H2" s="99"/>
+      <c r="I2" s="99"/>
+      <c r="J2" s="99"/>
+      <c r="K2" s="99"/>
+      <c r="L2" s="99"/>
+      <c r="M2" s="99"/>
+      <c r="N2" s="99"/>
+      <c r="O2" s="99"/>
+      <c r="P2" s="99"/>
+      <c r="Q2" s="99"/>
     </row>
     <row r="3" spans="1:17" ht="56.25" x14ac:dyDescent="0.4">
       <c r="C3" s="1"/>
@@ -7503,23 +7506,23 @@
   </cols>
   <sheetData>
     <row r="2" spans="1:17" ht="26.25" x14ac:dyDescent="0.4">
-      <c r="C2" s="98" t="s">
+      <c r="C2" s="99" t="s">
         <v>116</v>
       </c>
-      <c r="D2" s="98"/>
-      <c r="E2" s="98"/>
-      <c r="F2" s="98"/>
-      <c r="G2" s="98"/>
-      <c r="H2" s="98"/>
-      <c r="I2" s="98"/>
-      <c r="J2" s="98"/>
-      <c r="K2" s="98"/>
-      <c r="L2" s="98"/>
-      <c r="M2" s="98"/>
-      <c r="N2" s="98"/>
-      <c r="O2" s="98"/>
-      <c r="P2" s="98"/>
-      <c r="Q2" s="98"/>
+      <c r="D2" s="99"/>
+      <c r="E2" s="99"/>
+      <c r="F2" s="99"/>
+      <c r="G2" s="99"/>
+      <c r="H2" s="99"/>
+      <c r="I2" s="99"/>
+      <c r="J2" s="99"/>
+      <c r="K2" s="99"/>
+      <c r="L2" s="99"/>
+      <c r="M2" s="99"/>
+      <c r="N2" s="99"/>
+      <c r="O2" s="99"/>
+      <c r="P2" s="99"/>
+      <c r="Q2" s="99"/>
     </row>
     <row r="3" spans="1:17" ht="56.25" x14ac:dyDescent="0.4">
       <c r="C3" s="75"/>
@@ -8150,23 +8153,23 @@
   </cols>
   <sheetData>
     <row r="2" spans="1:17" ht="26.25" x14ac:dyDescent="0.4">
-      <c r="C2" s="98" t="s">
+      <c r="C2" s="99" t="s">
         <v>28</v>
       </c>
-      <c r="D2" s="98"/>
-      <c r="E2" s="98"/>
-      <c r="F2" s="98"/>
-      <c r="G2" s="98"/>
-      <c r="H2" s="98"/>
-      <c r="I2" s="98"/>
-      <c r="J2" s="98"/>
-      <c r="K2" s="98"/>
-      <c r="L2" s="98"/>
-      <c r="M2" s="98"/>
-      <c r="N2" s="98"/>
-      <c r="O2" s="98"/>
-      <c r="P2" s="98"/>
-      <c r="Q2" s="98"/>
+      <c r="D2" s="99"/>
+      <c r="E2" s="99"/>
+      <c r="F2" s="99"/>
+      <c r="G2" s="99"/>
+      <c r="H2" s="99"/>
+      <c r="I2" s="99"/>
+      <c r="J2" s="99"/>
+      <c r="K2" s="99"/>
+      <c r="L2" s="99"/>
+      <c r="M2" s="99"/>
+      <c r="N2" s="99"/>
+      <c r="O2" s="99"/>
+      <c r="P2" s="99"/>
+      <c r="Q2" s="99"/>
     </row>
     <row r="3" spans="1:17" ht="56.25" x14ac:dyDescent="0.4">
       <c r="C3" s="1"/>
@@ -8825,23 +8828,23 @@
   </cols>
   <sheetData>
     <row r="2" spans="1:17" ht="26.25" x14ac:dyDescent="0.4">
-      <c r="C2" s="98" t="s">
+      <c r="C2" s="99" t="s">
         <v>27</v>
       </c>
-      <c r="D2" s="98"/>
-      <c r="E2" s="98"/>
-      <c r="F2" s="98"/>
-      <c r="G2" s="98"/>
-      <c r="H2" s="98"/>
-      <c r="I2" s="98"/>
-      <c r="J2" s="98"/>
-      <c r="K2" s="98"/>
-      <c r="L2" s="98"/>
-      <c r="M2" s="98"/>
-      <c r="N2" s="98"/>
-      <c r="O2" s="98"/>
-      <c r="P2" s="98"/>
-      <c r="Q2" s="98"/>
+      <c r="D2" s="99"/>
+      <c r="E2" s="99"/>
+      <c r="F2" s="99"/>
+      <c r="G2" s="99"/>
+      <c r="H2" s="99"/>
+      <c r="I2" s="99"/>
+      <c r="J2" s="99"/>
+      <c r="K2" s="99"/>
+      <c r="L2" s="99"/>
+      <c r="M2" s="99"/>
+      <c r="N2" s="99"/>
+      <c r="O2" s="99"/>
+      <c r="P2" s="99"/>
+      <c r="Q2" s="99"/>
     </row>
     <row r="3" spans="1:17" ht="56.25" x14ac:dyDescent="0.4">
       <c r="C3" s="1"/>
@@ -9500,23 +9503,23 @@
   </cols>
   <sheetData>
     <row r="2" spans="1:17" ht="26.25" x14ac:dyDescent="0.4">
-      <c r="C2" s="98" t="s">
+      <c r="C2" s="99" t="s">
         <v>29</v>
       </c>
-      <c r="D2" s="98"/>
-      <c r="E2" s="98"/>
-      <c r="F2" s="98"/>
-      <c r="G2" s="98"/>
-      <c r="H2" s="98"/>
-      <c r="I2" s="98"/>
-      <c r="J2" s="98"/>
-      <c r="K2" s="98"/>
-      <c r="L2" s="98"/>
-      <c r="M2" s="98"/>
-      <c r="N2" s="98"/>
-      <c r="O2" s="98"/>
-      <c r="P2" s="98"/>
-      <c r="Q2" s="98"/>
+      <c r="D2" s="99"/>
+      <c r="E2" s="99"/>
+      <c r="F2" s="99"/>
+      <c r="G2" s="99"/>
+      <c r="H2" s="99"/>
+      <c r="I2" s="99"/>
+      <c r="J2" s="99"/>
+      <c r="K2" s="99"/>
+      <c r="L2" s="99"/>
+      <c r="M2" s="99"/>
+      <c r="N2" s="99"/>
+      <c r="O2" s="99"/>
+      <c r="P2" s="99"/>
+      <c r="Q2" s="99"/>
     </row>
     <row r="3" spans="1:17" ht="56.25" x14ac:dyDescent="0.4">
       <c r="C3" s="75"/>
@@ -10173,38 +10176,38 @@
   <sheetData>
     <row r="1" spans="1:17" ht="8.25" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="2" spans="1:17" ht="59.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="C2" s="99" t="s">
+      <c r="C2" s="100" t="s">
         <v>212</v>
       </c>
-      <c r="D2" s="99"/>
-      <c r="E2" s="99"/>
-      <c r="F2" s="99"/>
-      <c r="G2" s="99"/>
-      <c r="H2" s="99"/>
-      <c r="I2" s="99"/>
-      <c r="J2" s="99"/>
-      <c r="K2" s="99"/>
-      <c r="L2" s="99"/>
-      <c r="M2" s="99"/>
-      <c r="N2" s="99"/>
+      <c r="D2" s="100"/>
+      <c r="E2" s="100"/>
+      <c r="F2" s="100"/>
+      <c r="G2" s="100"/>
+      <c r="H2" s="100"/>
+      <c r="I2" s="100"/>
+      <c r="J2" s="100"/>
+      <c r="K2" s="100"/>
+      <c r="L2" s="100"/>
+      <c r="M2" s="100"/>
+      <c r="N2" s="100"/>
       <c r="O2" s="19"/>
     </row>
     <row r="3" spans="1:17" ht="20.25" x14ac:dyDescent="0.25">
       <c r="C3" s="83"/>
-      <c r="F3" s="100" t="s">
+      <c r="F3" s="101" t="s">
         <v>236</v>
       </c>
-      <c r="G3" s="100"/>
-      <c r="H3" s="100"/>
-      <c r="I3" s="100"/>
-      <c r="J3" s="100"/>
-      <c r="K3" s="100"/>
-      <c r="L3" s="100"/>
-      <c r="M3" s="100"/>
-      <c r="N3" s="100"/>
-      <c r="O3" s="100"/>
-      <c r="P3" s="100"/>
-      <c r="Q3" s="100"/>
+      <c r="G3" s="101"/>
+      <c r="H3" s="101"/>
+      <c r="I3" s="101"/>
+      <c r="J3" s="101"/>
+      <c r="K3" s="101"/>
+      <c r="L3" s="101"/>
+      <c r="M3" s="101"/>
+      <c r="N3" s="101"/>
+      <c r="O3" s="101"/>
+      <c r="P3" s="101"/>
+      <c r="Q3" s="101"/>
     </row>
     <row r="4" spans="1:17" ht="36" x14ac:dyDescent="0.2">
       <c r="A4" s="12" t="s">
@@ -10814,23 +10817,23 @@
   </cols>
   <sheetData>
     <row r="2" spans="1:17" ht="26.25" x14ac:dyDescent="0.4">
-      <c r="C2" s="98" t="s">
+      <c r="C2" s="99" t="s">
         <v>16</v>
       </c>
-      <c r="D2" s="98"/>
-      <c r="E2" s="98"/>
-      <c r="F2" s="98"/>
-      <c r="G2" s="98"/>
-      <c r="H2" s="98"/>
-      <c r="I2" s="98"/>
-      <c r="J2" s="98"/>
-      <c r="K2" s="98"/>
-      <c r="L2" s="98"/>
-      <c r="M2" s="98"/>
-      <c r="N2" s="98"/>
-      <c r="O2" s="98"/>
-      <c r="P2" s="98"/>
-      <c r="Q2" s="98"/>
+      <c r="D2" s="99"/>
+      <c r="E2" s="99"/>
+      <c r="F2" s="99"/>
+      <c r="G2" s="99"/>
+      <c r="H2" s="99"/>
+      <c r="I2" s="99"/>
+      <c r="J2" s="99"/>
+      <c r="K2" s="99"/>
+      <c r="L2" s="99"/>
+      <c r="M2" s="99"/>
+      <c r="N2" s="99"/>
+      <c r="O2" s="99"/>
+      <c r="P2" s="99"/>
+      <c r="Q2" s="99"/>
     </row>
     <row r="3" spans="1:17" ht="56.25" x14ac:dyDescent="0.4">
       <c r="C3" s="1"/>
@@ -11039,7 +11042,7 @@
       <c r="B11" s="73">
         <v>6</v>
       </c>
-      <c r="C11" s="111">
+      <c r="C11" s="98">
         <v>46232</v>
       </c>
       <c r="D11" s="73">
@@ -11066,7 +11069,7 @@
       <c r="B12" s="73">
         <v>7</v>
       </c>
-      <c r="C12" s="111">
+      <c r="C12" s="98">
         <v>46232</v>
       </c>
       <c r="D12" s="73">
@@ -11569,7 +11572,7 @@
       </c>
       <c r="C4" s="53">
         <f>SUM(C6:C2000)</f>
-        <v>15767</v>
+        <v>16075</v>
       </c>
     </row>
     <row r="5" spans="1:17" ht="18" x14ac:dyDescent="0.2">
@@ -13110,22 +13113,41 @@
       <c r="A71" s="8">
         <v>66</v>
       </c>
-      <c r="B71" s="51"/>
-      <c r="C71" s="55"/>
+      <c r="B71" s="51">
+        <v>46252</v>
+      </c>
+      <c r="C71" s="55">
+        <v>250</v>
+      </c>
       <c r="D71" s="8"/>
-      <c r="E71" s="8"/>
-      <c r="F71" s="8"/>
-      <c r="G71" s="8"/>
+      <c r="E71" s="8" t="s">
+        <v>142</v>
+      </c>
+      <c r="F71" s="8">
+        <v>12</v>
+      </c>
+      <c r="G71" s="8" t="s">
+        <v>232</v>
+      </c>
     </row>
     <row r="72" spans="1:7" ht="18" x14ac:dyDescent="0.25">
       <c r="A72" s="8">
         <v>68</v>
       </c>
-      <c r="B72" s="51"/>
-      <c r="C72" s="55"/>
-      <c r="E72" s="8"/>
+      <c r="B72" s="51">
+        <v>46256</v>
+      </c>
+      <c r="C72" s="55">
+        <v>58</v>
+      </c>
+      <c r="D72" s="8"/>
+      <c r="E72" s="8" t="s">
+        <v>260</v>
+      </c>
       <c r="F72" s="8"/>
-      <c r="G72" s="8"/>
+      <c r="G72" s="8" t="s">
+        <v>306</v>
+      </c>
     </row>
     <row r="73" spans="1:7" ht="18" x14ac:dyDescent="0.25">
       <c r="A73" s="8">
@@ -13365,21 +13387,21 @@
   </cols>
   <sheetData>
     <row r="2" spans="1:14" ht="26.25" x14ac:dyDescent="0.4">
-      <c r="B2" s="98" t="s">
+      <c r="B2" s="99" t="s">
         <v>13</v>
       </c>
-      <c r="C2" s="98"/>
-      <c r="D2" s="98"/>
-      <c r="E2" s="98"/>
-      <c r="F2" s="98"/>
-      <c r="G2" s="98"/>
-      <c r="H2" s="98"/>
-      <c r="I2" s="98"/>
-      <c r="J2" s="98"/>
-      <c r="K2" s="98"/>
-      <c r="L2" s="98"/>
-      <c r="M2" s="98"/>
-      <c r="N2" s="98"/>
+      <c r="C2" s="99"/>
+      <c r="D2" s="99"/>
+      <c r="E2" s="99"/>
+      <c r="F2" s="99"/>
+      <c r="G2" s="99"/>
+      <c r="H2" s="99"/>
+      <c r="I2" s="99"/>
+      <c r="J2" s="99"/>
+      <c r="K2" s="99"/>
+      <c r="L2" s="99"/>
+      <c r="M2" s="99"/>
+      <c r="N2" s="99"/>
     </row>
     <row r="3" spans="1:14" ht="18" x14ac:dyDescent="0.25">
       <c r="B3" s="45" t="s">
@@ -13416,7 +13438,7 @@
       <c r="B5" s="9"/>
       <c r="C5" s="70">
         <f>incomes!C4</f>
-        <v>15767</v>
+        <v>16075</v>
       </c>
       <c r="D5" s="71">
         <f>outcomes!C3</f>
@@ -13424,7 +13446,7 @@
       </c>
       <c r="E5" s="72">
         <f>(C3+C5)-D5</f>
-        <v>11098</v>
+        <v>11406</v>
       </c>
       <c r="F5" s="2"/>
       <c r="G5" s="2"/>
@@ -13789,21 +13811,21 @@
   </cols>
   <sheetData>
     <row r="2" spans="1:19" ht="26.25" x14ac:dyDescent="0.4">
-      <c r="B2" s="98" t="s">
+      <c r="B2" s="99" t="s">
         <v>10</v>
       </c>
-      <c r="C2" s="98"/>
-      <c r="D2" s="98"/>
-      <c r="E2" s="98"/>
-      <c r="F2" s="98"/>
-      <c r="G2" s="98"/>
-      <c r="H2" s="98"/>
-      <c r="I2" s="98"/>
-      <c r="J2" s="98"/>
-      <c r="K2" s="98"/>
-      <c r="L2" s="98"/>
-      <c r="M2" s="98"/>
-      <c r="N2" s="98"/>
+      <c r="C2" s="99"/>
+      <c r="D2" s="99"/>
+      <c r="E2" s="99"/>
+      <c r="F2" s="99"/>
+      <c r="G2" s="99"/>
+      <c r="H2" s="99"/>
+      <c r="I2" s="99"/>
+      <c r="J2" s="99"/>
+      <c r="K2" s="99"/>
+      <c r="L2" s="99"/>
+      <c r="M2" s="99"/>
+      <c r="N2" s="99"/>
     </row>
     <row r="3" spans="1:19" ht="18" x14ac:dyDescent="0.25">
       <c r="B3" s="58" t="s">
@@ -15270,38 +15292,38 @@
   <sheetData>
     <row r="1" spans="1:17" ht="8.25" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="2" spans="1:17" ht="59.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="C2" s="99" t="s">
+      <c r="C2" s="100" t="s">
         <v>185</v>
       </c>
-      <c r="D2" s="99"/>
-      <c r="E2" s="99"/>
-      <c r="F2" s="99"/>
-      <c r="G2" s="99"/>
-      <c r="H2" s="99"/>
-      <c r="I2" s="99"/>
-      <c r="J2" s="99"/>
-      <c r="K2" s="99"/>
-      <c r="L2" s="99"/>
-      <c r="M2" s="99"/>
-      <c r="N2" s="99"/>
+      <c r="D2" s="100"/>
+      <c r="E2" s="100"/>
+      <c r="F2" s="100"/>
+      <c r="G2" s="100"/>
+      <c r="H2" s="100"/>
+      <c r="I2" s="100"/>
+      <c r="J2" s="100"/>
+      <c r="K2" s="100"/>
+      <c r="L2" s="100"/>
+      <c r="M2" s="100"/>
+      <c r="N2" s="100"/>
       <c r="O2" s="19"/>
     </row>
     <row r="3" spans="1:17" ht="20.25" x14ac:dyDescent="0.25">
       <c r="C3" s="83"/>
-      <c r="F3" s="100" t="s">
+      <c r="F3" s="101" t="s">
         <v>188</v>
       </c>
-      <c r="G3" s="100"/>
-      <c r="H3" s="100"/>
-      <c r="I3" s="100"/>
-      <c r="J3" s="100"/>
-      <c r="K3" s="100"/>
-      <c r="L3" s="100"/>
-      <c r="M3" s="100"/>
-      <c r="N3" s="100"/>
-      <c r="O3" s="100"/>
-      <c r="P3" s="100"/>
-      <c r="Q3" s="100"/>
+      <c r="G3" s="101"/>
+      <c r="H3" s="101"/>
+      <c r="I3" s="101"/>
+      <c r="J3" s="101"/>
+      <c r="K3" s="101"/>
+      <c r="L3" s="101"/>
+      <c r="M3" s="101"/>
+      <c r="N3" s="101"/>
+      <c r="O3" s="101"/>
+      <c r="P3" s="101"/>
+      <c r="Q3" s="101"/>
     </row>
     <row r="4" spans="1:17" ht="36" x14ac:dyDescent="0.2">
       <c r="A4" s="12" t="s">
@@ -15826,38 +15848,38 @@
   </cols>
   <sheetData>
     <row r="2" spans="1:32" ht="26.25" x14ac:dyDescent="0.4">
-      <c r="B2" s="98" t="s">
+      <c r="B2" s="99" t="s">
         <v>36</v>
       </c>
-      <c r="C2" s="98"/>
-      <c r="D2" s="98"/>
-      <c r="E2" s="98"/>
-      <c r="F2" s="98"/>
-      <c r="G2" s="98"/>
-      <c r="H2" s="98"/>
-      <c r="I2" s="98"/>
-      <c r="J2" s="98"/>
-      <c r="K2" s="98"/>
-      <c r="L2" s="98"/>
-      <c r="M2" s="98"/>
-      <c r="N2" s="98"/>
-      <c r="O2" s="98"/>
-      <c r="P2" s="98"/>
-      <c r="Q2" s="98"/>
-      <c r="R2" s="98"/>
-      <c r="S2" s="98"/>
-      <c r="T2" s="98"/>
-      <c r="U2" s="98"/>
-      <c r="V2" s="98"/>
-      <c r="W2" s="98"/>
-      <c r="X2" s="98"/>
-      <c r="Y2" s="98"/>
-      <c r="Z2" s="98"/>
-      <c r="AA2" s="98"/>
-      <c r="AB2" s="98"/>
-      <c r="AC2" s="98"/>
-      <c r="AD2" s="98"/>
-      <c r="AE2" s="98"/>
+      <c r="C2" s="99"/>
+      <c r="D2" s="99"/>
+      <c r="E2" s="99"/>
+      <c r="F2" s="99"/>
+      <c r="G2" s="99"/>
+      <c r="H2" s="99"/>
+      <c r="I2" s="99"/>
+      <c r="J2" s="99"/>
+      <c r="K2" s="99"/>
+      <c r="L2" s="99"/>
+      <c r="M2" s="99"/>
+      <c r="N2" s="99"/>
+      <c r="O2" s="99"/>
+      <c r="P2" s="99"/>
+      <c r="Q2" s="99"/>
+      <c r="R2" s="99"/>
+      <c r="S2" s="99"/>
+      <c r="T2" s="99"/>
+      <c r="U2" s="99"/>
+      <c r="V2" s="99"/>
+      <c r="W2" s="99"/>
+      <c r="X2" s="99"/>
+      <c r="Y2" s="99"/>
+      <c r="Z2" s="99"/>
+      <c r="AA2" s="99"/>
+      <c r="AB2" s="99"/>
+      <c r="AC2" s="99"/>
+      <c r="AD2" s="99"/>
+      <c r="AE2" s="99"/>
     </row>
     <row r="3" spans="1:32" ht="18" x14ac:dyDescent="0.25">
       <c r="B3" s="10"/>
@@ -20149,37 +20171,37 @@
   <sheetData>
     <row r="1" spans="1:20" ht="26.25" x14ac:dyDescent="0.4">
       <c r="B1" s="18"/>
-      <c r="C1" s="101" t="s">
+      <c r="C1" s="102" t="s">
         <v>140</v>
       </c>
-      <c r="D1" s="101"/>
-      <c r="E1" s="101"/>
-      <c r="F1" s="101"/>
-      <c r="G1" s="101"/>
-      <c r="H1" s="101"/>
-      <c r="I1" s="101"/>
-      <c r="J1" s="101"/>
-      <c r="K1" s="101"/>
-      <c r="L1" s="101"/>
-      <c r="M1" s="101"/>
-      <c r="N1" s="101"/>
-      <c r="O1" s="101"/>
+      <c r="D1" s="102"/>
+      <c r="E1" s="102"/>
+      <c r="F1" s="102"/>
+      <c r="G1" s="102"/>
+      <c r="H1" s="102"/>
+      <c r="I1" s="102"/>
+      <c r="J1" s="102"/>
+      <c r="K1" s="102"/>
+      <c r="L1" s="102"/>
+      <c r="M1" s="102"/>
+      <c r="N1" s="102"/>
+      <c r="O1" s="102"/>
     </row>
     <row r="2" spans="1:20" ht="26.25" x14ac:dyDescent="0.4">
       <c r="B2" s="18"/>
-      <c r="C2" s="98"/>
-      <c r="D2" s="98"/>
-      <c r="E2" s="98"/>
-      <c r="F2" s="98"/>
-      <c r="G2" s="98"/>
-      <c r="H2" s="98"/>
-      <c r="I2" s="98"/>
-      <c r="J2" s="98"/>
-      <c r="K2" s="98"/>
-      <c r="L2" s="98"/>
-      <c r="M2" s="98"/>
-      <c r="N2" s="98"/>
-      <c r="O2" s="98"/>
+      <c r="C2" s="99"/>
+      <c r="D2" s="99"/>
+      <c r="E2" s="99"/>
+      <c r="F2" s="99"/>
+      <c r="G2" s="99"/>
+      <c r="H2" s="99"/>
+      <c r="I2" s="99"/>
+      <c r="J2" s="99"/>
+      <c r="K2" s="99"/>
+      <c r="L2" s="99"/>
+      <c r="M2" s="99"/>
+      <c r="N2" s="99"/>
+      <c r="O2" s="99"/>
     </row>
     <row r="3" spans="1:20" x14ac:dyDescent="0.2">
       <c r="B3" s="3"/>
@@ -20735,7 +20757,7 @@
       </c>
       <c r="N13" s="26">
         <f>Apartment12!D13</f>
-        <v>0</v>
+        <v>250</v>
       </c>
       <c r="O13" s="26">
         <f>Apartment13!D13</f>
@@ -21240,28 +21262,28 @@
   </cols>
   <sheetData>
     <row r="2" spans="1:14" ht="26.25" x14ac:dyDescent="0.4">
-      <c r="C2" s="98" t="s">
+      <c r="C2" s="99" t="s">
         <v>47</v>
       </c>
-      <c r="D2" s="98"/>
-      <c r="E2" s="98"/>
-      <c r="F2" s="98"/>
-      <c r="G2" s="98"/>
-      <c r="H2" s="98"/>
-      <c r="I2" s="98"/>
-      <c r="J2" s="98"/>
-      <c r="K2" s="98"/>
-      <c r="L2" s="98"/>
-      <c r="M2" s="98"/>
-      <c r="N2" s="98"/>
+      <c r="D2" s="99"/>
+      <c r="E2" s="99"/>
+      <c r="F2" s="99"/>
+      <c r="G2" s="99"/>
+      <c r="H2" s="99"/>
+      <c r="I2" s="99"/>
+      <c r="J2" s="99"/>
+      <c r="K2" s="99"/>
+      <c r="L2" s="99"/>
+      <c r="M2" s="99"/>
+      <c r="N2" s="99"/>
     </row>
     <row r="3" spans="1:14" ht="18" x14ac:dyDescent="0.25">
       <c r="C3" s="83"/>
-      <c r="G3" s="102" t="s">
+      <c r="G3" s="103" t="s">
         <v>94</v>
       </c>
-      <c r="H3" s="102"/>
-      <c r="I3" s="102"/>
+      <c r="H3" s="103"/>
+      <c r="I3" s="103"/>
     </row>
     <row r="4" spans="1:14" ht="36" x14ac:dyDescent="0.2">
       <c r="A4" s="12" t="s">
@@ -21871,23 +21893,23 @@
   </cols>
   <sheetData>
     <row r="2" spans="1:17" ht="26.25" x14ac:dyDescent="0.4">
-      <c r="C2" s="98" t="s">
+      <c r="C2" s="99" t="s">
         <v>21</v>
       </c>
-      <c r="D2" s="98"/>
-      <c r="E2" s="98"/>
-      <c r="F2" s="98"/>
-      <c r="G2" s="98"/>
-      <c r="H2" s="98"/>
-      <c r="I2" s="98"/>
-      <c r="J2" s="98"/>
-      <c r="K2" s="98"/>
-      <c r="L2" s="98"/>
-      <c r="M2" s="98"/>
-      <c r="N2" s="98"/>
-      <c r="O2" s="98"/>
-      <c r="P2" s="98"/>
-      <c r="Q2" s="98"/>
+      <c r="D2" s="99"/>
+      <c r="E2" s="99"/>
+      <c r="F2" s="99"/>
+      <c r="G2" s="99"/>
+      <c r="H2" s="99"/>
+      <c r="I2" s="99"/>
+      <c r="J2" s="99"/>
+      <c r="K2" s="99"/>
+      <c r="L2" s="99"/>
+      <c r="M2" s="99"/>
+      <c r="N2" s="99"/>
+      <c r="O2" s="99"/>
+      <c r="P2" s="99"/>
+      <c r="Q2" s="99"/>
     </row>
     <row r="3" spans="1:17" ht="56.25" x14ac:dyDescent="0.4">
       <c r="C3" s="1"/>
@@ -22540,23 +22562,23 @@
   </cols>
   <sheetData>
     <row r="2" spans="1:17" ht="26.25" x14ac:dyDescent="0.4">
-      <c r="C2" s="98" t="s">
+      <c r="C2" s="99" t="s">
         <v>20</v>
       </c>
-      <c r="D2" s="98"/>
-      <c r="E2" s="98"/>
-      <c r="F2" s="98"/>
-      <c r="G2" s="98"/>
-      <c r="H2" s="98"/>
-      <c r="I2" s="98"/>
-      <c r="J2" s="98"/>
-      <c r="K2" s="98"/>
-      <c r="L2" s="98"/>
-      <c r="M2" s="98"/>
-      <c r="N2" s="98"/>
-      <c r="O2" s="98"/>
-      <c r="P2" s="98"/>
-      <c r="Q2" s="98"/>
+      <c r="D2" s="99"/>
+      <c r="E2" s="99"/>
+      <c r="F2" s="99"/>
+      <c r="G2" s="99"/>
+      <c r="H2" s="99"/>
+      <c r="I2" s="99"/>
+      <c r="J2" s="99"/>
+      <c r="K2" s="99"/>
+      <c r="L2" s="99"/>
+      <c r="M2" s="99"/>
+      <c r="N2" s="99"/>
+      <c r="O2" s="99"/>
+      <c r="P2" s="99"/>
+      <c r="Q2" s="99"/>
     </row>
     <row r="3" spans="1:17" ht="56.25" x14ac:dyDescent="0.4">
       <c r="C3" s="75"/>
@@ -22583,7 +22605,7 @@
       <c r="C4" s="76"/>
       <c r="D4" s="83">
         <f>SUM(D6:D2001)</f>
-        <v>1750</v>
+        <v>2000</v>
       </c>
       <c r="E4" s="11"/>
       <c r="F4" s="83">
@@ -22816,8 +22838,12 @@
       <c r="B13" s="73">
         <v>8</v>
       </c>
-      <c r="C13" s="77"/>
-      <c r="D13" s="33"/>
+      <c r="C13" s="77">
+        <v>46252</v>
+      </c>
+      <c r="D13" s="33">
+        <v>250</v>
+      </c>
       <c r="E13" s="8"/>
       <c r="F13" s="33">
         <v>250</v>
@@ -23203,23 +23229,23 @@
   </cols>
   <sheetData>
     <row r="2" spans="1:17" ht="26.25" x14ac:dyDescent="0.4">
-      <c r="C2" s="98" t="s">
+      <c r="C2" s="99" t="s">
         <v>114</v>
       </c>
-      <c r="D2" s="98"/>
-      <c r="E2" s="98"/>
-      <c r="F2" s="98"/>
-      <c r="G2" s="98"/>
-      <c r="H2" s="98"/>
-      <c r="I2" s="98"/>
-      <c r="J2" s="98"/>
-      <c r="K2" s="98"/>
-      <c r="L2" s="98"/>
-      <c r="M2" s="98"/>
-      <c r="N2" s="98"/>
-      <c r="O2" s="98"/>
-      <c r="P2" s="98"/>
-      <c r="Q2" s="98"/>
+      <c r="D2" s="99"/>
+      <c r="E2" s="99"/>
+      <c r="F2" s="99"/>
+      <c r="G2" s="99"/>
+      <c r="H2" s="99"/>
+      <c r="I2" s="99"/>
+      <c r="J2" s="99"/>
+      <c r="K2" s="99"/>
+      <c r="L2" s="99"/>
+      <c r="M2" s="99"/>
+      <c r="N2" s="99"/>
+      <c r="O2" s="99"/>
+      <c r="P2" s="99"/>
+      <c r="Q2" s="99"/>
     </row>
     <row r="3" spans="1:17" ht="56.25" x14ac:dyDescent="0.4">
       <c r="C3" s="57"/>
@@ -23632,14 +23658,14 @@
       <c r="F20" s="8"/>
       <c r="G20" s="8"/>
       <c r="H20" s="2"/>
-      <c r="I20" s="103" t="s">
+      <c r="I20" s="104" t="s">
         <v>118</v>
       </c>
-      <c r="J20" s="103"/>
-      <c r="K20" s="103"/>
-      <c r="L20" s="103"/>
-      <c r="M20" s="103"/>
-      <c r="N20" s="103"/>
+      <c r="J20" s="104"/>
+      <c r="K20" s="104"/>
+      <c r="L20" s="104"/>
+      <c r="M20" s="104"/>
+      <c r="N20" s="104"/>
     </row>
     <row r="21" spans="1:17" ht="23.25" x14ac:dyDescent="0.35">
       <c r="A21" s="8"/>
@@ -23650,14 +23676,14 @@
       <c r="F21" s="8"/>
       <c r="G21" s="8"/>
       <c r="H21" s="2"/>
-      <c r="I21" s="103" t="s">
+      <c r="I21" s="104" t="s">
         <v>238</v>
       </c>
-      <c r="J21" s="103"/>
-      <c r="K21" s="103"/>
-      <c r="L21" s="103"/>
-      <c r="M21" s="103"/>
-      <c r="N21" s="103"/>
+      <c r="J21" s="104"/>
+      <c r="K21" s="104"/>
+      <c r="L21" s="104"/>
+      <c r="M21" s="104"/>
+      <c r="N21" s="104"/>
     </row>
     <row r="22" spans="1:17" ht="18" x14ac:dyDescent="0.25">
       <c r="A22" s="8"/>
@@ -23695,13 +23721,13 @@
       <c r="G23" s="48"/>
       <c r="H23" s="48"/>
       <c r="I23" s="48"/>
-      <c r="J23" s="104"/>
-      <c r="K23" s="104"/>
-      <c r="L23" s="104"/>
-      <c r="M23" s="104"/>
-      <c r="N23" s="104"/>
-      <c r="O23" s="104"/>
-      <c r="P23" s="104"/>
+      <c r="J23" s="105"/>
+      <c r="K23" s="105"/>
+      <c r="L23" s="105"/>
+      <c r="M23" s="105"/>
+      <c r="N23" s="105"/>
+      <c r="O23" s="105"/>
+      <c r="P23" s="105"/>
     </row>
     <row r="24" spans="1:17" ht="18" x14ac:dyDescent="0.25">
       <c r="A24" s="8"/>
@@ -23715,13 +23741,13 @@
       </c>
       <c r="H24" s="8"/>
       <c r="I24" s="8"/>
-      <c r="J24" s="104"/>
-      <c r="K24" s="104"/>
-      <c r="L24" s="104"/>
-      <c r="M24" s="104"/>
-      <c r="N24" s="104"/>
-      <c r="O24" s="104"/>
-      <c r="P24" s="104"/>
+      <c r="J24" s="105"/>
+      <c r="K24" s="105"/>
+      <c r="L24" s="105"/>
+      <c r="M24" s="105"/>
+      <c r="N24" s="105"/>
+      <c r="O24" s="105"/>
+      <c r="P24" s="105"/>
     </row>
     <row r="25" spans="1:17" ht="36" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="8"/>
@@ -23735,13 +23761,13 @@
       </c>
       <c r="H25" s="48"/>
       <c r="I25" s="48"/>
-      <c r="J25" s="104"/>
-      <c r="K25" s="104"/>
-      <c r="L25" s="104"/>
-      <c r="M25" s="104"/>
-      <c r="N25" s="104"/>
-      <c r="O25" s="104"/>
-      <c r="P25" s="104"/>
+      <c r="J25" s="105"/>
+      <c r="K25" s="105"/>
+      <c r="L25" s="105"/>
+      <c r="M25" s="105"/>
+      <c r="N25" s="105"/>
+      <c r="O25" s="105"/>
+      <c r="P25" s="105"/>
     </row>
     <row r="26" spans="1:17" ht="23.25" x14ac:dyDescent="0.35">
       <c r="A26" s="8"/>

--- a/Book2026.xlsx
+++ b/Book2026.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\syana05012019\2024\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{14E5E6B0-8E0A-4E7B-A69D-CA1EA50534BF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{490D07FC-EB9B-4D4E-834B-8378B098FC67}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" tabRatio="947" firstSheet="13" activeTab="20" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" tabRatio="947" firstSheet="13" activeTab="22" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="monthly_elctricity" sheetId="28" r:id="rId1"/>
@@ -47,7 +47,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="873" uniqueCount="307">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="876" uniqueCount="309">
   <si>
     <t>صفحة الإيرادات</t>
   </si>
@@ -968,6 +968,12 @@
   </si>
   <si>
     <t>تحت حساب فوائد شهادة  رقم 1807951149146700023 بتاريخ اصدار 21- ديسمبر - 2025 بفائدة 14%، عن شهر اغسطس / 2026</t>
+  </si>
+  <si>
+    <t>تحت حساب صيانة شهر اغسطس / 2026</t>
+  </si>
+  <si>
+    <t>تحت حساب فاتورة المياه عن شهر اغسطس /2026</t>
   </si>
 </sst>
 </file>
@@ -9546,7 +9552,7 @@
       <c r="C4" s="76"/>
       <c r="D4" s="11">
         <f>SUM(D6:D2001)</f>
-        <v>675</v>
+        <v>825</v>
       </c>
       <c r="E4" s="11"/>
       <c r="F4" s="83">
@@ -9753,7 +9759,7 @@
         <v>7</v>
       </c>
       <c r="C12" s="77">
-        <v>46266</v>
+        <v>46204</v>
       </c>
       <c r="D12" s="8">
         <v>150</v>
@@ -9780,9 +9786,11 @@
         <v>8</v>
       </c>
       <c r="C13" s="77">
-        <v>46266</v>
-      </c>
-      <c r="D13" s="8"/>
+        <v>46237</v>
+      </c>
+      <c r="D13" s="8">
+        <v>150</v>
+      </c>
       <c r="E13" s="8"/>
       <c r="F13" s="33">
         <v>150</v>
@@ -11572,7 +11580,7 @@
       </c>
       <c r="C4" s="53">
         <f>SUM(C6:C2000)</f>
-        <v>16075</v>
+        <v>16225</v>
       </c>
     </row>
     <row r="5" spans="1:17" ht="18" x14ac:dyDescent="0.2">
@@ -13153,12 +13161,21 @@
       <c r="A73" s="8">
         <v>69</v>
       </c>
-      <c r="B73" s="51"/>
-      <c r="C73" s="55"/>
-      <c r="D73" s="8"/>
-      <c r="E73" s="8"/>
-      <c r="F73" s="8"/>
-      <c r="G73" s="8"/>
+      <c r="B73" s="51">
+        <v>46237</v>
+      </c>
+      <c r="C73" s="55">
+        <v>150</v>
+      </c>
+      <c r="E73" s="8" t="s">
+        <v>160</v>
+      </c>
+      <c r="F73" s="8">
+        <v>2</v>
+      </c>
+      <c r="G73" s="8" t="s">
+        <v>307</v>
+      </c>
     </row>
     <row r="74" spans="1:7" ht="18" x14ac:dyDescent="0.25">
       <c r="A74" s="8">
@@ -13438,15 +13455,15 @@
       <c r="B5" s="9"/>
       <c r="C5" s="70">
         <f>incomes!C4</f>
-        <v>16075</v>
+        <v>16225</v>
       </c>
       <c r="D5" s="71">
         <f>outcomes!C3</f>
-        <v>18571</v>
+        <v>19601</v>
       </c>
       <c r="E5" s="72">
         <f>(C3+C5)-D5</f>
-        <v>11406</v>
+        <v>10526</v>
       </c>
       <c r="F5" s="2"/>
       <c r="G5" s="2"/>
@@ -13833,7 +13850,7 @@
       </c>
       <c r="C3" s="53">
         <f>SUM(C5:C2002)</f>
-        <v>18571</v>
+        <v>19601</v>
       </c>
     </row>
     <row r="4" spans="1:19" ht="36" x14ac:dyDescent="0.2">
@@ -14584,9 +14601,15 @@
       <c r="A42" s="33">
         <v>38</v>
       </c>
-      <c r="B42" s="60"/>
-      <c r="C42" s="55"/>
-      <c r="D42" s="8"/>
+      <c r="B42" s="60">
+        <v>46254</v>
+      </c>
+      <c r="C42" s="55">
+        <v>1030</v>
+      </c>
+      <c r="D42" s="8" t="s">
+        <v>308</v>
+      </c>
     </row>
     <row r="43" spans="1:20" ht="18" x14ac:dyDescent="0.25">
       <c r="A43" s="33">
@@ -20717,7 +20740,7 @@
       </c>
       <c r="D13" s="26">
         <f>Apartment2!D13</f>
-        <v>0</v>
+        <v>150</v>
       </c>
       <c r="E13" s="26">
         <f>Apartment3!D13</f>
@@ -21351,12 +21374,12 @@
       </c>
       <c r="C6" s="91">
         <f>Apartment2!D4</f>
-        <v>675</v>
+        <v>825</v>
       </c>
       <c r="D6" s="92"/>
       <c r="E6" s="94">
         <f t="shared" ref="E6:E18" si="0">D6-C6</f>
-        <v>-675</v>
+        <v>-825</v>
       </c>
       <c r="F6" s="2" t="s">
         <v>51</v>

--- a/Book2026.xlsx
+++ b/Book2026.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\syana05012019\2024\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{490D07FC-EB9B-4D4E-834B-8378B098FC67}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FE700AB7-43EA-4F64-9F51-98FA70394C9B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" tabRatio="947" firstSheet="13" activeTab="22" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" tabRatio="947" firstSheet="2" activeTab="11" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="monthly_elctricity" sheetId="28" r:id="rId1"/>
@@ -47,7 +47,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="876" uniqueCount="309">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="878" uniqueCount="310">
   <si>
     <t>صفحة الإيرادات</t>
   </si>
@@ -974,6 +974,9 @@
   </si>
   <si>
     <t>تحت حساب فاتورة المياه عن شهر اغسطس /2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">تحت حساب صيانة شهور يوليه - اغسطس - سبتمبر / 2026 </t>
   </si>
 </sst>
 </file>
@@ -4739,7 +4742,7 @@
       <c r="C4" s="49"/>
       <c r="D4" s="11">
         <f>SUM(D6:D2004)</f>
-        <v>900</v>
+        <v>1350</v>
       </c>
       <c r="E4" s="11"/>
       <c r="F4" s="11">
@@ -5002,9 +5005,11 @@
         <v>7</v>
       </c>
       <c r="C12" s="51">
-        <v>46359</v>
-      </c>
-      <c r="D12" s="55"/>
+        <v>46261</v>
+      </c>
+      <c r="D12" s="55">
+        <v>150</v>
+      </c>
       <c r="E12" s="8"/>
       <c r="F12" s="8">
         <v>150</v>
@@ -5038,9 +5043,11 @@
         <v>8</v>
       </c>
       <c r="C13" s="51">
-        <v>46359</v>
-      </c>
-      <c r="D13" s="55"/>
+        <v>46261</v>
+      </c>
+      <c r="D13" s="55">
+        <v>150</v>
+      </c>
       <c r="E13" s="8"/>
       <c r="F13" s="8">
         <v>150</v>
@@ -5068,9 +5075,11 @@
         <v>9</v>
       </c>
       <c r="C14" s="51">
-        <v>46359</v>
-      </c>
-      <c r="D14" s="55"/>
+        <v>46261</v>
+      </c>
+      <c r="D14" s="55">
+        <v>150</v>
+      </c>
       <c r="E14" s="8"/>
       <c r="F14" s="8">
         <v>150</v>
@@ -11580,7 +11589,7 @@
       </c>
       <c r="C4" s="53">
         <f>SUM(C6:C2000)</f>
-        <v>16225</v>
+        <v>16675</v>
       </c>
     </row>
     <row r="5" spans="1:17" ht="18" x14ac:dyDescent="0.2">
@@ -13181,12 +13190,22 @@
       <c r="A74" s="8">
         <v>70</v>
       </c>
-      <c r="B74" s="51"/>
-      <c r="C74" s="55"/>
+      <c r="B74" s="51">
+        <v>46261</v>
+      </c>
+      <c r="C74" s="55">
+        <v>450</v>
+      </c>
       <c r="D74" s="8"/>
-      <c r="E74" s="8"/>
-      <c r="F74" s="8"/>
-      <c r="G74" s="8"/>
+      <c r="E74" s="8" t="s">
+        <v>184</v>
+      </c>
+      <c r="F74" s="8">
+        <v>9</v>
+      </c>
+      <c r="G74" s="8" t="s">
+        <v>309</v>
+      </c>
     </row>
     <row r="75" spans="1:7" ht="18" x14ac:dyDescent="0.25">
       <c r="A75" s="8">
@@ -13455,7 +13474,7 @@
       <c r="B5" s="9"/>
       <c r="C5" s="70">
         <f>incomes!C4</f>
-        <v>16225</v>
+        <v>16675</v>
       </c>
       <c r="D5" s="71">
         <f>outcomes!C3</f>
@@ -13463,7 +13482,7 @@
       </c>
       <c r="E5" s="72">
         <f>(C3+C5)-D5</f>
-        <v>10526</v>
+        <v>10976</v>
       </c>
       <c r="F5" s="2"/>
       <c r="G5" s="2"/>
@@ -20706,7 +20725,7 @@
       </c>
       <c r="K12" s="26">
         <f>Apartment9!D12</f>
-        <v>0</v>
+        <v>150</v>
       </c>
       <c r="L12" s="26">
         <f>Apartment10!D12</f>
@@ -20768,7 +20787,7 @@
       </c>
       <c r="K13" s="26">
         <f>Apartment9!D13</f>
-        <v>0</v>
+        <v>150</v>
       </c>
       <c r="L13" s="26">
         <f>Apartment10!D13</f>
@@ -20830,7 +20849,7 @@
       </c>
       <c r="K14" s="26">
         <f>Apartment9!D14</f>
-        <v>0</v>
+        <v>150</v>
       </c>
       <c r="L14" s="26">
         <f>Apartment10!D14</f>
@@ -21562,12 +21581,12 @@
       </c>
       <c r="C13" s="91">
         <f>Apartment9!D4</f>
-        <v>900</v>
+        <v>1350</v>
       </c>
       <c r="D13" s="92"/>
       <c r="E13" s="94">
         <f t="shared" si="0"/>
-        <v>-900</v>
+        <v>-1350</v>
       </c>
       <c r="F13" s="2" t="s">
         <v>53</v>

--- a/Book2026.xlsx
+++ b/Book2026.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\syana05012019\2024\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FE700AB7-43EA-4F64-9F51-98FA70394C9B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{42009945-7713-4372-A028-5F6EC6B62C82}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" tabRatio="947" firstSheet="2" activeTab="11" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" tabRatio="947" firstSheet="13" activeTab="22" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="monthly_elctricity" sheetId="28" r:id="rId1"/>
@@ -47,7 +47,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="878" uniqueCount="310">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="881" uniqueCount="312">
   <si>
     <t>صفحة الإيرادات</t>
   </si>
@@ -977,6 +977,12 @@
   </si>
   <si>
     <t xml:space="preserve">تحت حساب صيانة شهور يوليه - اغسطس - سبتمبر / 2026 </t>
+  </si>
+  <si>
+    <t>تحت حساب نظافة السلم لام احمد عن شهر اغسطس /2026</t>
+  </si>
+  <si>
+    <t>تحت حساب كهرباء شهر اغسطس /2026</t>
   </si>
 </sst>
 </file>
@@ -1574,21 +1580,6 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" readingOrder="2"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1606,6 +1597,21 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -4786,12 +4792,12 @@
       <c r="Q5" s="12" t="s">
         <v>37</v>
       </c>
-      <c r="R5" s="106" t="s">
+      <c r="R5" s="101" t="s">
         <v>77</v>
       </c>
-      <c r="S5" s="107"/>
-      <c r="T5" s="107"/>
-      <c r="U5" s="108"/>
+      <c r="S5" s="102"/>
+      <c r="T5" s="102"/>
+      <c r="U5" s="103"/>
     </row>
     <row r="6" spans="1:22" ht="18" x14ac:dyDescent="0.25">
       <c r="A6" s="8">
@@ -5030,10 +5036,10 @@
         <f>SUM(Q6:Q11)</f>
         <v>0</v>
       </c>
-      <c r="R12" s="109"/>
-      <c r="S12" s="110"/>
-      <c r="T12" s="110"/>
-      <c r="U12" s="111"/>
+      <c r="R12" s="104"/>
+      <c r="S12" s="105"/>
+      <c r="T12" s="105"/>
+      <c r="U12" s="106"/>
     </row>
     <row r="13" spans="1:22" ht="18" x14ac:dyDescent="0.25">
       <c r="A13" s="8">
@@ -10211,20 +10217,20 @@
     </row>
     <row r="3" spans="1:17" ht="20.25" x14ac:dyDescent="0.25">
       <c r="C3" s="83"/>
-      <c r="F3" s="101" t="s">
+      <c r="F3" s="107" t="s">
         <v>236</v>
       </c>
-      <c r="G3" s="101"/>
-      <c r="H3" s="101"/>
-      <c r="I3" s="101"/>
-      <c r="J3" s="101"/>
-      <c r="K3" s="101"/>
-      <c r="L3" s="101"/>
-      <c r="M3" s="101"/>
-      <c r="N3" s="101"/>
-      <c r="O3" s="101"/>
-      <c r="P3" s="101"/>
-      <c r="Q3" s="101"/>
+      <c r="G3" s="107"/>
+      <c r="H3" s="107"/>
+      <c r="I3" s="107"/>
+      <c r="J3" s="107"/>
+      <c r="K3" s="107"/>
+      <c r="L3" s="107"/>
+      <c r="M3" s="107"/>
+      <c r="N3" s="107"/>
+      <c r="O3" s="107"/>
+      <c r="P3" s="107"/>
+      <c r="Q3" s="107"/>
     </row>
     <row r="4" spans="1:17" ht="36" x14ac:dyDescent="0.2">
       <c r="A4" s="12" t="s">
@@ -13478,11 +13484,11 @@
       </c>
       <c r="D5" s="71">
         <f>outcomes!C3</f>
-        <v>19601</v>
+        <v>20246</v>
       </c>
       <c r="E5" s="72">
         <f>(C3+C5)-D5</f>
-        <v>10976</v>
+        <v>10331</v>
       </c>
       <c r="F5" s="2"/>
       <c r="G5" s="2"/>
@@ -13869,7 +13875,7 @@
       </c>
       <c r="C3" s="53">
         <f>SUM(C5:C2002)</f>
-        <v>19601</v>
+        <v>20246</v>
       </c>
     </row>
     <row r="4" spans="1:19" ht="36" x14ac:dyDescent="0.2">
@@ -14634,25 +14640,43 @@
       <c r="A43" s="33">
         <v>39</v>
       </c>
-      <c r="B43" s="60"/>
-      <c r="C43" s="55"/>
-      <c r="D43" s="8"/>
+      <c r="B43" s="60">
+        <v>46262</v>
+      </c>
+      <c r="C43" s="55">
+        <v>400</v>
+      </c>
+      <c r="D43" s="8" t="s">
+        <v>310</v>
+      </c>
     </row>
     <row r="44" spans="1:20" ht="18" x14ac:dyDescent="0.25">
       <c r="A44" s="33">
         <v>40</v>
       </c>
-      <c r="B44" s="60"/>
-      <c r="C44" s="55"/>
-      <c r="D44" s="8"/>
+      <c r="B44" s="60">
+        <v>46264</v>
+      </c>
+      <c r="C44" s="55">
+        <v>243</v>
+      </c>
+      <c r="D44" s="8" t="s">
+        <v>311</v>
+      </c>
     </row>
     <row r="45" spans="1:20" ht="18" x14ac:dyDescent="0.25">
       <c r="A45" s="33">
         <v>41</v>
       </c>
-      <c r="B45" s="60"/>
-      <c r="C45" s="55"/>
-      <c r="D45" s="8"/>
+      <c r="B45" s="60">
+        <v>46264</v>
+      </c>
+      <c r="C45" s="55">
+        <v>2</v>
+      </c>
+      <c r="D45" s="8" t="s">
+        <v>275</v>
+      </c>
     </row>
     <row r="46" spans="1:20" ht="18" x14ac:dyDescent="0.25">
       <c r="A46" s="33">
@@ -15352,20 +15376,20 @@
     </row>
     <row r="3" spans="1:17" ht="20.25" x14ac:dyDescent="0.25">
       <c r="C3" s="83"/>
-      <c r="F3" s="101" t="s">
+      <c r="F3" s="107" t="s">
         <v>188</v>
       </c>
-      <c r="G3" s="101"/>
-      <c r="H3" s="101"/>
-      <c r="I3" s="101"/>
-      <c r="J3" s="101"/>
-      <c r="K3" s="101"/>
-      <c r="L3" s="101"/>
-      <c r="M3" s="101"/>
-      <c r="N3" s="101"/>
-      <c r="O3" s="101"/>
-      <c r="P3" s="101"/>
-      <c r="Q3" s="101"/>
+      <c r="G3" s="107"/>
+      <c r="H3" s="107"/>
+      <c r="I3" s="107"/>
+      <c r="J3" s="107"/>
+      <c r="K3" s="107"/>
+      <c r="L3" s="107"/>
+      <c r="M3" s="107"/>
+      <c r="N3" s="107"/>
+      <c r="O3" s="107"/>
+      <c r="P3" s="107"/>
+      <c r="Q3" s="107"/>
     </row>
     <row r="4" spans="1:17" ht="36" x14ac:dyDescent="0.2">
       <c r="A4" s="12" t="s">
@@ -20213,21 +20237,21 @@
   <sheetData>
     <row r="1" spans="1:20" ht="26.25" x14ac:dyDescent="0.4">
       <c r="B1" s="18"/>
-      <c r="C1" s="102" t="s">
+      <c r="C1" s="108" t="s">
         <v>140</v>
       </c>
-      <c r="D1" s="102"/>
-      <c r="E1" s="102"/>
-      <c r="F1" s="102"/>
-      <c r="G1" s="102"/>
-      <c r="H1" s="102"/>
-      <c r="I1" s="102"/>
-      <c r="J1" s="102"/>
-      <c r="K1" s="102"/>
-      <c r="L1" s="102"/>
-      <c r="M1" s="102"/>
-      <c r="N1" s="102"/>
-      <c r="O1" s="102"/>
+      <c r="D1" s="108"/>
+      <c r="E1" s="108"/>
+      <c r="F1" s="108"/>
+      <c r="G1" s="108"/>
+      <c r="H1" s="108"/>
+      <c r="I1" s="108"/>
+      <c r="J1" s="108"/>
+      <c r="K1" s="108"/>
+      <c r="L1" s="108"/>
+      <c r="M1" s="108"/>
+      <c r="N1" s="108"/>
+      <c r="O1" s="108"/>
     </row>
     <row r="2" spans="1:20" ht="26.25" x14ac:dyDescent="0.4">
       <c r="B2" s="18"/>
@@ -21321,11 +21345,11 @@
     </row>
     <row r="3" spans="1:14" ht="18" x14ac:dyDescent="0.25">
       <c r="C3" s="83"/>
-      <c r="G3" s="103" t="s">
+      <c r="G3" s="109" t="s">
         <v>94</v>
       </c>
-      <c r="H3" s="103"/>
-      <c r="I3" s="103"/>
+      <c r="H3" s="109"/>
+      <c r="I3" s="109"/>
     </row>
     <row r="4" spans="1:14" ht="36" x14ac:dyDescent="0.2">
       <c r="A4" s="12" t="s">
@@ -23700,14 +23724,14 @@
       <c r="F20" s="8"/>
       <c r="G20" s="8"/>
       <c r="H20" s="2"/>
-      <c r="I20" s="104" t="s">
+      <c r="I20" s="110" t="s">
         <v>118</v>
       </c>
-      <c r="J20" s="104"/>
-      <c r="K20" s="104"/>
-      <c r="L20" s="104"/>
-      <c r="M20" s="104"/>
-      <c r="N20" s="104"/>
+      <c r="J20" s="110"/>
+      <c r="K20" s="110"/>
+      <c r="L20" s="110"/>
+      <c r="M20" s="110"/>
+      <c r="N20" s="110"/>
     </row>
     <row r="21" spans="1:17" ht="23.25" x14ac:dyDescent="0.35">
       <c r="A21" s="8"/>
@@ -23718,14 +23742,14 @@
       <c r="F21" s="8"/>
       <c r="G21" s="8"/>
       <c r="H21" s="2"/>
-      <c r="I21" s="104" t="s">
+      <c r="I21" s="110" t="s">
         <v>238</v>
       </c>
-      <c r="J21" s="104"/>
-      <c r="K21" s="104"/>
-      <c r="L21" s="104"/>
-      <c r="M21" s="104"/>
-      <c r="N21" s="104"/>
+      <c r="J21" s="110"/>
+      <c r="K21" s="110"/>
+      <c r="L21" s="110"/>
+      <c r="M21" s="110"/>
+      <c r="N21" s="110"/>
     </row>
     <row r="22" spans="1:17" ht="18" x14ac:dyDescent="0.25">
       <c r="A22" s="8"/>
@@ -23763,13 +23787,13 @@
       <c r="G23" s="48"/>
       <c r="H23" s="48"/>
       <c r="I23" s="48"/>
-      <c r="J23" s="105"/>
-      <c r="K23" s="105"/>
-      <c r="L23" s="105"/>
-      <c r="M23" s="105"/>
-      <c r="N23" s="105"/>
-      <c r="O23" s="105"/>
-      <c r="P23" s="105"/>
+      <c r="J23" s="111"/>
+      <c r="K23" s="111"/>
+      <c r="L23" s="111"/>
+      <c r="M23" s="111"/>
+      <c r="N23" s="111"/>
+      <c r="O23" s="111"/>
+      <c r="P23" s="111"/>
     </row>
     <row r="24" spans="1:17" ht="18" x14ac:dyDescent="0.25">
       <c r="A24" s="8"/>
@@ -23783,13 +23807,13 @@
       </c>
       <c r="H24" s="8"/>
       <c r="I24" s="8"/>
-      <c r="J24" s="105"/>
-      <c r="K24" s="105"/>
-      <c r="L24" s="105"/>
-      <c r="M24" s="105"/>
-      <c r="N24" s="105"/>
-      <c r="O24" s="105"/>
-      <c r="P24" s="105"/>
+      <c r="J24" s="111"/>
+      <c r="K24" s="111"/>
+      <c r="L24" s="111"/>
+      <c r="M24" s="111"/>
+      <c r="N24" s="111"/>
+      <c r="O24" s="111"/>
+      <c r="P24" s="111"/>
     </row>
     <row r="25" spans="1:17" ht="36" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="8"/>
@@ -23803,13 +23827,13 @@
       </c>
       <c r="H25" s="48"/>
       <c r="I25" s="48"/>
-      <c r="J25" s="105"/>
-      <c r="K25" s="105"/>
-      <c r="L25" s="105"/>
-      <c r="M25" s="105"/>
-      <c r="N25" s="105"/>
-      <c r="O25" s="105"/>
-      <c r="P25" s="105"/>
+      <c r="J25" s="111"/>
+      <c r="K25" s="111"/>
+      <c r="L25" s="111"/>
+      <c r="M25" s="111"/>
+      <c r="N25" s="111"/>
+      <c r="O25" s="111"/>
+      <c r="P25" s="111"/>
     </row>
     <row r="26" spans="1:17" ht="23.25" x14ac:dyDescent="0.35">
       <c r="A26" s="8"/>

--- a/Book2026.xlsx
+++ b/Book2026.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\syana05012019\2024\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{42009945-7713-4372-A028-5F6EC6B62C82}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E6261968-BAD6-49CB-AF15-548F8062DA7C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" tabRatio="947" firstSheet="13" activeTab="22" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" tabRatio="947" firstSheet="13" activeTab="18" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="monthly_elctricity" sheetId="28" r:id="rId1"/>
@@ -47,7 +47,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="881" uniqueCount="312">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="889" uniqueCount="313">
   <si>
     <t>صفحة الإيرادات</t>
   </si>
@@ -983,6 +983,9 @@
   </si>
   <si>
     <t>تحت حساب كهرباء شهر اغسطس /2026</t>
+  </si>
+  <si>
+    <t>تحت حساب صيانة شهور سبتمبر - اكتوبر- نوفمبر - ديسمبر / 2026</t>
   </si>
 </sst>
 </file>
@@ -1580,6 +1583,21 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1597,21 +1615,6 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" readingOrder="2"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -4792,12 +4795,12 @@
       <c r="Q5" s="12" t="s">
         <v>37</v>
       </c>
-      <c r="R5" s="101" t="s">
+      <c r="R5" s="106" t="s">
         <v>77</v>
       </c>
-      <c r="S5" s="102"/>
-      <c r="T5" s="102"/>
-      <c r="U5" s="103"/>
+      <c r="S5" s="107"/>
+      <c r="T5" s="107"/>
+      <c r="U5" s="108"/>
     </row>
     <row r="6" spans="1:22" ht="18" x14ac:dyDescent="0.25">
       <c r="A6" s="8">
@@ -5036,10 +5039,10 @@
         <f>SUM(Q6:Q11)</f>
         <v>0</v>
       </c>
-      <c r="R12" s="104"/>
-      <c r="S12" s="105"/>
-      <c r="T12" s="105"/>
-      <c r="U12" s="106"/>
+      <c r="R12" s="109"/>
+      <c r="S12" s="110"/>
+      <c r="T12" s="110"/>
+      <c r="U12" s="111"/>
     </row>
     <row r="13" spans="1:22" ht="18" x14ac:dyDescent="0.25">
       <c r="A13" s="8">
@@ -6212,7 +6215,7 @@
       <c r="C4" s="49"/>
       <c r="D4" s="83">
         <f>SUM(D6:D2001)</f>
-        <v>2400</v>
+        <v>2700</v>
       </c>
       <c r="E4" s="11"/>
       <c r="F4" s="83">
@@ -6475,7 +6478,9 @@
       <c r="C14" s="63">
         <v>46267</v>
       </c>
-      <c r="D14" s="33"/>
+      <c r="D14" s="33">
+        <v>300</v>
+      </c>
       <c r="E14" s="8"/>
       <c r="F14" s="33">
         <v>300</v>
@@ -8217,7 +8222,7 @@
       <c r="C4" s="10"/>
       <c r="D4" s="11">
         <f>SUM(D6:D2001)</f>
-        <v>1200</v>
+        <v>1350</v>
       </c>
       <c r="E4" s="11"/>
       <c r="F4" s="11">
@@ -8480,7 +8485,9 @@
       <c r="C14" s="63">
         <v>46267</v>
       </c>
-      <c r="D14" s="8"/>
+      <c r="D14" s="8">
+        <v>150</v>
+      </c>
       <c r="E14" s="8"/>
       <c r="F14" s="8">
         <v>150</v>
@@ -8892,7 +8899,7 @@
       <c r="C4" s="62"/>
       <c r="D4" s="11">
         <f>SUM(D6:D2001)</f>
-        <v>1200</v>
+        <v>1350</v>
       </c>
       <c r="E4" s="11"/>
       <c r="F4" s="11">
@@ -9155,7 +9162,9 @@
       <c r="C14" s="63">
         <v>46267</v>
       </c>
-      <c r="D14" s="8"/>
+      <c r="D14" s="8">
+        <v>150</v>
+      </c>
       <c r="E14" s="8"/>
       <c r="F14" s="8">
         <v>150</v>
@@ -9567,7 +9576,7 @@
       <c r="C4" s="76"/>
       <c r="D4" s="11">
         <f>SUM(D6:D2001)</f>
-        <v>825</v>
+        <v>1425</v>
       </c>
       <c r="E4" s="11"/>
       <c r="F4" s="83">
@@ -9830,7 +9839,9 @@
       <c r="C14" s="77">
         <v>46299</v>
       </c>
-      <c r="D14" s="8"/>
+      <c r="D14" s="8">
+        <v>150</v>
+      </c>
       <c r="E14" s="8"/>
       <c r="F14" s="33">
         <v>150</v>
@@ -9855,7 +9866,9 @@
       <c r="C15" s="77">
         <v>46299</v>
       </c>
-      <c r="D15" s="8"/>
+      <c r="D15" s="8">
+        <v>150</v>
+      </c>
       <c r="E15" s="8"/>
       <c r="F15" s="33">
         <v>150</v>
@@ -9880,7 +9893,9 @@
       <c r="C16" s="77">
         <v>46350</v>
       </c>
-      <c r="D16" s="8"/>
+      <c r="D16" s="8">
+        <v>150</v>
+      </c>
       <c r="E16" s="8"/>
       <c r="F16" s="33">
         <v>150</v>
@@ -9905,7 +9920,9 @@
       <c r="C17" s="77">
         <v>46350</v>
       </c>
-      <c r="D17" s="8"/>
+      <c r="D17" s="8">
+        <v>150</v>
+      </c>
       <c r="E17" s="8"/>
       <c r="F17" s="33">
         <v>150</v>
@@ -10217,20 +10234,20 @@
     </row>
     <row r="3" spans="1:17" ht="20.25" x14ac:dyDescent="0.25">
       <c r="C3" s="83"/>
-      <c r="F3" s="107" t="s">
+      <c r="F3" s="101" t="s">
         <v>236</v>
       </c>
-      <c r="G3" s="107"/>
-      <c r="H3" s="107"/>
-      <c r="I3" s="107"/>
-      <c r="J3" s="107"/>
-      <c r="K3" s="107"/>
-      <c r="L3" s="107"/>
-      <c r="M3" s="107"/>
-      <c r="N3" s="107"/>
-      <c r="O3" s="107"/>
-      <c r="P3" s="107"/>
-      <c r="Q3" s="107"/>
+      <c r="G3" s="101"/>
+      <c r="H3" s="101"/>
+      <c r="I3" s="101"/>
+      <c r="J3" s="101"/>
+      <c r="K3" s="101"/>
+      <c r="L3" s="101"/>
+      <c r="M3" s="101"/>
+      <c r="N3" s="101"/>
+      <c r="O3" s="101"/>
+      <c r="P3" s="101"/>
+      <c r="Q3" s="101"/>
     </row>
     <row r="4" spans="1:17" ht="36" x14ac:dyDescent="0.2">
       <c r="A4" s="12" t="s">
@@ -11595,7 +11612,7 @@
       </c>
       <c r="C4" s="53">
         <f>SUM(C6:C2000)</f>
-        <v>16675</v>
+        <v>17875</v>
       </c>
     </row>
     <row r="5" spans="1:17" ht="18" x14ac:dyDescent="0.2">
@@ -13217,44 +13234,83 @@
       <c r="A75" s="8">
         <v>71</v>
       </c>
-      <c r="B75" s="51"/>
-      <c r="C75" s="55"/>
-      <c r="D75" s="8"/>
-      <c r="E75" s="8"/>
-      <c r="F75" s="8"/>
-      <c r="G75" s="8"/>
+      <c r="B75" s="51">
+        <v>46266</v>
+      </c>
+      <c r="C75" s="55">
+        <v>300</v>
+      </c>
+      <c r="E75" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="F75" s="8">
+        <v>7</v>
+      </c>
+      <c r="G75" s="8" t="s">
+        <v>233</v>
+      </c>
     </row>
     <row r="76" spans="1:7" ht="18" x14ac:dyDescent="0.25">
       <c r="A76" s="8">
         <v>72</v>
       </c>
-      <c r="B76" s="51"/>
-      <c r="C76" s="55"/>
+      <c r="B76" s="51">
+        <v>46266</v>
+      </c>
+      <c r="C76" s="55">
+        <v>150</v>
+      </c>
       <c r="D76" s="8"/>
-      <c r="E76" s="8"/>
-      <c r="F76" s="8"/>
-      <c r="G76" s="8"/>
+      <c r="E76" s="8" t="s">
+        <v>244</v>
+      </c>
+      <c r="F76" s="8">
+        <v>4</v>
+      </c>
+      <c r="G76" s="8" t="s">
+        <v>233</v>
+      </c>
     </row>
     <row r="77" spans="1:7" ht="18" x14ac:dyDescent="0.25">
       <c r="A77" s="8">
         <v>73</v>
       </c>
-      <c r="B77" s="51"/>
-      <c r="C77" s="55"/>
+      <c r="B77" s="51">
+        <v>46266</v>
+      </c>
+      <c r="C77" s="55">
+        <v>150</v>
+      </c>
       <c r="D77" s="8"/>
-      <c r="E77" s="8"/>
-      <c r="F77" s="8"/>
-      <c r="G77" s="8"/>
+      <c r="E77" s="8" t="s">
+        <v>141</v>
+      </c>
+      <c r="F77" s="8">
+        <v>3</v>
+      </c>
+      <c r="G77" s="8" t="s">
+        <v>233</v>
+      </c>
     </row>
     <row r="78" spans="1:7" ht="18" x14ac:dyDescent="0.25">
       <c r="A78" s="8">
         <v>74</v>
       </c>
-      <c r="B78" s="51"/>
-      <c r="C78" s="55"/>
-      <c r="E78" s="8"/>
-      <c r="F78" s="8"/>
-      <c r="G78" s="8"/>
+      <c r="B78" s="51">
+        <v>46268</v>
+      </c>
+      <c r="C78" s="55">
+        <v>600</v>
+      </c>
+      <c r="E78" s="8" t="s">
+        <v>160</v>
+      </c>
+      <c r="F78" s="8">
+        <v>2</v>
+      </c>
+      <c r="G78" s="8" t="s">
+        <v>312</v>
+      </c>
     </row>
     <row r="79" spans="1:7" ht="18" x14ac:dyDescent="0.25">
       <c r="A79" s="8">
@@ -13480,7 +13536,7 @@
       <c r="B5" s="9"/>
       <c r="C5" s="70">
         <f>incomes!C4</f>
-        <v>16675</v>
+        <v>17875</v>
       </c>
       <c r="D5" s="71">
         <f>outcomes!C3</f>
@@ -13488,7 +13544,7 @@
       </c>
       <c r="E5" s="72">
         <f>(C3+C5)-D5</f>
-        <v>10331</v>
+        <v>11531</v>
       </c>
       <c r="F5" s="2"/>
       <c r="G5" s="2"/>
@@ -15376,20 +15432,20 @@
     </row>
     <row r="3" spans="1:17" ht="20.25" x14ac:dyDescent="0.25">
       <c r="C3" s="83"/>
-      <c r="F3" s="107" t="s">
+      <c r="F3" s="101" t="s">
         <v>188</v>
       </c>
-      <c r="G3" s="107"/>
-      <c r="H3" s="107"/>
-      <c r="I3" s="107"/>
-      <c r="J3" s="107"/>
-      <c r="K3" s="107"/>
-      <c r="L3" s="107"/>
-      <c r="M3" s="107"/>
-      <c r="N3" s="107"/>
-      <c r="O3" s="107"/>
-      <c r="P3" s="107"/>
-      <c r="Q3" s="107"/>
+      <c r="G3" s="101"/>
+      <c r="H3" s="101"/>
+      <c r="I3" s="101"/>
+      <c r="J3" s="101"/>
+      <c r="K3" s="101"/>
+      <c r="L3" s="101"/>
+      <c r="M3" s="101"/>
+      <c r="N3" s="101"/>
+      <c r="O3" s="101"/>
+      <c r="P3" s="101"/>
+      <c r="Q3" s="101"/>
     </row>
     <row r="4" spans="1:17" ht="36" x14ac:dyDescent="0.2">
       <c r="A4" s="12" t="s">
@@ -20237,21 +20293,21 @@
   <sheetData>
     <row r="1" spans="1:20" ht="26.25" x14ac:dyDescent="0.4">
       <c r="B1" s="18"/>
-      <c r="C1" s="108" t="s">
+      <c r="C1" s="102" t="s">
         <v>140</v>
       </c>
-      <c r="D1" s="108"/>
-      <c r="E1" s="108"/>
-      <c r="F1" s="108"/>
-      <c r="G1" s="108"/>
-      <c r="H1" s="108"/>
-      <c r="I1" s="108"/>
-      <c r="J1" s="108"/>
-      <c r="K1" s="108"/>
-      <c r="L1" s="108"/>
-      <c r="M1" s="108"/>
-      <c r="N1" s="108"/>
-      <c r="O1" s="108"/>
+      <c r="D1" s="102"/>
+      <c r="E1" s="102"/>
+      <c r="F1" s="102"/>
+      <c r="G1" s="102"/>
+      <c r="H1" s="102"/>
+      <c r="I1" s="102"/>
+      <c r="J1" s="102"/>
+      <c r="K1" s="102"/>
+      <c r="L1" s="102"/>
+      <c r="M1" s="102"/>
+      <c r="N1" s="102"/>
+      <c r="O1" s="102"/>
     </row>
     <row r="2" spans="1:20" ht="26.25" x14ac:dyDescent="0.4">
       <c r="B2" s="18"/>
@@ -20845,15 +20901,15 @@
       </c>
       <c r="D14" s="26">
         <f>Apartment2!D14</f>
-        <v>0</v>
+        <v>150</v>
       </c>
       <c r="E14" s="26">
         <f>Apartment3!D14</f>
-        <v>0</v>
+        <v>150</v>
       </c>
       <c r="F14" s="26">
         <f>Apartment4!D14</f>
-        <v>0</v>
+        <v>150</v>
       </c>
       <c r="G14" s="26">
         <f>Apartment5!D14</f>
@@ -20865,7 +20921,7 @@
       </c>
       <c r="I14" s="26">
         <f>Apartment7!D14</f>
-        <v>0</v>
+        <v>300</v>
       </c>
       <c r="J14" s="26">
         <f>Apartment8!D14</f>
@@ -20907,7 +20963,7 @@
       </c>
       <c r="D15" s="26">
         <f>Apartment2!D15</f>
-        <v>0</v>
+        <v>150</v>
       </c>
       <c r="E15" s="26">
         <f>Apartment3!D15</f>
@@ -20969,7 +21025,7 @@
       </c>
       <c r="D16" s="26">
         <f>Apartment2!D16</f>
-        <v>0</v>
+        <v>150</v>
       </c>
       <c r="E16" s="26">
         <f>Apartment3!D16</f>
@@ -21031,7 +21087,7 @@
       </c>
       <c r="D17" s="26">
         <f>Apartment2!D17</f>
-        <v>0</v>
+        <v>150</v>
       </c>
       <c r="E17" s="26">
         <f>Apartment3!D17</f>
@@ -21345,11 +21401,11 @@
     </row>
     <row r="3" spans="1:14" ht="18" x14ac:dyDescent="0.25">
       <c r="C3" s="83"/>
-      <c r="G3" s="109" t="s">
+      <c r="G3" s="103" t="s">
         <v>94</v>
       </c>
-      <c r="H3" s="109"/>
-      <c r="I3" s="109"/>
+      <c r="H3" s="103"/>
+      <c r="I3" s="103"/>
     </row>
     <row r="4" spans="1:14" ht="36" x14ac:dyDescent="0.2">
       <c r="A4" s="12" t="s">
@@ -21417,12 +21473,12 @@
       </c>
       <c r="C6" s="91">
         <f>Apartment2!D4</f>
-        <v>825</v>
+        <v>1425</v>
       </c>
       <c r="D6" s="92"/>
       <c r="E6" s="94">
         <f t="shared" ref="E6:E18" si="0">D6-C6</f>
-        <v>-825</v>
+        <v>-1425</v>
       </c>
       <c r="F6" s="2" t="s">
         <v>51</v>
@@ -21444,12 +21500,12 @@
       </c>
       <c r="C7" s="91">
         <f>Apartment3!D4</f>
-        <v>1200</v>
+        <v>1350</v>
       </c>
       <c r="D7" s="92"/>
       <c r="E7" s="94">
         <f t="shared" si="0"/>
-        <v>-1200</v>
+        <v>-1350</v>
       </c>
       <c r="F7" s="2" t="s">
         <v>48</v>
@@ -21471,12 +21527,12 @@
       </c>
       <c r="C8" s="91">
         <f>Apartment4!D4</f>
-        <v>1200</v>
+        <v>1350</v>
       </c>
       <c r="D8" s="92"/>
       <c r="E8" s="94">
         <f t="shared" si="0"/>
-        <v>-1200</v>
+        <v>-1350</v>
       </c>
       <c r="F8" s="2" t="s">
         <v>48</v>
@@ -21551,12 +21607,12 @@
       </c>
       <c r="C11" s="91">
         <f>Apartment7!D4</f>
-        <v>2400</v>
+        <v>2700</v>
       </c>
       <c r="D11" s="92"/>
       <c r="E11" s="94">
         <f t="shared" si="0"/>
-        <v>-2400</v>
+        <v>-2700</v>
       </c>
       <c r="F11" s="2" t="s">
         <v>48</v>
@@ -23724,14 +23780,14 @@
       <c r="F20" s="8"/>
       <c r="G20" s="8"/>
       <c r="H20" s="2"/>
-      <c r="I20" s="110" t="s">
+      <c r="I20" s="104" t="s">
         <v>118</v>
       </c>
-      <c r="J20" s="110"/>
-      <c r="K20" s="110"/>
-      <c r="L20" s="110"/>
-      <c r="M20" s="110"/>
-      <c r="N20" s="110"/>
+      <c r="J20" s="104"/>
+      <c r="K20" s="104"/>
+      <c r="L20" s="104"/>
+      <c r="M20" s="104"/>
+      <c r="N20" s="104"/>
     </row>
     <row r="21" spans="1:17" ht="23.25" x14ac:dyDescent="0.35">
       <c r="A21" s="8"/>
@@ -23742,14 +23798,14 @@
       <c r="F21" s="8"/>
       <c r="G21" s="8"/>
       <c r="H21" s="2"/>
-      <c r="I21" s="110" t="s">
+      <c r="I21" s="104" t="s">
         <v>238</v>
       </c>
-      <c r="J21" s="110"/>
-      <c r="K21" s="110"/>
-      <c r="L21" s="110"/>
-      <c r="M21" s="110"/>
-      <c r="N21" s="110"/>
+      <c r="J21" s="104"/>
+      <c r="K21" s="104"/>
+      <c r="L21" s="104"/>
+      <c r="M21" s="104"/>
+      <c r="N21" s="104"/>
     </row>
     <row r="22" spans="1:17" ht="18" x14ac:dyDescent="0.25">
       <c r="A22" s="8"/>
@@ -23787,13 +23843,13 @@
       <c r="G23" s="48"/>
       <c r="H23" s="48"/>
       <c r="I23" s="48"/>
-      <c r="J23" s="111"/>
-      <c r="K23" s="111"/>
-      <c r="L23" s="111"/>
-      <c r="M23" s="111"/>
-      <c r="N23" s="111"/>
-      <c r="O23" s="111"/>
-      <c r="P23" s="111"/>
+      <c r="J23" s="105"/>
+      <c r="K23" s="105"/>
+      <c r="L23" s="105"/>
+      <c r="M23" s="105"/>
+      <c r="N23" s="105"/>
+      <c r="O23" s="105"/>
+      <c r="P23" s="105"/>
     </row>
     <row r="24" spans="1:17" ht="18" x14ac:dyDescent="0.25">
       <c r="A24" s="8"/>
@@ -23807,13 +23863,13 @@
       </c>
       <c r="H24" s="8"/>
       <c r="I24" s="8"/>
-      <c r="J24" s="111"/>
-      <c r="K24" s="111"/>
-      <c r="L24" s="111"/>
-      <c r="M24" s="111"/>
-      <c r="N24" s="111"/>
-      <c r="O24" s="111"/>
-      <c r="P24" s="111"/>
+      <c r="J24" s="105"/>
+      <c r="K24" s="105"/>
+      <c r="L24" s="105"/>
+      <c r="M24" s="105"/>
+      <c r="N24" s="105"/>
+      <c r="O24" s="105"/>
+      <c r="P24" s="105"/>
     </row>
     <row r="25" spans="1:17" ht="36" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="8"/>
@@ -23827,13 +23883,13 @@
       </c>
       <c r="H25" s="48"/>
       <c r="I25" s="48"/>
-      <c r="J25" s="111"/>
-      <c r="K25" s="111"/>
-      <c r="L25" s="111"/>
-      <c r="M25" s="111"/>
-      <c r="N25" s="111"/>
-      <c r="O25" s="111"/>
-      <c r="P25" s="111"/>
+      <c r="J25" s="105"/>
+      <c r="K25" s="105"/>
+      <c r="L25" s="105"/>
+      <c r="M25" s="105"/>
+      <c r="N25" s="105"/>
+      <c r="O25" s="105"/>
+      <c r="P25" s="105"/>
     </row>
     <row r="26" spans="1:17" ht="23.25" x14ac:dyDescent="0.35">
       <c r="A26" s="8"/>
